--- a/Cotacao_Servicos_Saude_Unidade_Movel_2026-10-07.xlsx
+++ b/Cotacao_Servicos_Saude_Unidade_Movel_2026-10-07.xlsx
@@ -61,7 +61,7 @@
     <t xml:space="preserve">VALOR GLOBAL ESTIMADO</t>
   </si>
   <si>
-    <t xml:space="preserve">Metodologia: para cada item foram reunidos três preços de contratações públicas (credenciamentos, pregões, atas de registro de preços, contratos e tabelas de credenciamento de órgãos e consórcios públicos), indicados nas colunas Fonte/Valor/Link de cada lote, com menor, média, mediana e maior valor. O valor unitário de referência de cada item é o valor adotado pela Administração para o credenciamento, aplicado uniformemente a todos os credenciados, e foi confrontado com as cotações para verificar sua compatibilidade com o mercado. Itens marcados como 'análogo' usam procedimento equivalente quando não havia o item idêntico na fonte. Os quantitativos são estimativas do TR e não geram obrigação de execução.</t>
+    <t xml:space="preserve">Metodologia: para cada item foram reunidos até três preços de contratações públicas (credenciamentos, pregões, atas de registro de preços, contratos e tabelas de credenciamento de órgãos e consórcios públicos), indicados nas colunas Fonte/Valor/Link de cada lote. O valor unitário de referência de cada item corresponde à MEDIANA dos preços coletados (Lei nº 14.133/2021, art. 23; IN SEGES/ME nº 65/2021, art. 6º), apresentada ao lado do menor preço, da média e do maior preço. Itens marcados como 'análogo' usam procedimento equivalente quando não havia o item idêntico na fonte. Itens com menos de três preços estão sujeitos à justificativa prevista no art. 6º, §5º, da IN SEGES/ME nº 65/2021. Os quantitativos são estimativas do TR e não geram obrigação de execução.</t>
   </si>
   <si>
     <t xml:space="preserve">LOTE 1 – EXAMES DE MAMOGRAFIA BILATERAL (unidade móvel)</t>
@@ -118,7 +118,7 @@
     <t xml:space="preserve">Maior (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor unit. referência (R$)</t>
+    <t xml:space="preserve">Valor unit. referência (R$) = mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Valor total estimado (R$)</t>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="B6" s="5" t="n">
         <f aca="false">'Lote 1 - Mamografia'!S4</f>
-        <v>4665118</v>
+        <v>4615986</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="B7" s="5" t="n">
         <f aca="false">'Lote 2 - Consultas'!S18</f>
-        <v>22774370.25</v>
+        <v>22868454.05</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">'Lote 3 - Exames'!S12</f>
-        <v>18905067.11</v>
+        <v>20674426.8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="B9" s="5" t="n">
         <f aca="false">'Lote 4 - Ressonancia'!S5</f>
-        <v>11650694.4</v>
+        <v>11851030</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="B10" s="5" t="n">
         <f aca="false">'Lote 5 - Odontologia'!S67</f>
-        <v>24700500.24</v>
+        <v>20579182.67</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="false">SUM(B6:B10)</f>
-        <v>82695750</v>
+        <v>80589079.52</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1538,11 +1538,12 @@
         <v>140.45</v>
       </c>
       <c r="R3" s="14" t="n">
-        <v>134.83</v>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+        <v>133.41</v>
       </c>
       <c r="S3" s="12" t="n">
-        <f aca="false">D3*R3</f>
-        <v>4665118</v>
+        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+        <v>4615986</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1568,7 +1569,7 @@
       <c r="R4" s="15"/>
       <c r="S4" s="7" t="n">
         <f aca="false">SUM(S3:S3)</f>
-        <v>4665118</v>
+        <v>4615986</v>
       </c>
     </row>
   </sheetData>
@@ -1755,11 +1756,12 @@
         <v>100</v>
       </c>
       <c r="R3" s="14" t="n">
-        <v>93</v>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+        <v>92.48</v>
       </c>
       <c r="S3" s="12" t="n">
-        <f aca="false">D3*R3</f>
-        <v>4039920</v>
+        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+        <v>4017331.2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1819,11 +1821,12 @@
         <v>115</v>
       </c>
       <c r="R4" s="14" t="n">
-        <v>95.31</v>
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
+        <v>97.63</v>
       </c>
       <c r="S4" s="12" t="n">
-        <f aca="false">D4*R4</f>
-        <v>2846433.15</v>
+        <f aca="false">IF(ISNUMBER(R4),D4*R4,0)</f>
+        <v>2915719.95</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1883,11 +1886,12 @@
         <v>125.24</v>
       </c>
       <c r="R5" s="14" t="n">
-        <v>97.62</v>
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
+        <v>100</v>
       </c>
       <c r="S5" s="12" t="n">
-        <f aca="false">D5*R5</f>
-        <v>2385344.7</v>
+        <f aca="false">IF(ISNUMBER(R5),D5*R5,0)</f>
+        <v>2443500</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1947,11 +1951,12 @@
         <v>115</v>
       </c>
       <c r="R6" s="14" t="n">
-        <v>107.59</v>
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
+        <v>114.97</v>
       </c>
       <c r="S6" s="12" t="n">
-        <f aca="false">D6*R6</f>
-        <v>2336854.8</v>
+        <f aca="false">IF(ISNUMBER(R6),D6*R6,0)</f>
+        <v>2497148.4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2011,11 +2016,12 @@
         <v>161.67</v>
       </c>
       <c r="R7" s="14" t="n">
-        <v>92.64</v>
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
+        <v>96.5</v>
       </c>
       <c r="S7" s="12" t="n">
-        <f aca="false">D7*R7</f>
-        <v>2012140.8</v>
+        <f aca="false">IF(ISNUMBER(R7),D7*R7,0)</f>
+        <v>2095980</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2075,11 +2081,12 @@
         <v>115</v>
       </c>
       <c r="R8" s="14" t="n">
-        <v>95.31</v>
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
+        <v>103.2</v>
       </c>
       <c r="S8" s="12" t="n">
-        <f aca="false">D8*R8</f>
-        <v>1380088.8</v>
+        <f aca="false">IF(ISNUMBER(R8),D8*R8,0)</f>
+        <v>1494336</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2139,11 +2146,12 @@
         <v>115</v>
       </c>
       <c r="R9" s="14" t="n">
-        <v>112.64</v>
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
+        <v>101.56</v>
       </c>
       <c r="S9" s="12" t="n">
-        <f aca="false">D9*R9</f>
-        <v>1529088</v>
+        <f aca="false">IF(ISNUMBER(R9),D9*R9,0)</f>
+        <v>1378677</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2203,11 +2211,12 @@
         <v>116.67</v>
       </c>
       <c r="R10" s="14" t="n">
-        <v>112.64</v>
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
+        <v>115</v>
       </c>
       <c r="S10" s="12" t="n">
-        <f aca="false">D10*R10</f>
-        <v>1427148.8</v>
+        <f aca="false">IF(ISNUMBER(R10),D10*R10,0)</f>
+        <v>1457050</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2267,11 +2276,12 @@
         <v>115</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>112.64</v>
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
+        <v>90</v>
       </c>
       <c r="S11" s="12" t="n">
-        <f aca="false">D11*R11</f>
-        <v>1325209.6</v>
+        <f aca="false">IF(ISNUMBER(R11),D11*R11,0)</f>
+        <v>1058850</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2331,11 +2341,12 @@
         <v>115</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>112.64</v>
+        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",ROUND(P12,2))</f>
+        <v>105.87</v>
       </c>
       <c r="S12" s="12" t="n">
-        <f aca="false">D12*R12</f>
-        <v>1223270.4</v>
+        <f aca="false">IF(ISNUMBER(R12),D12*R12,0)</f>
+        <v>1149748.2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2395,11 +2406,12 @@
         <v>115</v>
       </c>
       <c r="R13" s="14" t="n">
-        <v>93</v>
+        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",ROUND(P13,2))</f>
+        <v>106.1</v>
       </c>
       <c r="S13" s="12" t="n">
-        <f aca="false">D13*R13</f>
-        <v>925815</v>
+        <f aca="false">IF(ISNUMBER(R13),D13*R13,0)</f>
+        <v>1056225.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2459,11 +2471,12 @@
         <v>115</v>
       </c>
       <c r="R14" s="14" t="n">
-        <v>93.72</v>
+        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",ROUND(P14,2))</f>
+        <v>97.63</v>
       </c>
       <c r="S14" s="12" t="n">
-        <f aca="false">D14*R14</f>
-        <v>339266.4</v>
+        <f aca="false">IF(ISNUMBER(R14),D14*R14,0)</f>
+        <v>353420.6</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2523,11 +2536,12 @@
         <v>115</v>
       </c>
       <c r="R15" s="14" t="n">
-        <v>104.7</v>
+        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",ROUND(P15,2))</f>
+        <v>90</v>
       </c>
       <c r="S15" s="12" t="n">
-        <f aca="false">D15*R15</f>
-        <v>284260.5</v>
+        <f aca="false">IF(ISNUMBER(R15),D15*R15,0)</f>
+        <v>244350</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2587,11 +2601,12 @@
         <v>115</v>
       </c>
       <c r="R16" s="14" t="n">
-        <v>95.31</v>
+        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",ROUND(P16,2))</f>
+        <v>91.96</v>
       </c>
       <c r="S16" s="12" t="n">
-        <f aca="false">D16*R16</f>
-        <v>517533.3</v>
+        <f aca="false">IF(ISNUMBER(R16),D16*R16,0)</f>
+        <v>499342.8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2651,11 +2666,12 @@
         <v>161.67</v>
       </c>
       <c r="R17" s="14" t="n">
-        <v>93</v>
+        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",ROUND(P17,2))</f>
+        <v>95.2</v>
       </c>
       <c r="S17" s="12" t="n">
-        <f aca="false">D17*R17</f>
-        <v>201996</v>
+        <f aca="false">IF(ISNUMBER(R17),D17*R17,0)</f>
+        <v>206774.4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2681,7 +2697,7 @@
       <c r="R18" s="15"/>
       <c r="S18" s="7" t="n">
         <f aca="false">SUM(S3:S17)</f>
-        <v>22774370.25</v>
+        <v>22868454.05</v>
       </c>
     </row>
   </sheetData>
@@ -2910,11 +2926,12 @@
         <v>136.91</v>
       </c>
       <c r="R3" s="14" t="n">
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+        <v>115.05</v>
       </c>
       <c r="S3" s="12" t="n">
-        <f aca="false">D3*R3</f>
-        <v>5536640</v>
+        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+        <v>7547280</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2974,11 +2991,12 @@
         <v>150</v>
       </c>
       <c r="R4" s="14" t="n">
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
+        <v>90</v>
       </c>
       <c r="S4" s="12" t="n">
-        <f aca="false">D4*R4</f>
-        <v>882824</v>
+        <f aca="false">IF(ISNUMBER(R4),D4*R4,0)</f>
+        <v>941400</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3038,11 +3056,12 @@
         <v>135</v>
       </c>
       <c r="R5" s="14" t="n">
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
+        <v>89.72</v>
       </c>
       <c r="S5" s="12" t="n">
-        <f aca="false">D5*R5</f>
-        <v>1799830</v>
+        <f aca="false">IF(ISNUMBER(R5),D5*R5,0)</f>
+        <v>1913279</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3102,11 +3121,12 @@
         <v>90</v>
       </c>
       <c r="R6" s="14" t="n">
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
+        <v>85.72</v>
       </c>
       <c r="S6" s="12" t="n">
-        <f aca="false">D6*R6</f>
-        <v>882824</v>
+        <f aca="false">IF(ISNUMBER(R6),D6*R6,0)</f>
+        <v>896631.2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3166,11 +3186,12 @@
         <v>244.92</v>
       </c>
       <c r="R7" s="14" t="n">
-        <v>273.31</v>
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
+        <v>211.26</v>
       </c>
       <c r="S7" s="12" t="n">
-        <f aca="false">D7*R7</f>
-        <v>4068219.35</v>
+        <f aca="false">IF(ISNUMBER(R7),D7*R7,0)</f>
+        <v>3144605.1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3230,11 +3251,12 @@
         <v>187.17</v>
       </c>
       <c r="R8" s="14" t="n">
-        <v>122.24</v>
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
+        <v>75</v>
       </c>
       <c r="S8" s="12" t="n">
-        <f aca="false">D8*R8</f>
-        <v>387989.76</v>
+        <f aca="false">IF(ISNUMBER(R8),D8*R8,0)</f>
+        <v>238050</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3294,11 +3316,12 @@
         <v>90.74</v>
       </c>
       <c r="R9" s="14" t="n">
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
+        <v>90</v>
       </c>
       <c r="S9" s="12" t="n">
-        <f aca="false">D9*R9</f>
-        <v>381910</v>
+        <f aca="false">IF(ISNUMBER(R9),D9*R9,0)</f>
+        <v>407250</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3358,11 +3381,12 @@
         <v>100.74</v>
       </c>
       <c r="R10" s="14" t="n">
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
+        <v>90.74</v>
       </c>
       <c r="S10" s="12" t="n">
-        <f aca="false">D10*R10</f>
-        <v>381910</v>
+        <f aca="false">IF(ISNUMBER(R10),D10*R10,0)</f>
+        <v>410598.5</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3422,11 +3446,12 @@
         <v>155</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
+        <v>95.31</v>
       </c>
       <c r="S11" s="12" t="n">
-        <f aca="false">D11*R11</f>
-        <v>4582920</v>
+        <f aca="false">IF(ISNUMBER(R11),D11*R11,0)</f>
+        <v>5175333</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3452,7 +3477,7 @@
       <c r="R12" s="15"/>
       <c r="S12" s="7" t="n">
         <f aca="false">SUM(S3:S11)</f>
-        <v>18905067.11</v>
+        <v>20674426.8</v>
       </c>
     </row>
   </sheetData>
@@ -3663,11 +3688,12 @@
         <v>543.33</v>
       </c>
       <c r="R3" s="14" t="n">
-        <v>403.2</v>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+        <v>420</v>
       </c>
       <c r="S3" s="12" t="n">
-        <f aca="false">D3*R3</f>
-        <v>10946880</v>
+        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+        <v>11403000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3727,11 +3753,12 @@
         <v>300</v>
       </c>
       <c r="R4" s="14" t="n">
-        <v>172.8</v>
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
+        <v>110</v>
       </c>
       <c r="S4" s="12" t="n">
-        <f aca="false">D4*R4</f>
-        <v>703814.4</v>
+        <f aca="false">IF(ISNUMBER(R4),D4*R4,0)</f>
+        <v>448030</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3757,7 +3784,7 @@
       <c r="R5" s="15"/>
       <c r="S5" s="7" t="n">
         <f aca="false">SUM(S3:S4)</f>
-        <v>11650694.4</v>
+        <v>11851030</v>
       </c>
     </row>
   </sheetData>
@@ -3947,11 +3974,12 @@
         <v>90.1</v>
       </c>
       <c r="R3" s="14" t="n">
-        <v>86.28</v>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+        <v>78.4</v>
       </c>
       <c r="S3" s="12" t="n">
-        <f aca="false">D3*R3</f>
-        <v>7775381.04</v>
+        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+        <v>7065251.2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4011,11 +4039,12 @@
         <v>76.05</v>
       </c>
       <c r="R4" s="14" t="n">
-        <v>69.81</v>
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
+        <v>53.8</v>
       </c>
       <c r="S4" s="12" t="n">
-        <f aca="false">D4*R4</f>
-        <v>63178.05</v>
+        <f aca="false">IF(ISNUMBER(R4),D4*R4,0)</f>
+        <v>48689</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4075,11 +4104,12 @@
         <v>76.05</v>
       </c>
       <c r="R5" s="14" t="n">
-        <v>69.81</v>
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
+        <v>53.8</v>
       </c>
       <c r="S5" s="12" t="n">
-        <f aca="false">D5*R5</f>
-        <v>63178.05</v>
+        <f aca="false">IF(ISNUMBER(R5),D5*R5,0)</f>
+        <v>48689</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4139,11 +4169,12 @@
         <v>98.27</v>
       </c>
       <c r="R6" s="14" t="n">
-        <v>90.2</v>
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
+        <v>83.97</v>
       </c>
       <c r="S6" s="12" t="n">
-        <f aca="false">D6*R6</f>
-        <v>81631</v>
+        <f aca="false">IF(ISNUMBER(R6),D6*R6,0)</f>
+        <v>75992.85</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4199,11 +4230,12 @@
         <v>116.21</v>
       </c>
       <c r="R7" s="14" t="n">
-        <v>106.67</v>
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
+        <v>99.21</v>
       </c>
       <c r="S7" s="12" t="n">
-        <f aca="false">D7*R7</f>
-        <v>146777.92</v>
+        <f aca="false">IF(ISNUMBER(R7),D7*R7,0)</f>
+        <v>136512.96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4263,11 +4295,12 @@
         <v>109.36</v>
       </c>
       <c r="R8" s="14" t="n">
-        <v>104.71</v>
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
+        <v>80.7</v>
       </c>
       <c r="S8" s="12" t="n">
-        <f aca="false">D8*R8</f>
-        <v>134238.22</v>
+        <f aca="false">IF(ISNUMBER(R8),D8*R8,0)</f>
+        <v>103457.4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4327,11 +4360,12 @@
         <v>90.1</v>
       </c>
       <c r="R9" s="14" t="n">
-        <v>86.28</v>
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
+        <v>66.5</v>
       </c>
       <c r="S9" s="12" t="n">
-        <f aca="false">D9*R9</f>
-        <v>1285830.84</v>
+        <f aca="false">IF(ISNUMBER(R9),D9*R9,0)</f>
+        <v>991049.5</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4391,11 +4425,12 @@
         <v>90</v>
       </c>
       <c r="R10" s="14" t="n">
-        <v>90.2</v>
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
+        <v>82.42</v>
       </c>
       <c r="S10" s="12" t="n">
-        <f aca="false">D10*R10</f>
-        <v>403284.2</v>
+        <f aca="false">IF(ISNUMBER(R10),D10*R10,0)</f>
+        <v>368499.82</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4455,11 +4490,12 @@
         <v>73</v>
       </c>
       <c r="R11" s="14" t="n">
-        <v>69.81</v>
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
+        <v>72.91</v>
       </c>
       <c r="S11" s="12" t="n">
-        <f aca="false">D11*R11</f>
-        <v>63178.05</v>
+        <f aca="false">IF(ISNUMBER(R11),D11*R11,0)</f>
+        <v>65983.55</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4519,11 +4555,12 @@
         <v>96.28</v>
       </c>
       <c r="R12" s="14" t="n">
-        <v>92.16</v>
+        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",ROUND(P12,2))</f>
+        <v>71</v>
       </c>
       <c r="S12" s="12" t="n">
-        <f aca="false">D12*R12</f>
-        <v>83404.8</v>
+        <f aca="false">IF(ISNUMBER(R12),D12*R12,0)</f>
+        <v>64255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4583,11 +4620,12 @@
         <v>167</v>
       </c>
       <c r="R13" s="14" t="n">
-        <v>131.38</v>
+        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",ROUND(P13,2))</f>
+        <v>104.5</v>
       </c>
       <c r="S13" s="12" t="n">
-        <f aca="false">D13*R13</f>
-        <v>118898.9</v>
+        <f aca="false">IF(ISNUMBER(R13),D13*R13,0)</f>
+        <v>94572.5</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4647,11 +4685,12 @@
         <v>166</v>
       </c>
       <c r="R14" s="14" t="n">
-        <v>141.17</v>
+        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",ROUND(P14,2))</f>
+        <v>108.75</v>
       </c>
       <c r="S14" s="12" t="n">
-        <f aca="false">D14*R14</f>
-        <v>717567.11</v>
+        <f aca="false">IF(ISNUMBER(R14),D14*R14,0)</f>
+        <v>552776.25</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4703,11 +4742,12 @@
         <v>66.5</v>
       </c>
       <c r="R15" s="14" t="n">
-        <v>86.28</v>
+        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",ROUND(P15,2))</f>
+        <v>66.5</v>
       </c>
       <c r="S15" s="12" t="n">
-        <f aca="false">D15*R15</f>
-        <v>78083.4</v>
+        <f aca="false">IF(ISNUMBER(R15),D15*R15,0)</f>
+        <v>60182.5</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4759,11 +4799,12 @@
         <v>82.2</v>
       </c>
       <c r="R16" s="14" t="n">
-        <v>106.67</v>
+        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",ROUND(P16,2))</f>
+        <v>82.2</v>
       </c>
       <c r="S16" s="12" t="n">
-        <f aca="false">D16*R16</f>
-        <v>96536.35</v>
+        <f aca="false">IF(ISNUMBER(R16),D16*R16,0)</f>
+        <v>74391</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4815,11 +4856,12 @@
         <v>107.6</v>
       </c>
       <c r="R17" s="14" t="n">
-        <v>139.62</v>
+        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",ROUND(P17,2))</f>
+        <v>107.6</v>
       </c>
       <c r="S17" s="12" t="n">
-        <f aca="false">D17*R17</f>
-        <v>126356.1</v>
+        <f aca="false">IF(ISNUMBER(R17),D17*R17,0)</f>
+        <v>97378</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4871,11 +4913,12 @@
         <v>107.6</v>
       </c>
       <c r="R18" s="14" t="n">
-        <v>139.62</v>
+        <f aca="false">IF(COUNT(F18,I18,L18)=0,"Sem cotação",ROUND(P18,2))</f>
+        <v>107.6</v>
       </c>
       <c r="S18" s="12" t="n">
-        <f aca="false">D18*R18</f>
-        <v>126356.1</v>
+        <f aca="false">IF(ISNUMBER(R18),D18*R18,0)</f>
+        <v>97378</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4927,11 +4970,12 @@
         <v>66.5</v>
       </c>
       <c r="R19" s="14" t="n">
-        <v>86.28</v>
+        <f aca="false">IF(COUNT(F19,I19,L19)=0,"Sem cotação",ROUND(P19,2))</f>
+        <v>66.5</v>
       </c>
       <c r="S19" s="12" t="n">
-        <f aca="false">D19*R19</f>
-        <v>78083.4</v>
+        <f aca="false">IF(ISNUMBER(R19),D19*R19,0)</f>
+        <v>60182.5</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4983,11 +5027,12 @@
         <v>107.6</v>
       </c>
       <c r="R20" s="14" t="n">
-        <v>139.62</v>
+        <f aca="false">IF(COUNT(F20,I20,L20)=0,"Sem cotação",ROUND(P20,2))</f>
+        <v>107.6</v>
       </c>
       <c r="S20" s="12" t="n">
-        <f aca="false">D20*R20</f>
-        <v>126356.1</v>
+        <f aca="false">IF(ISNUMBER(R20),D20*R20,0)</f>
+        <v>97378</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5047,11 +5092,12 @@
         <v>127.89</v>
       </c>
       <c r="R21" s="14" t="n">
-        <v>161.97</v>
+        <f aca="false">IF(COUNT(F21,I21,L21)=0,"Sem cotação",ROUND(P21,2))</f>
+        <v>124.8</v>
       </c>
       <c r="S21" s="12" t="n">
-        <f aca="false">D21*R21</f>
-        <v>500811.24</v>
+        <f aca="false">IF(ISNUMBER(R21),D21*R21,0)</f>
+        <v>385881.6</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5111,11 +5157,12 @@
         <v>70.5</v>
       </c>
       <c r="R22" s="14" t="n">
-        <v>88.24</v>
+        <f aca="false">IF(COUNT(F22,I22,L22)=0,"Sem cotação",ROUND(P22,2))</f>
+        <v>68</v>
       </c>
       <c r="S22" s="12" t="n">
-        <f aca="false">D22*R22</f>
-        <v>958286.4</v>
+        <f aca="false">IF(ISNUMBER(R22),D22*R22,0)</f>
+        <v>738480</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5175,11 +5222,12 @@
         <v>104.25</v>
       </c>
       <c r="R23" s="14" t="n">
-        <v>135.3</v>
+        <f aca="false">IF(COUNT(F23,I23,L23)=0,"Sem cotação",ROUND(P23,2))</f>
+        <v>99</v>
       </c>
       <c r="S23" s="12" t="n">
-        <f aca="false">D23*R23</f>
-        <v>24489.3</v>
+        <f aca="false">IF(ISNUMBER(R23),D23*R23,0)</f>
+        <v>17919</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5239,11 +5287,12 @@
         <v>124.8</v>
       </c>
       <c r="R24" s="14" t="n">
-        <v>161.97</v>
+        <f aca="false">IF(COUNT(F24,I24,L24)=0,"Sem cotação",ROUND(P24,2))</f>
+        <v>99</v>
       </c>
       <c r="S24" s="12" t="n">
-        <f aca="false">D24*R24</f>
-        <v>409460.16</v>
+        <f aca="false">IF(ISNUMBER(R24),D24*R24,0)</f>
+        <v>250272</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5303,11 +5352,12 @@
         <v>113</v>
       </c>
       <c r="R25" s="14" t="n">
-        <v>135.3</v>
+        <f aca="false">IF(COUNT(F25,I25,L25)=0,"Sem cotação",ROUND(P25,2))</f>
+        <v>104.25</v>
       </c>
       <c r="S25" s="12" t="n">
-        <f aca="false">D25*R25</f>
-        <v>13124.1</v>
+        <f aca="false">IF(ISNUMBER(R25),D25*R25,0)</f>
+        <v>10112.25</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5367,11 +5417,12 @@
         <v>152</v>
       </c>
       <c r="R26" s="14" t="n">
-        <v>222.37</v>
+        <f aca="false">IF(COUNT(F26,I26,L26)=0,"Sem cotação",ROUND(P26,2))</f>
+        <v>139.6</v>
       </c>
       <c r="S26" s="12" t="n">
-        <f aca="false">D26*R26</f>
-        <v>22681.74</v>
+        <f aca="false">IF(ISNUMBER(R26),D26*R26,0)</f>
+        <v>14239.2</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5431,11 +5482,12 @@
         <v>171.35</v>
       </c>
       <c r="R27" s="14" t="n">
-        <v>222.37</v>
+        <f aca="false">IF(COUNT(F27,I27,L27)=0,"Sem cotação",ROUND(P27,2))</f>
+        <v>166</v>
       </c>
       <c r="S27" s="12" t="n">
-        <f aca="false">D27*R27</f>
-        <v>10673.76</v>
+        <f aca="false">IF(ISNUMBER(R27),D27*R27,0)</f>
+        <v>7968</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5491,11 +5543,12 @@
         <v>235.75</v>
       </c>
       <c r="R28" s="14" t="n">
-        <v>305.91</v>
+        <f aca="false">IF(COUNT(F28,I28,L28)=0,"Sem cotação",ROUND(P28,2))</f>
+        <v>218.13</v>
       </c>
       <c r="S28" s="12" t="n">
-        <f aca="false">D28*R28</f>
-        <v>276848.55</v>
+        <f aca="false">IF(ISNUMBER(R28),D28*R28,0)</f>
+        <v>197407.65</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5547,11 +5600,12 @@
         <v>136</v>
       </c>
       <c r="R29" s="14" t="n">
-        <v>176.48</v>
+        <f aca="false">IF(COUNT(F29,I29,L29)=0,"Sem cotação",ROUND(P29,2))</f>
+        <v>136</v>
       </c>
       <c r="S29" s="12" t="n">
-        <f aca="false">D29*R29</f>
-        <v>8471.04</v>
+        <f aca="false">IF(ISNUMBER(R29),D29*R29,0)</f>
+        <v>6528</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5611,11 +5665,12 @@
         <v>150</v>
       </c>
       <c r="R30" s="14" t="n">
-        <v>143.13</v>
+        <f aca="false">IF(COUNT(F30,I30,L30)=0,"Sem cotação",ROUND(P30,2))</f>
+        <v>149.56</v>
       </c>
       <c r="S30" s="12" t="n">
-        <f aca="false">D30*R30</f>
-        <v>129532.65</v>
+        <f aca="false">IF(ISNUMBER(R30),D30*R30,0)</f>
+        <v>135351.8</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5675,11 +5730,12 @@
         <v>76.05</v>
       </c>
       <c r="R31" s="14" t="n">
-        <v>69.81</v>
+        <f aca="false">IF(COUNT(F31,I31,L31)=0,"Sem cotação",ROUND(P31,2))</f>
+        <v>53.8</v>
       </c>
       <c r="S31" s="12" t="n">
-        <f aca="false">D31*R31</f>
-        <v>63178.05</v>
+        <f aca="false">IF(ISNUMBER(R31),D31*R31,0)</f>
+        <v>48689</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5739,11 +5795,12 @@
         <v>72.91</v>
       </c>
       <c r="R32" s="14" t="n">
-        <v>69.81</v>
+        <f aca="false">IF(COUNT(F32,I32,L32)=0,"Sem cotação",ROUND(P32,2))</f>
+        <v>53.8</v>
       </c>
       <c r="S32" s="12" t="n">
-        <f aca="false">D32*R32</f>
-        <v>63178.05</v>
+        <f aca="false">IF(ISNUMBER(R32),D32*R32,0)</f>
+        <v>48689</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5803,11 +5860,12 @@
         <v>64.31</v>
       </c>
       <c r="R33" s="14" t="n">
-        <v>61.57</v>
+        <f aca="false">IF(COUNT(F33,I33,L33)=0,"Sem cotação",ROUND(P33,2))</f>
+        <v>43.9</v>
       </c>
       <c r="S33" s="12" t="n">
-        <f aca="false">D33*R33</f>
-        <v>1350968.94</v>
+        <f aca="false">IF(ISNUMBER(R33),D33*R33,0)</f>
+        <v>963253.8</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5867,11 +5925,12 @@
         <v>94.22</v>
       </c>
       <c r="R34" s="14" t="n">
-        <v>90.2</v>
+        <f aca="false">IF(COUNT(F34,I34,L34)=0,"Sem cotação",ROUND(P34,2))</f>
+        <v>69.5</v>
       </c>
       <c r="S34" s="12" t="n">
-        <f aca="false">D34*R34</f>
-        <v>81631</v>
+        <f aca="false">IF(ISNUMBER(R34),D34*R34,0)</f>
+        <v>62897.5</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5931,11 +5990,12 @@
         <v>137.21</v>
       </c>
       <c r="R35" s="14" t="n">
-        <v>131.38</v>
+        <f aca="false">IF(COUNT(F35,I35,L35)=0,"Sem cotação",ROUND(P35,2))</f>
+        <v>101.25</v>
       </c>
       <c r="S35" s="12" t="n">
-        <f aca="false">D35*R35</f>
-        <v>118898.9</v>
+        <f aca="false">IF(ISNUMBER(R35),D35*R35,0)</f>
+        <v>91631.25</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5995,11 +6055,12 @@
         <v>641.01</v>
       </c>
       <c r="R36" s="14" t="n">
-        <v>613.78</v>
+        <f aca="false">IF(COUNT(F36,I36,L36)=0,"Sem cotação",ROUND(P36,2))</f>
+        <v>600</v>
       </c>
       <c r="S36" s="12" t="n">
-        <f aca="false">D36*R36</f>
-        <v>555470.9</v>
+        <f aca="false">IF(ISNUMBER(R36),D36*R36,0)</f>
+        <v>543000</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6059,11 +6120,12 @@
         <v>638</v>
       </c>
       <c r="R37" s="14" t="n">
-        <v>278.43</v>
+        <f aca="false">IF(COUNT(F37,I37,L37)=0,"Sem cotação",ROUND(P37,2))</f>
+        <v>290.89</v>
       </c>
       <c r="S37" s="12" t="n">
-        <f aca="false">D37*R37</f>
-        <v>67380.06</v>
+        <f aca="false">IF(ISNUMBER(R37),D37*R37,0)</f>
+        <v>70395.38</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6123,11 +6185,12 @@
         <v>653.36</v>
       </c>
       <c r="R38" s="14" t="n">
-        <v>521.28</v>
+        <f aca="false">IF(COUNT(F38,I38,L38)=0,"Sem cotação",ROUND(P38,2))</f>
+        <v>482</v>
       </c>
       <c r="S38" s="12" t="n">
-        <f aca="false">D38*R38</f>
-        <v>471758.4</v>
+        <f aca="false">IF(ISNUMBER(R38),D38*R38,0)</f>
+        <v>436210</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6187,11 +6250,12 @@
         <v>18.32</v>
       </c>
       <c r="R39" s="14" t="n">
-        <v>15.13</v>
+        <f aca="false">IF(COUNT(F39,I39,L39)=0,"Sem cotação",ROUND(P39,2))</f>
+        <v>15.82</v>
       </c>
       <c r="S39" s="12" t="n">
-        <f aca="false">D39*R39</f>
-        <v>13692.65</v>
+        <f aca="false">IF(ISNUMBER(R39),D39*R39,0)</f>
+        <v>14317.1</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6251,11 +6315,12 @@
         <v>257.8</v>
       </c>
       <c r="R40" s="14" t="n">
-        <v>334.54</v>
+        <f aca="false">IF(COUNT(F40,I40,L40)=0,"Sem cotação",ROUND(P40,2))</f>
+        <v>180</v>
       </c>
       <c r="S40" s="12" t="n">
-        <f aca="false">D40*R40</f>
-        <v>276330.04</v>
+        <f aca="false">IF(ISNUMBER(R40),D40*R40,0)</f>
+        <v>148680</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6315,11 +6380,12 @@
         <v>238</v>
       </c>
       <c r="R41" s="14" t="n">
-        <v>178.44</v>
+        <f aca="false">IF(COUNT(F41,I41,L41)=0,"Sem cotação",ROUND(P41,2))</f>
+        <v>186.38</v>
       </c>
       <c r="S41" s="12" t="n">
-        <f aca="false">D41*R41</f>
-        <v>161488.2</v>
+        <f aca="false">IF(ISNUMBER(R41),D41*R41,0)</f>
+        <v>168673.9</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6375,11 +6441,12 @@
         <v>68</v>
       </c>
       <c r="R42" s="14" t="n">
-        <v>88.24</v>
+        <f aca="false">IF(COUNT(F42,I42,L42)=0,"Sem cotação",ROUND(P42,2))</f>
+        <v>49</v>
       </c>
       <c r="S42" s="12" t="n">
-        <f aca="false">D42*R42</f>
-        <v>79857.2</v>
+        <f aca="false">IF(ISNUMBER(R42),D42*R42,0)</f>
+        <v>44345</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6439,11 +6506,12 @@
         <v>78.5</v>
       </c>
       <c r="R43" s="14" t="n">
-        <v>53.33</v>
+        <f aca="false">IF(COUNT(F43,I43,L43)=0,"Sem cotação",ROUND(P43,2))</f>
+        <v>41.1</v>
       </c>
       <c r="S43" s="12" t="n">
-        <f aca="false">D43*R43</f>
-        <v>79781.68</v>
+        <f aca="false">IF(ISNUMBER(R43),D43*R43,0)</f>
+        <v>61485.6</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6503,11 +6571,12 @@
         <v>90</v>
       </c>
       <c r="R44" s="14" t="n">
-        <v>90.2</v>
+        <f aca="false">IF(COUNT(F44,I44,L44)=0,"Sem cotação",ROUND(P44,2))</f>
+        <v>78.5</v>
       </c>
       <c r="S44" s="12" t="n">
-        <f aca="false">D44*R44</f>
-        <v>134939.2</v>
+        <f aca="false">IF(ISNUMBER(R44),D44*R44,0)</f>
+        <v>117436</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6567,11 +6636,12 @@
         <v>115.53</v>
       </c>
       <c r="R45" s="14" t="n">
-        <v>110.59</v>
+        <f aca="false">IF(COUNT(F45,I45,L45)=0,"Sem cotação",ROUND(P45,2))</f>
+        <v>107</v>
       </c>
       <c r="S45" s="12" t="n">
-        <f aca="false">D45*R45</f>
-        <v>70777.6</v>
+        <f aca="false">IF(ISNUMBER(R45),D45*R45,0)</f>
+        <v>68480</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6631,11 +6701,12 @@
         <v>121</v>
       </c>
       <c r="R46" s="14" t="n">
-        <v>110.59</v>
+        <f aca="false">IF(COUNT(F46,I46,L46)=0,"Sem cotação",ROUND(P46,2))</f>
+        <v>115.53</v>
       </c>
       <c r="S46" s="12" t="n">
-        <f aca="false">D46*R46</f>
-        <v>555935.93</v>
+        <f aca="false">IF(ISNUMBER(R46),D46*R46,0)</f>
+        <v>580769.31</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6695,11 +6766,12 @@
         <v>137.21</v>
       </c>
       <c r="R47" s="14" t="n">
-        <v>131.38</v>
+        <f aca="false">IF(COUNT(F47,I47,L47)=0,"Sem cotação",ROUND(P47,2))</f>
+        <v>101.25</v>
       </c>
       <c r="S47" s="12" t="n">
-        <f aca="false">D47*R47</f>
-        <v>417000.12</v>
+        <f aca="false">IF(ISNUMBER(R47),D47*R47,0)</f>
+        <v>321367.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6759,11 +6831,12 @@
         <v>180.2</v>
       </c>
       <c r="R48" s="14" t="n">
-        <v>172.56</v>
+        <f aca="false">IF(COUNT(F48,I48,L48)=0,"Sem cotação",ROUND(P48,2))</f>
+        <v>133</v>
       </c>
       <c r="S48" s="12" t="n">
-        <f aca="false">D48*R48</f>
-        <v>547705.44</v>
+        <f aca="false">IF(ISNUMBER(R48),D48*R48,0)</f>
+        <v>422142</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6823,11 +6896,12 @@
         <v>223.2</v>
       </c>
       <c r="R49" s="14" t="n">
-        <v>213.75</v>
+        <f aca="false">IF(COUNT(F49,I49,L49)=0,"Sem cotação",ROUND(P49,2))</f>
+        <v>164.75</v>
       </c>
       <c r="S49" s="12" t="n">
-        <f aca="false">D49*R49</f>
-        <v>580331.25</v>
+        <f aca="false">IF(ISNUMBER(R49),D49*R49,0)</f>
+        <v>447296.25</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6887,11 +6961,12 @@
         <v>248.99</v>
       </c>
       <c r="R50" s="14" t="n">
-        <v>238.46</v>
+        <f aca="false">IF(COUNT(F50,I50,L50)=0,"Sem cotação",ROUND(P50,2))</f>
+        <v>183.8</v>
       </c>
       <c r="S50" s="12" t="n">
-        <f aca="false">D50*R50</f>
-        <v>1198738.42</v>
+        <f aca="false">IF(ISNUMBER(R50),D50*R50,0)</f>
+        <v>923962.6</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6951,11 +7026,12 @@
         <v>223.2</v>
       </c>
       <c r="R51" s="14" t="n">
-        <v>213.75</v>
+        <f aca="false">IF(COUNT(F51,I51,L51)=0,"Sem cotação",ROUND(P51,2))</f>
+        <v>164.75</v>
       </c>
       <c r="S51" s="12" t="n">
-        <f aca="false">D51*R51</f>
-        <v>1074521.25</v>
+        <f aca="false">IF(ISNUMBER(R51),D51*R51,0)</f>
+        <v>828198.25</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7015,11 +7091,12 @@
         <v>248.99</v>
       </c>
       <c r="R52" s="14" t="n">
-        <v>238.46</v>
+        <f aca="false">IF(COUNT(F52,I52,L52)=0,"Sem cotação",ROUND(P52,2))</f>
+        <v>183.8</v>
       </c>
       <c r="S52" s="12" t="n">
-        <f aca="false">D52*R52</f>
-        <v>1309383.86</v>
+        <f aca="false">IF(ISNUMBER(R52),D52*R52,0)</f>
+        <v>1009245.8</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7079,11 +7156,12 @@
         <v>137.21</v>
       </c>
       <c r="R53" s="14" t="n">
-        <v>131.38</v>
+        <f aca="false">IF(COUNT(F53,I53,L53)=0,"Sem cotação",ROUND(P53,2))</f>
+        <v>101.25</v>
       </c>
       <c r="S53" s="12" t="n">
-        <f aca="false">D53*R53</f>
-        <v>118898.9</v>
+        <f aca="false">IF(ISNUMBER(R53),D53*R53,0)</f>
+        <v>91631.25</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7143,11 +7221,12 @@
         <v>71.36</v>
       </c>
       <c r="R54" s="14" t="n">
-        <v>65.49</v>
+        <f aca="false">IF(COUNT(F54,I54,L54)=0,"Sem cotação",ROUND(P54,2))</f>
+        <v>56.5</v>
       </c>
       <c r="S54" s="12" t="n">
-        <f aca="false">D54*R54</f>
-        <v>59268.45</v>
+        <f aca="false">IF(ISNUMBER(R54),D54*R54,0)</f>
+        <v>51132.5</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7207,11 +7286,12 @@
         <v>343.95</v>
       </c>
       <c r="R55" s="14" t="n">
-        <v>315.7</v>
+        <f aca="false">IF(COUNT(F55,I55,L55)=0,"Sem cotação",ROUND(P55,2))</f>
+        <v>329.77</v>
       </c>
       <c r="S55" s="12" t="n">
-        <f aca="false">D55*R55</f>
-        <v>285708.5</v>
+        <f aca="false">IF(ISNUMBER(R55),D55*R55,0)</f>
+        <v>298441.85</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7271,11 +7351,12 @@
         <v>252.11</v>
       </c>
       <c r="R56" s="14" t="n">
-        <v>233.33</v>
+        <f aca="false">IF(COUNT(F56,I56,L56)=0,"Sem cotação",ROUND(P56,2))</f>
+        <v>243.78</v>
       </c>
       <c r="S56" s="12" t="n">
-        <f aca="false">D56*R56</f>
-        <v>211163.65</v>
+        <f aca="false">IF(ISNUMBER(R56),D56*R56,0)</f>
+        <v>220620.9</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7331,11 +7412,12 @@
         <v>86.7</v>
       </c>
       <c r="R57" s="14" t="n">
-        <v>112.55</v>
+        <f aca="false">IF(COUNT(F57,I57,L57)=0,"Sem cotação",ROUND(P57,2))</f>
+        <v>53.35</v>
       </c>
       <c r="S57" s="12" t="n">
-        <f aca="false">D57*R57</f>
-        <v>101857.75</v>
+        <f aca="false">IF(ISNUMBER(R57),D57*R57,0)</f>
+        <v>48281.75</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7382,12 +7464,13 @@
         <f aca="false">IF(COUNT(F58,I58,L58)=0,"",MAX(F58,I58,L58))</f>
         <v/>
       </c>
-      <c r="R58" s="14" t="n">
-        <v>145.49</v>
+      <c r="R58" s="14" t="str">
+        <f aca="false">IF(COUNT(F58,I58,L58)=0,"Sem cotação",ROUND(P58,2))</f>
+        <v>Sem cotação</v>
       </c>
       <c r="S58" s="12" t="n">
-        <f aca="false">D58*R58</f>
-        <v>131668.45</v>
+        <f aca="false">IF(ISNUMBER(R58),D58*R58,0)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7447,11 +7530,12 @@
         <v>610.5</v>
       </c>
       <c r="R59" s="14" t="n">
-        <v>398.07</v>
+        <f aca="false">IF(COUNT(F59,I59,L59)=0,"Sem cotação",ROUND(P59,2))</f>
+        <v>415.75</v>
       </c>
       <c r="S59" s="12" t="n">
-        <f aca="false">D59*R59</f>
-        <v>78021.72</v>
+        <f aca="false">IF(ISNUMBER(R59),D59*R59,0)</f>
+        <v>81487</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7511,11 +7595,12 @@
         <v>123.5</v>
       </c>
       <c r="R60" s="14" t="n">
-        <v>93.33</v>
+        <f aca="false">IF(COUNT(F60,I60,L60)=0,"Sem cotação",ROUND(P60,2))</f>
+        <v>71.9</v>
       </c>
       <c r="S60" s="12" t="n">
-        <f aca="false">D60*R60</f>
-        <v>84463.65</v>
+        <f aca="false">IF(ISNUMBER(R60),D60*R60,0)</f>
+        <v>65069.5</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7567,11 +7652,12 @@
         <v>53.8</v>
       </c>
       <c r="R61" s="14" t="n">
-        <v>69.81</v>
+        <f aca="false">IF(COUNT(F61,I61,L61)=0,"Sem cotação",ROUND(P61,2))</f>
+        <v>53.8</v>
       </c>
       <c r="S61" s="12" t="n">
-        <f aca="false">D61*R61</f>
-        <v>63178.05</v>
+        <f aca="false">IF(ISNUMBER(R61),D61*R61,0)</f>
+        <v>48689</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7631,11 +7717,12 @@
         <v>339.58</v>
       </c>
       <c r="R62" s="14" t="n">
-        <v>317.66</v>
+        <f aca="false">IF(COUNT(F62,I62,L62)=0,"Sem cotação",ROUND(P62,2))</f>
+        <v>331.82</v>
       </c>
       <c r="S62" s="12" t="n">
-        <f aca="false">D62*R62</f>
-        <v>287482.3</v>
+        <f aca="false">IF(ISNUMBER(R62),D62*R62,0)</f>
+        <v>300297.1</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7691,11 +7778,12 @@
         <v>143.39</v>
       </c>
       <c r="R63" s="14" t="n">
-        <v>137.26</v>
+        <f aca="false">IF(COUNT(F63,I63,L63)=0,"Sem cotação",ROUND(P63,2))</f>
+        <v>124.57</v>
       </c>
       <c r="S63" s="12" t="n">
-        <f aca="false">D63*R63</f>
-        <v>16471.2</v>
+        <f aca="false">IF(ISNUMBER(R63),D63*R63,0)</f>
+        <v>14948.4</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7755,11 +7843,12 @@
         <v>259.88</v>
       </c>
       <c r="R64" s="14" t="n">
-        <v>231.37</v>
+        <f aca="false">IF(COUNT(F64,I64,L64)=0,"Sem cotação",ROUND(P64,2))</f>
+        <v>240.59</v>
       </c>
       <c r="S64" s="12" t="n">
-        <f aca="false">D64*R64</f>
-        <v>31234.95</v>
+        <f aca="false">IF(ISNUMBER(R64),D64*R64,0)</f>
+        <v>32479.65</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7819,11 +7908,12 @@
         <v>514.65</v>
       </c>
       <c r="R65" s="14" t="n">
-        <v>398.07</v>
+        <f aca="false">IF(COUNT(F65,I65,L65)=0,"Sem cotação",ROUND(P65,2))</f>
+        <v>415.75</v>
       </c>
       <c r="S65" s="12" t="n">
-        <f aca="false">D65*R65</f>
-        <v>28661.04</v>
+        <f aca="false">IF(ISNUMBER(R65),D65*R65,0)</f>
+        <v>29934</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7879,11 +7969,12 @@
         <v>156</v>
       </c>
       <c r="R66" s="14" t="n">
-        <v>94.11</v>
+        <f aca="false">IF(COUNT(F66,I66,L66)=0,"Sem cotação",ROUND(P66,2))</f>
+        <v>114.25</v>
       </c>
       <c r="S66" s="12" t="n">
-        <f aca="false">D66*R66</f>
-        <v>6775.92</v>
+        <f aca="false">IF(ISNUMBER(R66),D66*R66,0)</f>
+        <v>8226</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7909,7 +8000,7 @@
       <c r="R67" s="15"/>
       <c r="S67" s="7" t="n">
         <f aca="false">SUM(S3:S66)</f>
-        <v>24700500.24</v>
+        <v>20579182.67</v>
       </c>
     </row>
   </sheetData>

--- a/Cotacao_Servicos_Saude_Unidade_Movel_2026-10-07.xlsx
+++ b/Cotacao_Servicos_Saude_Unidade_Movel_2026-10-07.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="884" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="246">
   <si>
     <t xml:space="preserve">COTAÇÃO DE PREÇOS DE REFERÊNCIA – SERVIÇOS ESPECIALIZADOS EM SAÚDE EM UNIDADES MÓVEIS (Carretas)</t>
   </si>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">VALOR GLOBAL ESTIMADO</t>
   </si>
   <si>
-    <t xml:space="preserve">Metodologia: para cada item foram reunidos até três preços de contratações públicas (credenciamentos, pregões, atas de registro de preços, contratos e tabelas de credenciamento de órgãos e consórcios públicos), indicados nas colunas Fonte/Valor/Link de cada lote. O valor unitário de referência de cada item corresponde à MEDIANA dos preços coletados (Lei nº 14.133/2021, art. 23; IN SEGES/ME nº 65/2021, art. 6º), apresentada ao lado do menor preço, da média e do maior preço. Itens marcados como 'análogo' usam procedimento equivalente quando não havia o item idêntico na fonte. Itens com menos de três preços estão sujeitos à justificativa prevista no art. 6º, §5º, da IN SEGES/ME nº 65/2021. Os quantitativos são estimativas do TR e não geram obrigação de execução.</t>
+    <t xml:space="preserve">Metodologia: para cada item foram reunidos até três preços de contratações públicas (credenciamentos, pregões, atas de registro de preços, contratos e tabelas de credenciamento de órgãos e consórcios públicos), indicados nas colunas Fonte/Valor/Link de cada lote. O valor unitário de referência de cada item corresponde à MEDIANA dos preços coletados (Lei nº 14.133/2021, art. 23; IN SEGES/ME nº 65/2021, art. 6º), apresentada ao lado do menor preço, da média e do maior preço. Para os serviços com correspondente na Tabela de Serviços de Saúde executados em unidades móveis/itinerantes do ICISMEP (TSPS 2026), a mediana foi confrontada com o valor ICISMEP e limitada a 96% desse valor (redução mínima de 4%), como ajuste percentual para assegurar a vantajosidade da contratação. Itens marcados como 'análogo' usam procedimento equivalente quando não havia o item idêntico na fonte. Itens com menos de três preços estão sujeitos à justificativa prevista no art. 6º, §5º, da IN SEGES/ME nº 65/2021. Os quantitativos são estimativas do TR e não geram obrigação de execução.</t>
   </si>
   <si>
     <t xml:space="preserve">LOTE 1 – EXAMES DE MAMOGRAFIA BILATERAL (unidade móvel)</t>
@@ -118,7 +118,16 @@
     <t xml:space="preserve">Maior (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">Valor unit. referência (R$) = mediana</t>
+    <t xml:space="preserve">Valor ICISMEP – TSPS 2026, serviço em unidade móvel/itinerante (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Limite: ICISMEP − 4% (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor unit. referência (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diferença ref. x ICISMEP (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Valor total estimado (R$)</t>
@@ -302,6 +311,9 @@
   </si>
   <si>
     <t xml:space="preserve">https://pncp.gov.br/app/editais/05193057000178/2026/124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem correspondente</t>
   </si>
   <si>
     <t xml:space="preserve">DENSITOMETRIA ÓSSEA, em unidade móvel, com laudo</t>
@@ -758,10 +770,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.00"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -839,7 +852,6 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
-      <color rgb="FF0000FF"/>
       <name val="Cambria"/>
       <family val="0"/>
       <charset val="1"/>
@@ -914,7 +926,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -972,6 +984,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1277,7 +1293,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="n">
-        <f aca="false">'Lote 1 - Mamografia'!S4</f>
+        <f aca="false">'Lote 1 - Mamografia'!V4</f>
         <v>4615986</v>
       </c>
     </row>
@@ -1286,7 +1302,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="n">
-        <f aca="false">'Lote 2 - Consultas'!S18</f>
+        <f aca="false">'Lote 2 - Consultas'!V18</f>
         <v>22868454.05</v>
       </c>
     </row>
@@ -1295,8 +1311,8 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="n">
-        <f aca="false">'Lote 3 - Exames'!S12</f>
-        <v>20674426.8</v>
+        <f aca="false">'Lote 3 - Exames'!V12</f>
+        <v>17831513.1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1304,7 +1320,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="n">
-        <f aca="false">'Lote 4 - Ressonancia'!S5</f>
+        <f aca="false">'Lote 4 - Ressonancia'!V5</f>
         <v>11851030</v>
       </c>
     </row>
@@ -1313,7 +1329,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="n">
-        <f aca="false">'Lote 5 - Odontologia'!S67</f>
+        <f aca="false">'Lote 5 - Odontologia'!V67</f>
         <v>20579182.67</v>
       </c>
     </row>
@@ -1323,7 +1339,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="false">SUM(B6:B10)</f>
-        <v>80589079.52</v>
+        <v>77746165.82</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1378,7 +1394,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S4"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1395,8 +1411,11 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1421,6 +1440,9 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
@@ -1480,46 +1502,55 @@
       <c r="S2" s="9" t="s">
         <v>31</v>
       </c>
+      <c r="T2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>34600</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>80</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="I3" s="12" t="n">
         <v>133.41</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="L3" s="12" t="n">
         <v>140.45</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="N3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MIN(F3,I3,L3))</f>
@@ -1537,44 +1568,58 @@
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MAX(F3,I3,L3))</f>
         <v>140.45</v>
       </c>
-      <c r="R3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+      <c r="R3" s="12" t="n">
+        <v>140.45</v>
+      </c>
+      <c r="S3" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R3),ROUNDDOWN(R3*0.96,2),"—")</f>
+        <v>134.83</v>
+      </c>
+      <c r="T3" s="14" t="n">
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
         <v>133.41</v>
       </c>
-      <c r="S3" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+      <c r="U3" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R3),ISNUMBER(T3)),T3/R3-1,"—")</f>
+        <v>-0.050124599501602</v>
+      </c>
+      <c r="V3" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T3),D3*T3,0)</f>
         <v>4615986</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15"/>
+      <c r="A4" s="16"/>
       <c r="B4" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="15"/>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="15"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="15"/>
-      <c r="O4" s="15"/>
-      <c r="P4" s="15"/>
-      <c r="Q4" s="15"/>
-      <c r="R4" s="15"/>
-      <c r="S4" s="7" t="n">
-        <f aca="false">SUM(S3:S3)</f>
+        <v>43</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
+      <c r="V4" s="7" t="n">
+        <f aca="false">SUM(V3:V3)</f>
         <v>4615986</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="https://pncp.gov.br/pncp-api/v1/orgaos/71203715000190/compras/2026/1/arquivos/1"/>
@@ -1596,7 +1641,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S18"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -1613,13 +1658,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1639,6 +1687,9 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
@@ -1698,46 +1749,55 @@
       <c r="S2" s="9" t="s">
         <v>31</v>
       </c>
+      <c r="T2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>43440</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I3" s="12" t="n">
         <v>92.48</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L3" s="12" t="n">
         <v>100</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MIN(F3,I3,L3))</f>
@@ -1755,12 +1815,23 @@
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MAX(F3,I3,L3))</f>
         <v>100</v>
       </c>
-      <c r="R3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+      <c r="R3" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S3" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R3),ROUNDDOWN(R3*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T3" s="14" t="n">
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
         <v>92.48</v>
       </c>
-      <c r="S3" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+      <c r="U3" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R3),ISNUMBER(T3)),T3/R3-1,"—")</f>
+        <v>-0.63008</v>
+      </c>
+      <c r="V3" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T3),D3*T3,0)</f>
         <v>4017331.2</v>
       </c>
     </row>
@@ -1769,40 +1840,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>29865</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F4" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I4" s="12" t="n">
         <v>97.63</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L4" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MIN(F4,I4,L4))</f>
@@ -1820,12 +1891,23 @@
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MAX(F4,I4,L4))</f>
         <v>115</v>
       </c>
-      <c r="R4" s="14" t="n">
-        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
+      <c r="R4" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S4" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R4),ROUNDDOWN(R4*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T4" s="14" t="n">
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",IF(ISNUMBER(S4),MIN(ROUND(P4,2),S4),ROUND(P4,2)))</f>
         <v>97.63</v>
       </c>
-      <c r="S4" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R4),D4*R4,0)</f>
+      <c r="U4" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R4),ISNUMBER(T4)),T4/R4-1,"—")</f>
+        <v>-0.60948</v>
+      </c>
+      <c r="V4" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T4),D4*T4,0)</f>
         <v>2915719.95</v>
       </c>
     </row>
@@ -1834,40 +1916,40 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>24435</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>75</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="I5" s="12" t="n">
         <v>100</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L5" s="12" t="n">
         <v>125.24</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N5" s="12" t="n">
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MIN(F5,I5,L5))</f>
@@ -1885,12 +1967,23 @@
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MAX(F5,I5,L5))</f>
         <v>125.24</v>
       </c>
-      <c r="R5" s="14" t="n">
-        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
+      <c r="R5" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S5" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R5),ROUNDDOWN(R5*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T5" s="14" t="n">
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",IF(ISNUMBER(S5),MIN(ROUND(P5,2),S5),ROUND(P5,2)))</f>
         <v>100</v>
       </c>
-      <c r="S5" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R5),D5*R5,0)</f>
+      <c r="U5" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R5),ISNUMBER(T5)),T5/R5-1,"—")</f>
+        <v>-0.6</v>
+      </c>
+      <c r="V5" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T5),D5*T5,0)</f>
         <v>2443500</v>
       </c>
     </row>
@@ -1899,40 +1992,40 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>21720</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I6" s="12" t="n">
         <v>114.97</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L6" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MIN(F6,I6,L6))</f>
@@ -1950,12 +2043,23 @@
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MAX(F6,I6,L6))</f>
         <v>115</v>
       </c>
-      <c r="R6" s="14" t="n">
-        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
+      <c r="R6" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S6" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R6),ROUNDDOWN(R6*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T6" s="14" t="n">
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",IF(ISNUMBER(S6),MIN(ROUND(P6,2),S6),ROUND(P6,2)))</f>
         <v>114.97</v>
       </c>
-      <c r="S6" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R6),D6*R6,0)</f>
+      <c r="U6" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R6),ISNUMBER(T6)),T6/R6-1,"—")</f>
+        <v>-0.54012</v>
+      </c>
+      <c r="V6" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T6),D6*T6,0)</f>
         <v>2497148.4</v>
       </c>
     </row>
@@ -1964,40 +2068,40 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>21720</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>96.5</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L7" s="12" t="n">
         <v>161.67</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N7" s="12" t="n">
         <f aca="false">IF(COUNT(F7,I7,L7)=0,"",MIN(F7,I7,L7))</f>
@@ -2015,12 +2119,23 @@
         <f aca="false">IF(COUNT(F7,I7,L7)=0,"",MAX(F7,I7,L7))</f>
         <v>161.67</v>
       </c>
-      <c r="R7" s="14" t="n">
-        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
+      <c r="R7" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S7" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R7),ROUNDDOWN(R7*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T7" s="14" t="n">
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",IF(ISNUMBER(S7),MIN(ROUND(P7,2),S7),ROUND(P7,2)))</f>
         <v>96.5</v>
       </c>
-      <c r="S7" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R7),D7*R7,0)</f>
+      <c r="U7" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R7),ISNUMBER(T7)),T7/R7-1,"—")</f>
+        <v>-0.614</v>
+      </c>
+      <c r="V7" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T7),D7*T7,0)</f>
         <v>2095980</v>
       </c>
     </row>
@@ -2029,40 +2144,40 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>14480</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I8" s="12" t="n">
         <v>103.2</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N8" s="12" t="n">
         <f aca="false">IF(COUNT(F8,I8,L8)=0,"",MIN(F8,I8,L8))</f>
@@ -2080,12 +2195,23 @@
         <f aca="false">IF(COUNT(F8,I8,L8)=0,"",MAX(F8,I8,L8))</f>
         <v>115</v>
       </c>
-      <c r="R8" s="14" t="n">
-        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
+      <c r="R8" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S8" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R8),ROUNDDOWN(R8*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T8" s="14" t="n">
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",IF(ISNUMBER(S8),MIN(ROUND(P8,2),S8),ROUND(P8,2)))</f>
         <v>103.2</v>
       </c>
-      <c r="S8" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R8),D8*R8,0)</f>
+      <c r="U8" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R8),ISNUMBER(T8)),T8/R8-1,"—")</f>
+        <v>-0.5872</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T8),D8*T8,0)</f>
         <v>1494336</v>
       </c>
     </row>
@@ -2094,40 +2220,40 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>13575</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>101.56</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N9" s="12" t="n">
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MIN(F9,I9,L9))</f>
@@ -2145,12 +2271,23 @@
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MAX(F9,I9,L9))</f>
         <v>115</v>
       </c>
-      <c r="R9" s="14" t="n">
-        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
+      <c r="R9" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S9" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R9),ROUNDDOWN(R9*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T9" s="14" t="n">
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",IF(ISNUMBER(S9),MIN(ROUND(P9,2),S9),ROUND(P9,2)))</f>
         <v>101.56</v>
       </c>
-      <c r="S9" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R9),D9*R9,0)</f>
+      <c r="U9" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R9),ISNUMBER(T9)),T9/R9-1,"—")</f>
+        <v>-0.59376</v>
+      </c>
+      <c r="V9" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T9),D9*T9,0)</f>
         <v>1378677</v>
       </c>
     </row>
@@ -2159,40 +2296,40 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>12670</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I10" s="12" t="n">
         <v>116.67</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N10" s="12" t="n">
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MIN(F10,I10,L10))</f>
@@ -2210,12 +2347,23 @@
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MAX(F10,I10,L10))</f>
         <v>116.67</v>
       </c>
-      <c r="R10" s="14" t="n">
-        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
+      <c r="R10" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S10" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R10),ROUNDDOWN(R10*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T10" s="14" t="n">
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",IF(ISNUMBER(S10),MIN(ROUND(P10,2),S10),ROUND(P10,2)))</f>
         <v>115</v>
       </c>
-      <c r="S10" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R10),D10*R10,0)</f>
+      <c r="U10" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R10),ISNUMBER(T10)),T10/R10-1,"—")</f>
+        <v>-0.54</v>
+      </c>
+      <c r="V10" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T10),D10*T10,0)</f>
         <v>1457050</v>
       </c>
     </row>
@@ -2224,40 +2372,40 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>11765</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>90</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MIN(F11,I11,L11))</f>
@@ -2275,12 +2423,23 @@
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MAX(F11,I11,L11))</f>
         <v>115</v>
       </c>
-      <c r="R11" s="14" t="n">
-        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
+      <c r="R11" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S11" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R11),ROUNDDOWN(R11*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T11" s="14" t="n">
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",IF(ISNUMBER(S11),MIN(ROUND(P11,2),S11),ROUND(P11,2)))</f>
         <v>90</v>
       </c>
-      <c r="S11" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R11),D11*R11,0)</f>
+      <c r="U11" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R11),ISNUMBER(T11)),T11/R11-1,"—")</f>
+        <v>-0.64</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T11),D11*T11,0)</f>
         <v>1058850</v>
       </c>
     </row>
@@ -2289,40 +2448,40 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>10860</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>105.87</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">IF(COUNT(F12,I12,L12)=0,"",MIN(F12,I12,L12))</f>
@@ -2340,12 +2499,23 @@
         <f aca="false">IF(COUNT(F12,I12,L12)=0,"",MAX(F12,I12,L12))</f>
         <v>115</v>
       </c>
-      <c r="R12" s="14" t="n">
-        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",ROUND(P12,2))</f>
+      <c r="R12" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S12" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R12),ROUNDDOWN(R12*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T12" s="14" t="n">
+        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",IF(ISNUMBER(S12),MIN(ROUND(P12,2),S12),ROUND(P12,2)))</f>
         <v>105.87</v>
       </c>
-      <c r="S12" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R12),D12*R12,0)</f>
+      <c r="U12" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R12),ISNUMBER(T12)),T12/R12-1,"—")</f>
+        <v>-0.57652</v>
+      </c>
+      <c r="V12" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T12),D12*T12,0)</f>
         <v>1149748.2</v>
       </c>
     </row>
@@ -2354,40 +2524,40 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>9955</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>106.1</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N13" s="12" t="n">
         <f aca="false">IF(COUNT(F13,I13,L13)=0,"",MIN(F13,I13,L13))</f>
@@ -2405,12 +2575,23 @@
         <f aca="false">IF(COUNT(F13,I13,L13)=0,"",MAX(F13,I13,L13))</f>
         <v>115</v>
       </c>
-      <c r="R13" s="14" t="n">
-        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",ROUND(P13,2))</f>
+      <c r="R13" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S13" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R13),ROUNDDOWN(R13*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T13" s="14" t="n">
+        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",IF(ISNUMBER(S13),MIN(ROUND(P13,2),S13),ROUND(P13,2)))</f>
         <v>106.1</v>
       </c>
-      <c r="S13" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R13),D13*R13,0)</f>
+      <c r="U13" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R13),ISNUMBER(T13)),T13/R13-1,"—")</f>
+        <v>-0.5756</v>
+      </c>
+      <c r="V13" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T13),D13*T13,0)</f>
         <v>1056225.5</v>
       </c>
     </row>
@@ -2419,40 +2600,40 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>3620</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>97.63</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N14" s="12" t="n">
         <f aca="false">IF(COUNT(F14,I14,L14)=0,"",MIN(F14,I14,L14))</f>
@@ -2470,12 +2651,23 @@
         <f aca="false">IF(COUNT(F14,I14,L14)=0,"",MAX(F14,I14,L14))</f>
         <v>115</v>
       </c>
-      <c r="R14" s="14" t="n">
-        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",ROUND(P14,2))</f>
+      <c r="R14" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S14" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R14),ROUNDDOWN(R14*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T14" s="14" t="n">
+        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",IF(ISNUMBER(S14),MIN(ROUND(P14,2),S14),ROUND(P14,2)))</f>
         <v>97.63</v>
       </c>
-      <c r="S14" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R14),D14*R14,0)</f>
+      <c r="U14" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R14),ISNUMBER(T14)),T14/R14-1,"—")</f>
+        <v>-0.60948</v>
+      </c>
+      <c r="V14" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T14),D14*T14,0)</f>
         <v>353420.6</v>
       </c>
     </row>
@@ -2484,40 +2676,40 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>2715</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>90</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M15" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N15" s="12" t="n">
         <f aca="false">IF(COUNT(F15,I15,L15)=0,"",MIN(F15,I15,L15))</f>
@@ -2535,12 +2727,23 @@
         <f aca="false">IF(COUNT(F15,I15,L15)=0,"",MAX(F15,I15,L15))</f>
         <v>115</v>
       </c>
-      <c r="R15" s="14" t="n">
-        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",ROUND(P15,2))</f>
+      <c r="R15" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S15" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R15),ROUNDDOWN(R15*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T15" s="14" t="n">
+        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",IF(ISNUMBER(S15),MIN(ROUND(P15,2),S15),ROUND(P15,2)))</f>
         <v>90</v>
       </c>
-      <c r="S15" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R15),D15*R15,0)</f>
+      <c r="U15" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R15),ISNUMBER(T15)),T15/R15-1,"—")</f>
+        <v>-0.64</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T15),D15*T15,0)</f>
         <v>244350</v>
       </c>
     </row>
@@ -2549,40 +2752,40 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>5430</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I16" s="12" t="n">
         <v>91.96</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K16" s="10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>115</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N16" s="12" t="n">
         <f aca="false">IF(COUNT(F16,I16,L16)=0,"",MIN(F16,I16,L16))</f>
@@ -2600,12 +2803,23 @@
         <f aca="false">IF(COUNT(F16,I16,L16)=0,"",MAX(F16,I16,L16))</f>
         <v>115</v>
       </c>
-      <c r="R16" s="14" t="n">
-        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",ROUND(P16,2))</f>
+      <c r="R16" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S16" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R16),ROUNDDOWN(R16*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T16" s="14" t="n">
+        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",IF(ISNUMBER(S16),MIN(ROUND(P16,2),S16),ROUND(P16,2)))</f>
         <v>91.96</v>
       </c>
-      <c r="S16" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R16),D16*R16,0)</f>
+      <c r="U16" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R16),ISNUMBER(T16)),T16/R16-1,"—")</f>
+        <v>-0.63216</v>
+      </c>
+      <c r="V16" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T16),D16*T16,0)</f>
         <v>499342.8</v>
       </c>
     </row>
@@ -2614,40 +2828,40 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>2172</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>95.2</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K17" s="10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>161.67</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N17" s="12" t="n">
         <f aca="false">IF(COUNT(F17,I17,L17)=0,"",MIN(F17,I17,L17))</f>
@@ -2665,44 +2879,58 @@
         <f aca="false">IF(COUNT(F17,I17,L17)=0,"",MAX(F17,I17,L17))</f>
         <v>161.67</v>
       </c>
-      <c r="R17" s="14" t="n">
-        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",ROUND(P17,2))</f>
+      <c r="R17" s="12" t="n">
+        <v>250</v>
+      </c>
+      <c r="S17" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(R17),ROUNDDOWN(R17*0.96,2),"—")</f>
+        <v>240</v>
+      </c>
+      <c r="T17" s="14" t="n">
+        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",IF(ISNUMBER(S17),MIN(ROUND(P17,2),S17),ROUND(P17,2)))</f>
         <v>95.2</v>
       </c>
-      <c r="S17" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R17),D17*R17,0)</f>
+      <c r="U17" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R17),ISNUMBER(T17)),T17/R17-1,"—")</f>
+        <v>-0.6192</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T17),D17*T17,0)</f>
         <v>206774.4</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15"/>
+      <c r="A18" s="16"/>
       <c r="B18" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="15"/>
-      <c r="R18" s="15"/>
-      <c r="S18" s="7" t="n">
-        <f aca="false">SUM(S3:S17)</f>
+        <v>43</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="16"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16"/>
+      <c r="P18" s="16"/>
+      <c r="Q18" s="16"/>
+      <c r="R18" s="16"/>
+      <c r="S18" s="16"/>
+      <c r="T18" s="16"/>
+      <c r="U18" s="16"/>
+      <c r="V18" s="7" t="n">
+        <f aca="false">SUM(V3:V17)</f>
         <v>22868454.05</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="https://saude.es.gov.br/Media/sesa/Credenciamento/EDITAL%20SESA-SRSV-NRA%20001-26.pdf"/>
@@ -2766,7 +2994,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:V12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -2783,13 +3011,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2809,6 +3040,9 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
@@ -2868,46 +3102,55 @@
       <c r="S2" s="9" t="s">
         <v>31</v>
       </c>
+      <c r="T2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>65600</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>115.05</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I3" s="12" t="n">
         <v>136.91</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L3" s="12" t="n">
         <v>83.54</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MIN(F3,I3,L3))</f>
@@ -2925,13 +3168,24 @@
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MAX(F3,I3,L3))</f>
         <v>136.91</v>
       </c>
-      <c r="R3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
-        <v>115.05</v>
+      <c r="R3" s="12" t="n">
+        <v>87.92</v>
       </c>
       <c r="S3" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
-        <v>7547280</v>
+        <f aca="false">IF(ISNUMBER(R3),ROUNDDOWN(R3*0.96,2),"—")</f>
+        <v>84.4</v>
+      </c>
+      <c r="T3" s="14" t="n">
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
+        <v>84.4</v>
+      </c>
+      <c r="U3" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R3),ISNUMBER(T3)),T3/R3-1,"—")</f>
+        <v>-0.0400363967242948</v>
+      </c>
+      <c r="V3" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T3),D3*T3,0)</f>
+        <v>5536640</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2939,40 +3193,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>10460</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F4" s="12" t="n">
         <v>90</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I4" s="12" t="n">
         <v>87.9</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L4" s="12" t="n">
         <v>150</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MIN(F4,I4,L4))</f>
@@ -2990,13 +3244,24 @@
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MAX(F4,I4,L4))</f>
         <v>150</v>
       </c>
-      <c r="R4" s="14" t="n">
-        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
-        <v>90</v>
+      <c r="R4" s="12" t="n">
+        <v>87.92</v>
       </c>
       <c r="S4" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R4),D4*R4,0)</f>
-        <v>941400</v>
+        <f aca="false">IF(ISNUMBER(R4),ROUNDDOWN(R4*0.96,2),"—")</f>
+        <v>84.4</v>
+      </c>
+      <c r="T4" s="14" t="n">
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",IF(ISNUMBER(S4),MIN(ROUND(P4,2),S4),ROUND(P4,2)))</f>
+        <v>84.4</v>
+      </c>
+      <c r="U4" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R4),ISNUMBER(T4)),T4/R4-1,"—")</f>
+        <v>-0.0400363967242948</v>
+      </c>
+      <c r="V4" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T4),D4*T4,0)</f>
+        <v>882824</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3004,40 +3269,40 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>21325</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>62.79</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="I5" s="12" t="n">
         <v>89.72</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="L5" s="12" t="n">
         <v>135</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N5" s="12" t="n">
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MIN(F5,I5,L5))</f>
@@ -3055,13 +3320,24 @@
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MAX(F5,I5,L5))</f>
         <v>135</v>
       </c>
-      <c r="R5" s="14" t="n">
-        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
-        <v>89.72</v>
+      <c r="R5" s="12" t="n">
+        <v>87.92</v>
       </c>
       <c r="S5" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R5),D5*R5,0)</f>
-        <v>1913279</v>
+        <f aca="false">IF(ISNUMBER(R5),ROUNDDOWN(R5*0.96,2),"—")</f>
+        <v>84.4</v>
+      </c>
+      <c r="T5" s="14" t="n">
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",IF(ISNUMBER(S5),MIN(ROUND(P5,2),S5),ROUND(P5,2)))</f>
+        <v>84.4</v>
+      </c>
+      <c r="U5" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R5),ISNUMBER(T5)),T5/R5-1,"—")</f>
+        <v>-0.0400363967242948</v>
+      </c>
+      <c r="V5" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T5),D5*T5,0)</f>
+        <v>1799830</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3069,40 +3345,40 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>10460</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>90</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I6" s="12" t="n">
         <v>85.72</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L6" s="12" t="n">
         <v>71.28</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MIN(F6,I6,L6))</f>
@@ -3120,13 +3396,24 @@
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MAX(F6,I6,L6))</f>
         <v>90</v>
       </c>
-      <c r="R6" s="14" t="n">
-        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
-        <v>85.72</v>
+      <c r="R6" s="12" t="n">
+        <v>87.92</v>
       </c>
       <c r="S6" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R6),D6*R6,0)</f>
-        <v>896631.2</v>
+        <f aca="false">IF(ISNUMBER(R6),ROUNDDOWN(R6*0.96,2),"—")</f>
+        <v>84.4</v>
+      </c>
+      <c r="T6" s="14" t="n">
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",IF(ISNUMBER(S6),MIN(ROUND(P6,2),S6),ROUND(P6,2)))</f>
+        <v>84.4</v>
+      </c>
+      <c r="U6" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R6),ISNUMBER(T6)),T6/R6-1,"—")</f>
+        <v>-0.0400363967242948</v>
+      </c>
+      <c r="V6" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T6),D6*T6,0)</f>
+        <v>882824</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3134,40 +3421,40 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>14885</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>211.26</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>244.92</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="L7" s="12" t="n">
         <v>190.45</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="N7" s="12" t="n">
         <f aca="false">IF(COUNT(F7,I7,L7)=0,"",MIN(F7,I7,L7))</f>
@@ -3185,12 +3472,23 @@
         <f aca="false">IF(COUNT(F7,I7,L7)=0,"",MAX(F7,I7,L7))</f>
         <v>244.92</v>
       </c>
-      <c r="R7" s="14" t="n">
-        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
+      <c r="R7" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S7" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R7),ROUNDDOWN(R7*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T7" s="14" t="n">
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",IF(ISNUMBER(S7),MIN(ROUND(P7,2),S7),ROUND(P7,2)))</f>
         <v>211.26</v>
       </c>
-      <c r="S7" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R7),D7*R7,0)</f>
+      <c r="U7" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R7),ISNUMBER(T7)),T7/R7-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V7" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T7),D7*T7,0)</f>
         <v>3144605.1</v>
       </c>
     </row>
@@ -3199,40 +3497,40 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>3174</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>187.17</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I8" s="12" t="n">
         <v>64.37</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>75</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="N8" s="12" t="n">
         <f aca="false">IF(COUNT(F8,I8,L8)=0,"",MIN(F8,I8,L8))</f>
@@ -3250,12 +3548,23 @@
         <f aca="false">IF(COUNT(F8,I8,L8)=0,"",MAX(F8,I8,L8))</f>
         <v>187.17</v>
       </c>
-      <c r="R8" s="14" t="n">
-        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
+      <c r="R8" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S8" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R8),ROUNDDOWN(R8*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T8" s="14" t="n">
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",IF(ISNUMBER(S8),MIN(ROUND(P8,2),S8),ROUND(P8,2)))</f>
         <v>75</v>
       </c>
-      <c r="S8" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R8),D8*R8,0)</f>
+      <c r="U8" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R8),ISNUMBER(T8)),T8/R8-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T8),D8*T8,0)</f>
         <v>238050</v>
       </c>
     </row>
@@ -3264,40 +3573,40 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>4525</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>90</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>90.74</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>44.28</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N9" s="12" t="n">
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MIN(F9,I9,L9))</f>
@@ -3315,13 +3624,24 @@
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MAX(F9,I9,L9))</f>
         <v>90.74</v>
       </c>
-      <c r="R9" s="14" t="n">
-        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
-        <v>90</v>
+      <c r="R9" s="12" t="n">
+        <v>87.92</v>
       </c>
       <c r="S9" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R9),D9*R9,0)</f>
-        <v>407250</v>
+        <f aca="false">IF(ISNUMBER(R9),ROUNDDOWN(R9*0.96,2),"—")</f>
+        <v>84.4</v>
+      </c>
+      <c r="T9" s="14" t="n">
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",IF(ISNUMBER(S9),MIN(ROUND(P9,2),S9),ROUND(P9,2)))</f>
+        <v>84.4</v>
+      </c>
+      <c r="U9" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R9),ISNUMBER(T9)),T9/R9-1,"—")</f>
+        <v>-0.0400363967242948</v>
+      </c>
+      <c r="V9" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T9),D9*T9,0)</f>
+        <v>381910</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3329,40 +3649,40 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>4525</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>100.74</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="I10" s="12" t="n">
         <v>90.74</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>44.28</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="N10" s="12" t="n">
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MIN(F10,I10,L10))</f>
@@ -3380,13 +3700,24 @@
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MAX(F10,I10,L10))</f>
         <v>100.74</v>
       </c>
-      <c r="R10" s="14" t="n">
-        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
-        <v>90.74</v>
+      <c r="R10" s="12" t="n">
+        <v>87.92</v>
       </c>
       <c r="S10" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R10),D10*R10,0)</f>
-        <v>410598.5</v>
+        <f aca="false">IF(ISNUMBER(R10),ROUNDDOWN(R10*0.96,2),"—")</f>
+        <v>84.4</v>
+      </c>
+      <c r="T10" s="14" t="n">
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",IF(ISNUMBER(S10),MIN(ROUND(P10,2),S10),ROUND(P10,2)))</f>
+        <v>84.4</v>
+      </c>
+      <c r="U10" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R10),ISNUMBER(T10)),T10/R10-1,"—")</f>
+        <v>-0.0400363967242948</v>
+      </c>
+      <c r="V10" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T10),D10*T10,0)</f>
+        <v>381910</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3394,40 +3725,40 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>54300</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>95.31</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>86.98</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>155</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MIN(F11,I11,L11))</f>
@@ -3445,44 +3776,58 @@
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MAX(F11,I11,L11))</f>
         <v>155</v>
       </c>
-      <c r="R11" s="14" t="n">
-        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
-        <v>95.31</v>
+      <c r="R11" s="12" t="n">
+        <v>87.92</v>
       </c>
       <c r="S11" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R11),D11*R11,0)</f>
-        <v>5175333</v>
+        <f aca="false">IF(ISNUMBER(R11),ROUNDDOWN(R11*0.96,2),"—")</f>
+        <v>84.4</v>
+      </c>
+      <c r="T11" s="14" t="n">
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",IF(ISNUMBER(S11),MIN(ROUND(P11,2),S11),ROUND(P11,2)))</f>
+        <v>84.4</v>
+      </c>
+      <c r="U11" s="15" t="n">
+        <f aca="false">IF(AND(ISNUMBER(R11),ISNUMBER(T11)),T11/R11-1,"—")</f>
+        <v>-0.0400363967242948</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T11),D11*T11,0)</f>
+        <v>4582920</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="15"/>
-      <c r="R12" s="15"/>
-      <c r="S12" s="7" t="n">
-        <f aca="false">SUM(S3:S11)</f>
-        <v>20674426.8</v>
+        <v>43</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="16"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="16"/>
+      <c r="N12" s="16"/>
+      <c r="O12" s="16"/>
+      <c r="P12" s="16"/>
+      <c r="Q12" s="16"/>
+      <c r="R12" s="16"/>
+      <c r="S12" s="16"/>
+      <c r="T12" s="16"/>
+      <c r="U12" s="16"/>
+      <c r="V12" s="7" t="n">
+        <f aca="false">SUM(V3:V11)</f>
+        <v>17831513.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="https://www.sarapui.sp.gov.br/ata-registro-preco/page/1/download/839"/>
@@ -3528,7 +3873,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S5"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -3545,13 +3890,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3571,6 +3919,9 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
@@ -3630,46 +3981,55 @@
       <c r="S2" s="9" t="s">
         <v>31</v>
       </c>
+      <c r="T2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>27150</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>420</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="I3" s="12" t="n">
         <v>400</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="L3" s="12" t="n">
         <v>543.33</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MIN(F3,I3,L3))</f>
@@ -3687,12 +4047,23 @@
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MAX(F3,I3,L3))</f>
         <v>543.33</v>
       </c>
-      <c r="R3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+      <c r="R3" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S3" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R3),ROUNDDOWN(R3*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T3" s="14" t="n">
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
         <v>420</v>
       </c>
-      <c r="S3" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+      <c r="U3" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R3),ISNUMBER(T3)),T3/R3-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V3" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T3),D3*T3,0)</f>
         <v>11403000</v>
       </c>
     </row>
@@ -3701,40 +4072,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>4073</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="F4" s="12" t="n">
         <v>77</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="I4" s="12" t="n">
         <v>300</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="L4" s="12" t="n">
         <v>110</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="N4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MIN(F4,I4,L4))</f>
@@ -3752,44 +4123,58 @@
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MAX(F4,I4,L4))</f>
         <v>300</v>
       </c>
-      <c r="R4" s="14" t="n">
-        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
+      <c r="R4" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S4" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R4),ROUNDDOWN(R4*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T4" s="14" t="n">
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",IF(ISNUMBER(S4),MIN(ROUND(P4,2),S4),ROUND(P4,2)))</f>
         <v>110</v>
       </c>
-      <c r="S4" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R4),D4*R4,0)</f>
+      <c r="U4" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R4),ISNUMBER(T4)),T4/R4-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V4" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T4),D4*T4,0)</f>
         <v>448030</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="15"/>
-      <c r="O5" s="15"/>
-      <c r="P5" s="15"/>
-      <c r="Q5" s="15"/>
-      <c r="R5" s="15"/>
-      <c r="S5" s="7" t="n">
-        <f aca="false">SUM(S3:S4)</f>
+        <v>43</v>
+      </c>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
+      <c r="V5" s="7" t="n">
+        <f aca="false">SUM(V3:V4)</f>
         <v>11851030</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="https://pncp.gov.br/pncp-api/v1/orgaos/71203715000190/compras/2026/1/arquivos/1"/>
@@ -3814,7 +4199,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:S67"/>
+  <dimension ref="A1:V67"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -3831,13 +4216,16 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3857,6 +4245,9 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
       <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="9" t="s">
@@ -3916,46 +4307,55 @@
       <c r="S2" s="9" t="s">
         <v>31</v>
       </c>
+      <c r="T2" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="U2" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="V2" s="9" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="n">
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C3" s="10" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D3" s="11" t="n">
         <v>90118</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>66.5</v>
       </c>
       <c r="G3" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I3" s="12" t="n">
         <v>90.1</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L3" s="12" t="n">
         <v>78.4</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MIN(F3,I3,L3))</f>
@@ -3973,12 +4373,23 @@
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MAX(F3,I3,L3))</f>
         <v>90.1</v>
       </c>
-      <c r="R3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+      <c r="R3" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S3" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R3),ROUNDDOWN(R3*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T3" s="14" t="n">
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
         <v>78.4</v>
       </c>
-      <c r="S3" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R3),D3*R3,0)</f>
+      <c r="U3" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R3),ISNUMBER(T3)),T3/R3-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V3" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T3),D3*T3,0)</f>
         <v>7065251.2</v>
       </c>
     </row>
@@ -3987,40 +4398,40 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F4" s="12" t="n">
         <v>53.8</v>
       </c>
       <c r="G4" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I4" s="12" t="n">
         <v>76.05</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L4" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MIN(F4,I4,L4))</f>
@@ -4038,12 +4449,23 @@
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MAX(F4,I4,L4))</f>
         <v>76.05</v>
       </c>
-      <c r="R4" s="14" t="n">
-        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
+      <c r="R4" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S4" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R4),ROUNDDOWN(R4*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T4" s="14" t="n">
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",IF(ISNUMBER(S4),MIN(ROUND(P4,2),S4),ROUND(P4,2)))</f>
         <v>53.8</v>
       </c>
-      <c r="S4" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R4),D4*R4,0)</f>
+      <c r="U4" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R4),ISNUMBER(T4)),T4/R4-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V4" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T4),D4*T4,0)</f>
         <v>48689</v>
       </c>
     </row>
@@ -4052,40 +4474,40 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>53.8</v>
       </c>
       <c r="G5" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I5" s="12" t="n">
         <v>76.05</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="L5" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N5" s="12" t="n">
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MIN(F5,I5,L5))</f>
@@ -4103,12 +4525,23 @@
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MAX(F5,I5,L5))</f>
         <v>76.05</v>
       </c>
-      <c r="R5" s="14" t="n">
-        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
+      <c r="R5" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S5" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R5),ROUNDDOWN(R5*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T5" s="14" t="n">
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",IF(ISNUMBER(S5),MIN(ROUND(P5,2),S5),ROUND(P5,2)))</f>
         <v>53.8</v>
       </c>
-      <c r="S5" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R5),D5*R5,0)</f>
+      <c r="U5" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R5),ISNUMBER(T5)),T5/R5-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V5" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T5),D5*T5,0)</f>
         <v>48689</v>
       </c>
     </row>
@@ -4117,40 +4550,40 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>69.5</v>
       </c>
       <c r="G6" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I6" s="12" t="n">
         <v>98.27</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L6" s="12" t="n">
         <v>83.97</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MIN(F6,I6,L6))</f>
@@ -4168,12 +4601,23 @@
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MAX(F6,I6,L6))</f>
         <v>98.27</v>
       </c>
-      <c r="R6" s="14" t="n">
-        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
+      <c r="R6" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S6" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R6),ROUNDDOWN(R6*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T6" s="14" t="n">
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",IF(ISNUMBER(S6),MIN(ROUND(P6,2),S6),ROUND(P6,2)))</f>
         <v>83.97</v>
       </c>
-      <c r="S6" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R6),D6*R6,0)</f>
+      <c r="U6" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R6),ISNUMBER(T6)),T6/R6-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V6" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T6),D6*T6,0)</f>
         <v>75992.85</v>
       </c>
     </row>
@@ -4182,34 +4626,34 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>1376</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>82.2</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>116.21</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="10"/>
@@ -4229,12 +4673,23 @@
         <f aca="false">IF(COUNT(F7,I7,L7)=0,"",MAX(F7,I7,L7))</f>
         <v>116.21</v>
       </c>
-      <c r="R7" s="14" t="n">
-        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
+      <c r="R7" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S7" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R7),ROUNDDOWN(R7*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T7" s="14" t="n">
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",IF(ISNUMBER(S7),MIN(ROUND(P7,2),S7),ROUND(P7,2)))</f>
         <v>99.21</v>
       </c>
-      <c r="S7" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R7),D7*R7,0)</f>
+      <c r="U7" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R7),ISNUMBER(T7)),T7/R7-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V7" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T7),D7*T7,0)</f>
         <v>136512.96</v>
       </c>
     </row>
@@ -4243,40 +4698,40 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>1282</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>80.7</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I8" s="12" t="n">
         <v>109.36</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>43.9</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N8" s="12" t="n">
         <f aca="false">IF(COUNT(F8,I8,L8)=0,"",MIN(F8,I8,L8))</f>
@@ -4294,12 +4749,23 @@
         <f aca="false">IF(COUNT(F8,I8,L8)=0,"",MAX(F8,I8,L8))</f>
         <v>109.36</v>
       </c>
-      <c r="R8" s="14" t="n">
-        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
+      <c r="R8" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S8" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R8),ROUNDDOWN(R8*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T8" s="14" t="n">
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",IF(ISNUMBER(S8),MIN(ROUND(P8,2),S8),ROUND(P8,2)))</f>
         <v>80.7</v>
       </c>
-      <c r="S8" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R8),D8*R8,0)</f>
+      <c r="U8" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R8),ISNUMBER(T8)),T8/R8-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V8" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T8),D8*T8,0)</f>
         <v>103457.4</v>
       </c>
     </row>
@@ -4308,40 +4774,40 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>14903</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>66.5</v>
       </c>
       <c r="G9" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>90.1</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>54.44</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N9" s="12" t="n">
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MIN(F9,I9,L9))</f>
@@ -4359,12 +4825,23 @@
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MAX(F9,I9,L9))</f>
         <v>90.1</v>
       </c>
-      <c r="R9" s="14" t="n">
-        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
+      <c r="R9" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S9" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R9),ROUNDDOWN(R9*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T9" s="14" t="n">
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",IF(ISNUMBER(S9),MIN(ROUND(P9,2),S9),ROUND(P9,2)))</f>
         <v>66.5</v>
       </c>
-      <c r="S9" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R9),D9*R9,0)</f>
+      <c r="U9" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R9),ISNUMBER(T9)),T9/R9-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V9" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T9),D9*T9,0)</f>
         <v>991049.5</v>
       </c>
     </row>
@@ -4373,40 +4850,40 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>4471</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>69.5</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I10" s="12" t="n">
         <v>90</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>82.42</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="N10" s="12" t="n">
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MIN(F10,I10,L10))</f>
@@ -4424,12 +4901,23 @@
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MAX(F10,I10,L10))</f>
         <v>90</v>
       </c>
-      <c r="R10" s="14" t="n">
-        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
+      <c r="R10" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S10" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R10),ROUNDDOWN(R10*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T10" s="14" t="n">
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",IF(ISNUMBER(S10),MIN(ROUND(P10,2),S10),ROUND(P10,2)))</f>
         <v>82.42</v>
       </c>
-      <c r="S10" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R10),D10*R10,0)</f>
+      <c r="U10" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R10),ISNUMBER(T10)),T10/R10-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V10" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T10),D10*T10,0)</f>
         <v>368499.82</v>
       </c>
     </row>
@@ -4438,40 +4926,40 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>53.8</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>72.91</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>73</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MIN(F11,I11,L11))</f>
@@ -4489,12 +4977,23 @@
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MAX(F11,I11,L11))</f>
         <v>73</v>
       </c>
-      <c r="R11" s="14" t="n">
-        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
+      <c r="R11" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S11" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R11),ROUNDDOWN(R11*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T11" s="14" t="n">
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",IF(ISNUMBER(S11),MIN(ROUND(P11,2),S11),ROUND(P11,2)))</f>
         <v>72.91</v>
       </c>
-      <c r="S11" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R11),D11*R11,0)</f>
+      <c r="U11" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R11),ISNUMBER(T11)),T11/R11-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V11" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T11),D11*T11,0)</f>
         <v>65983.55</v>
       </c>
     </row>
@@ -4503,40 +5002,40 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>71</v>
       </c>
       <c r="G12" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>96.28</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>48</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">IF(COUNT(F12,I12,L12)=0,"",MIN(F12,I12,L12))</f>
@@ -4554,12 +5053,23 @@
         <f aca="false">IF(COUNT(F12,I12,L12)=0,"",MAX(F12,I12,L12))</f>
         <v>96.28</v>
       </c>
-      <c r="R12" s="14" t="n">
-        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",ROUND(P12,2))</f>
+      <c r="R12" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S12" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R12),ROUNDDOWN(R12*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T12" s="14" t="n">
+        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",IF(ISNUMBER(S12),MIN(ROUND(P12,2),S12),ROUND(P12,2)))</f>
         <v>71</v>
       </c>
-      <c r="S12" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R12),D12*R12,0)</f>
+      <c r="U12" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R12),ISNUMBER(T12)),T12/R12-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V12" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T12),D12*T12,0)</f>
         <v>64255</v>
       </c>
     </row>
@@ -4568,40 +5078,40 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>101.25</v>
       </c>
       <c r="G13" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>104.5</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>167</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N13" s="12" t="n">
         <f aca="false">IF(COUNT(F13,I13,L13)=0,"",MIN(F13,I13,L13))</f>
@@ -4619,12 +5129,23 @@
         <f aca="false">IF(COUNT(F13,I13,L13)=0,"",MAX(F13,I13,L13))</f>
         <v>167</v>
       </c>
-      <c r="R13" s="14" t="n">
-        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",ROUND(P13,2))</f>
+      <c r="R13" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S13" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R13),ROUNDDOWN(R13*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T13" s="14" t="n">
+        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",IF(ISNUMBER(S13),MIN(ROUND(P13,2),S13),ROUND(P13,2)))</f>
         <v>104.5</v>
       </c>
-      <c r="S13" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R13),D13*R13,0)</f>
+      <c r="U13" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R13),ISNUMBER(T13)),T13/R13-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V13" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T13),D13*T13,0)</f>
         <v>94572.5</v>
       </c>
     </row>
@@ -4633,40 +5154,40 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>5083</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>108.75</v>
       </c>
       <c r="G14" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>166</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>61</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N14" s="12" t="n">
         <f aca="false">IF(COUNT(F14,I14,L14)=0,"",MIN(F14,I14,L14))</f>
@@ -4684,12 +5205,23 @@
         <f aca="false">IF(COUNT(F14,I14,L14)=0,"",MAX(F14,I14,L14))</f>
         <v>166</v>
       </c>
-      <c r="R14" s="14" t="n">
-        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",ROUND(P14,2))</f>
+      <c r="R14" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S14" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R14),ROUNDDOWN(R14*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T14" s="14" t="n">
+        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",IF(ISNUMBER(S14),MIN(ROUND(P14,2),S14),ROUND(P14,2)))</f>
         <v>108.75</v>
       </c>
-      <c r="S14" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R14),D14*R14,0)</f>
+      <c r="U14" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R14),ISNUMBER(T14)),T14/R14-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V14" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T14),D14*T14,0)</f>
         <v>552776.25</v>
       </c>
     </row>
@@ -4698,30 +5230,30 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>66.5</v>
       </c>
       <c r="G15" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L15" s="12"/>
       <c r="M15" s="10"/>
@@ -4741,12 +5273,23 @@
         <f aca="false">IF(COUNT(F15,I15,L15)=0,"",MAX(F15,I15,L15))</f>
         <v>66.5</v>
       </c>
-      <c r="R15" s="14" t="n">
-        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",ROUND(P15,2))</f>
+      <c r="R15" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S15" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R15),ROUNDDOWN(R15*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T15" s="14" t="n">
+        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",IF(ISNUMBER(S15),MIN(ROUND(P15,2),S15),ROUND(P15,2)))</f>
         <v>66.5</v>
       </c>
-      <c r="S15" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R15),D15*R15,0)</f>
+      <c r="U15" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R15),ISNUMBER(T15)),T15/R15-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V15" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T15),D15*T15,0)</f>
         <v>60182.5</v>
       </c>
     </row>
@@ -4755,30 +5298,30 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>82.2</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L16" s="12"/>
       <c r="M16" s="10"/>
@@ -4798,12 +5341,23 @@
         <f aca="false">IF(COUNT(F16,I16,L16)=0,"",MAX(F16,I16,L16))</f>
         <v>82.2</v>
       </c>
-      <c r="R16" s="14" t="n">
-        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",ROUND(P16,2))</f>
+      <c r="R16" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S16" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R16),ROUNDDOWN(R16*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T16" s="14" t="n">
+        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",IF(ISNUMBER(S16),MIN(ROUND(P16,2),S16),ROUND(P16,2)))</f>
         <v>82.2</v>
       </c>
-      <c r="S16" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R16),D16*R16,0)</f>
+      <c r="U16" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R16),ISNUMBER(T16)),T16/R16-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V16" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T16),D16*T16,0)</f>
         <v>74391</v>
       </c>
     </row>
@@ -4812,30 +5366,30 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>107.6</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="10"/>
@@ -4855,12 +5409,23 @@
         <f aca="false">IF(COUNT(F17,I17,L17)=0,"",MAX(F17,I17,L17))</f>
         <v>107.6</v>
       </c>
-      <c r="R17" s="14" t="n">
-        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",ROUND(P17,2))</f>
+      <c r="R17" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S17" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R17),ROUNDDOWN(R17*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T17" s="14" t="n">
+        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",IF(ISNUMBER(S17),MIN(ROUND(P17,2),S17),ROUND(P17,2)))</f>
         <v>107.6</v>
       </c>
-      <c r="S17" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R17),D17*R17,0)</f>
+      <c r="U17" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R17),ISNUMBER(T17)),T17/R17-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V17" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T17),D17*T17,0)</f>
         <v>97378</v>
       </c>
     </row>
@@ -4869,30 +5434,30 @@
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>107.6</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="10"/>
@@ -4912,12 +5477,23 @@
         <f aca="false">IF(COUNT(F18,I18,L18)=0,"",MAX(F18,I18,L18))</f>
         <v>107.6</v>
       </c>
-      <c r="R18" s="14" t="n">
-        <f aca="false">IF(COUNT(F18,I18,L18)=0,"Sem cotação",ROUND(P18,2))</f>
+      <c r="R18" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S18" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R18),ROUNDDOWN(R18*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T18" s="14" t="n">
+        <f aca="false">IF(COUNT(F18,I18,L18)=0,"Sem cotação",IF(ISNUMBER(S18),MIN(ROUND(P18,2),S18),ROUND(P18,2)))</f>
         <v>107.6</v>
       </c>
-      <c r="S18" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R18),D18*R18,0)</f>
+      <c r="U18" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R18),ISNUMBER(T18)),T18/R18-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V18" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T18),D18*T18,0)</f>
         <v>97378</v>
       </c>
     </row>
@@ -4926,30 +5502,30 @@
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>66.5</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="10"/>
@@ -4969,12 +5545,23 @@
         <f aca="false">IF(COUNT(F19,I19,L19)=0,"",MAX(F19,I19,L19))</f>
         <v>66.5</v>
       </c>
-      <c r="R19" s="14" t="n">
-        <f aca="false">IF(COUNT(F19,I19,L19)=0,"Sem cotação",ROUND(P19,2))</f>
+      <c r="R19" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S19" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R19),ROUNDDOWN(R19*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T19" s="14" t="n">
+        <f aca="false">IF(COUNT(F19,I19,L19)=0,"Sem cotação",IF(ISNUMBER(S19),MIN(ROUND(P19,2),S19),ROUND(P19,2)))</f>
         <v>66.5</v>
       </c>
-      <c r="S19" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R19),D19*R19,0)</f>
+      <c r="U19" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R19),ISNUMBER(T19)),T19/R19-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V19" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T19),D19*T19,0)</f>
         <v>60182.5</v>
       </c>
     </row>
@@ -4983,30 +5570,30 @@
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>107.6</v>
       </c>
       <c r="G20" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="10"/>
@@ -5026,12 +5613,23 @@
         <f aca="false">IF(COUNT(F20,I20,L20)=0,"",MAX(F20,I20,L20))</f>
         <v>107.6</v>
       </c>
-      <c r="R20" s="14" t="n">
-        <f aca="false">IF(COUNT(F20,I20,L20)=0,"Sem cotação",ROUND(P20,2))</f>
+      <c r="R20" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S20" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R20),ROUNDDOWN(R20*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T20" s="14" t="n">
+        <f aca="false">IF(COUNT(F20,I20,L20)=0,"Sem cotação",IF(ISNUMBER(S20),MIN(ROUND(P20,2),S20),ROUND(P20,2)))</f>
         <v>107.6</v>
       </c>
-      <c r="S20" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R20),D20*R20,0)</f>
+      <c r="U20" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R20),ISNUMBER(T20)),T20/R20-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V20" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T20),D20*T20,0)</f>
         <v>97378</v>
       </c>
     </row>
@@ -5040,40 +5638,40 @@
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>3092</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>124.8</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>127.89</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>123.5</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N21" s="12" t="n">
         <f aca="false">IF(COUNT(F21,I21,L21)=0,"",MIN(F21,I21,L21))</f>
@@ -5091,12 +5689,23 @@
         <f aca="false">IF(COUNT(F21,I21,L21)=0,"",MAX(F21,I21,L21))</f>
         <v>127.89</v>
       </c>
-      <c r="R21" s="14" t="n">
-        <f aca="false">IF(COUNT(F21,I21,L21)=0,"Sem cotação",ROUND(P21,2))</f>
+      <c r="R21" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S21" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R21),ROUNDDOWN(R21*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T21" s="14" t="n">
+        <f aca="false">IF(COUNT(F21,I21,L21)=0,"Sem cotação",IF(ISNUMBER(S21),MIN(ROUND(P21,2),S21),ROUND(P21,2)))</f>
         <v>124.8</v>
       </c>
-      <c r="S21" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R21),D21*R21,0)</f>
+      <c r="U21" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R21),ISNUMBER(T21)),T21/R21-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V21" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T21),D21*T21,0)</f>
         <v>385881.6</v>
       </c>
     </row>
@@ -5105,40 +5714,40 @@
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>10860</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>68</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>70.5</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>53.28</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N22" s="12" t="n">
         <f aca="false">IF(COUNT(F22,I22,L22)=0,"",MIN(F22,I22,L22))</f>
@@ -5156,12 +5765,23 @@
         <f aca="false">IF(COUNT(F22,I22,L22)=0,"",MAX(F22,I22,L22))</f>
         <v>70.5</v>
       </c>
-      <c r="R22" s="14" t="n">
-        <f aca="false">IF(COUNT(F22,I22,L22)=0,"Sem cotação",ROUND(P22,2))</f>
+      <c r="R22" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S22" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R22),ROUNDDOWN(R22*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T22" s="14" t="n">
+        <f aca="false">IF(COUNT(F22,I22,L22)=0,"Sem cotação",IF(ISNUMBER(S22),MIN(ROUND(P22,2),S22),ROUND(P22,2)))</f>
         <v>68</v>
       </c>
-      <c r="S22" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R22),D22*R22,0)</f>
+      <c r="U22" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R22),ISNUMBER(T22)),T22/R22-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V22" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T22),D22*T22,0)</f>
         <v>738480</v>
       </c>
     </row>
@@ -5170,40 +5790,40 @@
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>181</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>104.25</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>99</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>98.49</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N23" s="12" t="n">
         <f aca="false">IF(COUNT(F23,I23,L23)=0,"",MIN(F23,I23,L23))</f>
@@ -5221,12 +5841,23 @@
         <f aca="false">IF(COUNT(F23,I23,L23)=0,"",MAX(F23,I23,L23))</f>
         <v>104.25</v>
       </c>
-      <c r="R23" s="14" t="n">
-        <f aca="false">IF(COUNT(F23,I23,L23)=0,"Sem cotação",ROUND(P23,2))</f>
+      <c r="R23" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S23" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R23),ROUNDDOWN(R23*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T23" s="14" t="n">
+        <f aca="false">IF(COUNT(F23,I23,L23)=0,"Sem cotação",IF(ISNUMBER(S23),MIN(ROUND(P23,2),S23),ROUND(P23,2)))</f>
         <v>99</v>
       </c>
-      <c r="S23" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R23),D23*R23,0)</f>
+      <c r="U23" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R23),ISNUMBER(T23)),T23/R23-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V23" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T23),D23*T23,0)</f>
         <v>17919</v>
       </c>
     </row>
@@ -5235,40 +5866,40 @@
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>2528</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>124.8</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>99</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>98.49</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N24" s="12" t="n">
         <f aca="false">IF(COUNT(F24,I24,L24)=0,"",MIN(F24,I24,L24))</f>
@@ -5286,12 +5917,23 @@
         <f aca="false">IF(COUNT(F24,I24,L24)=0,"",MAX(F24,I24,L24))</f>
         <v>124.8</v>
       </c>
-      <c r="R24" s="14" t="n">
-        <f aca="false">IF(COUNT(F24,I24,L24)=0,"Sem cotação",ROUND(P24,2))</f>
+      <c r="R24" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S24" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R24),ROUNDDOWN(R24*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T24" s="14" t="n">
+        <f aca="false">IF(COUNT(F24,I24,L24)=0,"Sem cotação",IF(ISNUMBER(S24),MIN(ROUND(P24,2),S24),ROUND(P24,2)))</f>
         <v>99</v>
       </c>
-      <c r="S24" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R24),D24*R24,0)</f>
+      <c r="U24" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R24),ISNUMBER(T24)),T24/R24-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V24" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T24),D24*T24,0)</f>
         <v>250272</v>
       </c>
     </row>
@@ -5300,40 +5942,40 @@
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>97</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>104.25</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>113</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>100.45</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N25" s="12" t="n">
         <f aca="false">IF(COUNT(F25,I25,L25)=0,"",MIN(F25,I25,L25))</f>
@@ -5351,12 +5993,23 @@
         <f aca="false">IF(COUNT(F25,I25,L25)=0,"",MAX(F25,I25,L25))</f>
         <v>113</v>
       </c>
-      <c r="R25" s="14" t="n">
-        <f aca="false">IF(COUNT(F25,I25,L25)=0,"Sem cotação",ROUND(P25,2))</f>
+      <c r="R25" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S25" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R25),ROUNDDOWN(R25*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T25" s="14" t="n">
+        <f aca="false">IF(COUNT(F25,I25,L25)=0,"Sem cotação",IF(ISNUMBER(S25),MIN(ROUND(P25,2),S25),ROUND(P25,2)))</f>
         <v>104.25</v>
       </c>
-      <c r="S25" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R25),D25*R25,0)</f>
+      <c r="U25" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R25),ISNUMBER(T25)),T25/R25-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V25" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T25),D25*T25,0)</f>
         <v>10112.25</v>
       </c>
     </row>
@@ -5365,40 +6018,40 @@
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>102</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>139.6</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>152</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>82.5</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N26" s="12" t="n">
         <f aca="false">IF(COUNT(F26,I26,L26)=0,"",MIN(F26,I26,L26))</f>
@@ -5416,12 +6069,23 @@
         <f aca="false">IF(COUNT(F26,I26,L26)=0,"",MAX(F26,I26,L26))</f>
         <v>152</v>
       </c>
-      <c r="R26" s="14" t="n">
-        <f aca="false">IF(COUNT(F26,I26,L26)=0,"Sem cotação",ROUND(P26,2))</f>
+      <c r="R26" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S26" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R26),ROUNDDOWN(R26*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T26" s="14" t="n">
+        <f aca="false">IF(COUNT(F26,I26,L26)=0,"Sem cotação",IF(ISNUMBER(S26),MIN(ROUND(P26,2),S26),ROUND(P26,2)))</f>
         <v>139.6</v>
       </c>
-      <c r="S26" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R26),D26*R26,0)</f>
+      <c r="U26" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R26),ISNUMBER(T26)),T26/R26-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V26" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T26),D26*T26,0)</f>
         <v>14239.2</v>
       </c>
     </row>
@@ -5430,40 +6094,40 @@
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>48</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>171.35</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>166</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>82.5</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N27" s="12" t="n">
         <f aca="false">IF(COUNT(F27,I27,L27)=0,"",MIN(F27,I27,L27))</f>
@@ -5481,12 +6145,23 @@
         <f aca="false">IF(COUNT(F27,I27,L27)=0,"",MAX(F27,I27,L27))</f>
         <v>171.35</v>
       </c>
-      <c r="R27" s="14" t="n">
-        <f aca="false">IF(COUNT(F27,I27,L27)=0,"Sem cotação",ROUND(P27,2))</f>
+      <c r="R27" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S27" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R27),ROUNDDOWN(R27*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T27" s="14" t="n">
+        <f aca="false">IF(COUNT(F27,I27,L27)=0,"Sem cotação",IF(ISNUMBER(S27),MIN(ROUND(P27,2),S27),ROUND(P27,2)))</f>
         <v>166</v>
       </c>
-      <c r="S27" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R27),D27*R27,0)</f>
+      <c r="U27" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R27),ISNUMBER(T27)),T27/R27-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V27" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T27),D27*T27,0)</f>
         <v>7968</v>
       </c>
     </row>
@@ -5495,34 +6170,34 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>235.75</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>200.5</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="10"/>
@@ -5542,12 +6217,23 @@
         <f aca="false">IF(COUNT(F28,I28,L28)=0,"",MAX(F28,I28,L28))</f>
         <v>235.75</v>
       </c>
-      <c r="R28" s="14" t="n">
-        <f aca="false">IF(COUNT(F28,I28,L28)=0,"Sem cotação",ROUND(P28,2))</f>
+      <c r="R28" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S28" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R28),ROUNDDOWN(R28*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T28" s="14" t="n">
+        <f aca="false">IF(COUNT(F28,I28,L28)=0,"Sem cotação",IF(ISNUMBER(S28),MIN(ROUND(P28,2),S28),ROUND(P28,2)))</f>
         <v>218.13</v>
       </c>
-      <c r="S28" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R28),D28*R28,0)</f>
+      <c r="U28" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R28),ISNUMBER(T28)),T28/R28-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V28" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T28),D28*T28,0)</f>
         <v>197407.65</v>
       </c>
     </row>
@@ -5556,30 +6242,30 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>48</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>136</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="10"/>
@@ -5599,12 +6285,23 @@
         <f aca="false">IF(COUNT(F29,I29,L29)=0,"",MAX(F29,I29,L29))</f>
         <v>136</v>
       </c>
-      <c r="R29" s="14" t="n">
-        <f aca="false">IF(COUNT(F29,I29,L29)=0,"Sem cotação",ROUND(P29,2))</f>
+      <c r="R29" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S29" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R29),ROUNDDOWN(R29*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T29" s="14" t="n">
+        <f aca="false">IF(COUNT(F29,I29,L29)=0,"Sem cotação",IF(ISNUMBER(S29),MIN(ROUND(P29,2),S29),ROUND(P29,2)))</f>
         <v>136</v>
       </c>
-      <c r="S29" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R29),D29*R29,0)</f>
+      <c r="U29" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R29),ISNUMBER(T29)),T29/R29-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V29" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T29),D29*T29,0)</f>
         <v>6528</v>
       </c>
     </row>
@@ -5613,40 +6310,40 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>110.25</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>149.56</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>150</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N30" s="12" t="n">
         <f aca="false">IF(COUNT(F30,I30,L30)=0,"",MIN(F30,I30,L30))</f>
@@ -5664,12 +6361,23 @@
         <f aca="false">IF(COUNT(F30,I30,L30)=0,"",MAX(F30,I30,L30))</f>
         <v>150</v>
       </c>
-      <c r="R30" s="14" t="n">
-        <f aca="false">IF(COUNT(F30,I30,L30)=0,"Sem cotação",ROUND(P30,2))</f>
+      <c r="R30" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S30" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R30),ROUNDDOWN(R30*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T30" s="14" t="n">
+        <f aca="false">IF(COUNT(F30,I30,L30)=0,"Sem cotação",IF(ISNUMBER(S30),MIN(ROUND(P30,2),S30),ROUND(P30,2)))</f>
         <v>149.56</v>
       </c>
-      <c r="S30" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R30),D30*R30,0)</f>
+      <c r="U30" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R30),ISNUMBER(T30)),T30/R30-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V30" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T30),D30*T30,0)</f>
         <v>135351.8</v>
       </c>
     </row>
@@ -5678,40 +6386,40 @@
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>53.8</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>76.05</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N31" s="12" t="n">
         <f aca="false">IF(COUNT(F31,I31,L31)=0,"",MIN(F31,I31,L31))</f>
@@ -5729,12 +6437,23 @@
         <f aca="false">IF(COUNT(F31,I31,L31)=0,"",MAX(F31,I31,L31))</f>
         <v>76.05</v>
       </c>
-      <c r="R31" s="14" t="n">
-        <f aca="false">IF(COUNT(F31,I31,L31)=0,"Sem cotação",ROUND(P31,2))</f>
+      <c r="R31" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S31" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R31),ROUNDDOWN(R31*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T31" s="14" t="n">
+        <f aca="false">IF(COUNT(F31,I31,L31)=0,"Sem cotação",IF(ISNUMBER(S31),MIN(ROUND(P31,2),S31),ROUND(P31,2)))</f>
         <v>53.8</v>
       </c>
-      <c r="S31" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R31),D31*R31,0)</f>
+      <c r="U31" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R31),ISNUMBER(T31)),T31/R31-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V31" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T31),D31*T31,0)</f>
         <v>48689</v>
       </c>
     </row>
@@ -5743,40 +6462,40 @@
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>53.8</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>72.91</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N32" s="12" t="n">
         <f aca="false">IF(COUNT(F32,I32,L32)=0,"",MIN(F32,I32,L32))</f>
@@ -5794,12 +6513,23 @@
         <f aca="false">IF(COUNT(F32,I32,L32)=0,"",MAX(F32,I32,L32))</f>
         <v>72.91</v>
       </c>
-      <c r="R32" s="14" t="n">
-        <f aca="false">IF(COUNT(F32,I32,L32)=0,"Sem cotação",ROUND(P32,2))</f>
+      <c r="R32" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S32" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R32),ROUNDDOWN(R32*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T32" s="14" t="n">
+        <f aca="false">IF(COUNT(F32,I32,L32)=0,"Sem cotação",IF(ISNUMBER(S32),MIN(ROUND(P32,2),S32),ROUND(P32,2)))</f>
         <v>53.8</v>
       </c>
-      <c r="S32" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R32),D32*R32,0)</f>
+      <c r="U32" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R32),ISNUMBER(T32)),T32/R32-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V32" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T32),D32*T32,0)</f>
         <v>48689</v>
       </c>
     </row>
@@ -5808,40 +6538,40 @@
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>21942</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>64.31</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>43.9</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>10.3</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N33" s="12" t="n">
         <f aca="false">IF(COUNT(F33,I33,L33)=0,"",MIN(F33,I33,L33))</f>
@@ -5859,12 +6589,23 @@
         <f aca="false">IF(COUNT(F33,I33,L33)=0,"",MAX(F33,I33,L33))</f>
         <v>64.31</v>
       </c>
-      <c r="R33" s="14" t="n">
-        <f aca="false">IF(COUNT(F33,I33,L33)=0,"Sem cotação",ROUND(P33,2))</f>
+      <c r="R33" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S33" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R33),ROUNDDOWN(R33*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T33" s="14" t="n">
+        <f aca="false">IF(COUNT(F33,I33,L33)=0,"Sem cotação",IF(ISNUMBER(S33),MIN(ROUND(P33,2),S33),ROUND(P33,2)))</f>
         <v>43.9</v>
       </c>
-      <c r="S33" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R33),D33*R33,0)</f>
+      <c r="U33" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R33),ISNUMBER(T33)),T33/R33-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V33" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T33),D33*T33,0)</f>
         <v>963253.8</v>
       </c>
     </row>
@@ -5873,40 +6614,40 @@
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>69.5</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>94.22</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>19.5</v>
       </c>
       <c r="M34" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N34" s="12" t="n">
         <f aca="false">IF(COUNT(F34,I34,L34)=0,"",MIN(F34,I34,L34))</f>
@@ -5924,12 +6665,23 @@
         <f aca="false">IF(COUNT(F34,I34,L34)=0,"",MAX(F34,I34,L34))</f>
         <v>94.22</v>
       </c>
-      <c r="R34" s="14" t="n">
-        <f aca="false">IF(COUNT(F34,I34,L34)=0,"Sem cotação",ROUND(P34,2))</f>
+      <c r="R34" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S34" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R34),ROUNDDOWN(R34*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T34" s="14" t="n">
+        <f aca="false">IF(COUNT(F34,I34,L34)=0,"Sem cotação",IF(ISNUMBER(S34),MIN(ROUND(P34,2),S34),ROUND(P34,2)))</f>
         <v>69.5</v>
       </c>
-      <c r="S34" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R34),D34*R34,0)</f>
+      <c r="U34" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R34),ISNUMBER(T34)),T34/R34-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V34" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T34),D34*T34,0)</f>
         <v>62897.5</v>
       </c>
     </row>
@@ -5938,40 +6690,40 @@
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>101.25</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>137.21</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M35" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N35" s="12" t="n">
         <f aca="false">IF(COUNT(F35,I35,L35)=0,"",MIN(F35,I35,L35))</f>
@@ -5989,12 +6741,23 @@
         <f aca="false">IF(COUNT(F35,I35,L35)=0,"",MAX(F35,I35,L35))</f>
         <v>137.21</v>
       </c>
-      <c r="R35" s="14" t="n">
-        <f aca="false">IF(COUNT(F35,I35,L35)=0,"Sem cotação",ROUND(P35,2))</f>
+      <c r="R35" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S35" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R35),ROUNDDOWN(R35*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T35" s="14" t="n">
+        <f aca="false">IF(COUNT(F35,I35,L35)=0,"Sem cotação",IF(ISNUMBER(S35),MIN(ROUND(P35,2),S35),ROUND(P35,2)))</f>
         <v>101.25</v>
       </c>
-      <c r="S35" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R35),D35*R35,0)</f>
+      <c r="U35" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R35),ISNUMBER(T35)),T35/R35-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V35" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T35),D35*T35,0)</f>
         <v>91631.25</v>
       </c>
     </row>
@@ -6003,40 +6766,40 @@
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>473</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>641.01</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>600</v>
       </c>
       <c r="M36" s="13" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N36" s="12" t="n">
         <f aca="false">IF(COUNT(F36,I36,L36)=0,"",MIN(F36,I36,L36))</f>
@@ -6054,12 +6817,23 @@
         <f aca="false">IF(COUNT(F36,I36,L36)=0,"",MAX(F36,I36,L36))</f>
         <v>641.01</v>
       </c>
-      <c r="R36" s="14" t="n">
-        <f aca="false">IF(COUNT(F36,I36,L36)=0,"Sem cotação",ROUND(P36,2))</f>
+      <c r="R36" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S36" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R36),ROUNDDOWN(R36*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T36" s="14" t="n">
+        <f aca="false">IF(COUNT(F36,I36,L36)=0,"Sem cotação",IF(ISNUMBER(S36),MIN(ROUND(P36,2),S36),ROUND(P36,2)))</f>
         <v>600</v>
       </c>
-      <c r="S36" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R36),D36*R36,0)</f>
+      <c r="U36" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R36),ISNUMBER(T36)),T36/R36-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V36" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T36),D36*T36,0)</f>
         <v>543000</v>
       </c>
     </row>
@@ -6068,40 +6842,40 @@
         <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>242</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>214.5</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>290.89</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>638</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N37" s="12" t="n">
         <f aca="false">IF(COUNT(F37,I37,L37)=0,"",MIN(F37,I37,L37))</f>
@@ -6119,12 +6893,23 @@
         <f aca="false">IF(COUNT(F37,I37,L37)=0,"",MAX(F37,I37,L37))</f>
         <v>638</v>
       </c>
-      <c r="R37" s="14" t="n">
-        <f aca="false">IF(COUNT(F37,I37,L37)=0,"Sem cotação",ROUND(P37,2))</f>
+      <c r="R37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S37" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R37),ROUNDDOWN(R37*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T37" s="14" t="n">
+        <f aca="false">IF(COUNT(F37,I37,L37)=0,"Sem cotação",IF(ISNUMBER(S37),MIN(ROUND(P37,2),S37),ROUND(P37,2)))</f>
         <v>290.89</v>
       </c>
-      <c r="S37" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R37),D37*R37,0)</f>
+      <c r="U37" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R37),ISNUMBER(T37)),T37/R37-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V37" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T37),D37*T37,0)</f>
         <v>70395.38</v>
       </c>
     </row>
@@ -6133,40 +6918,40 @@
         <v>36</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>482</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>653.36</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>450</v>
       </c>
       <c r="M38" s="13" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N38" s="12" t="n">
         <f aca="false">IF(COUNT(F38,I38,L38)=0,"",MIN(F38,I38,L38))</f>
@@ -6184,12 +6969,23 @@
         <f aca="false">IF(COUNT(F38,I38,L38)=0,"",MAX(F38,I38,L38))</f>
         <v>653.36</v>
       </c>
-      <c r="R38" s="14" t="n">
-        <f aca="false">IF(COUNT(F38,I38,L38)=0,"Sem cotação",ROUND(P38,2))</f>
+      <c r="R38" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S38" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R38),ROUNDDOWN(R38*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T38" s="14" t="n">
+        <f aca="false">IF(COUNT(F38,I38,L38)=0,"Sem cotação",IF(ISNUMBER(S38),MIN(ROUND(P38,2),S38),ROUND(P38,2)))</f>
         <v>482</v>
       </c>
-      <c r="S38" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R38),D38*R38,0)</f>
+      <c r="U38" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R38),ISNUMBER(T38)),T38/R38-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V38" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T38),D38*T38,0)</f>
         <v>436210</v>
       </c>
     </row>
@@ -6198,40 +6994,40 @@
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>11.66</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>15.82</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>18.32</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N39" s="12" t="n">
         <f aca="false">IF(COUNT(F39,I39,L39)=0,"",MIN(F39,I39,L39))</f>
@@ -6249,12 +7045,23 @@
         <f aca="false">IF(COUNT(F39,I39,L39)=0,"",MAX(F39,I39,L39))</f>
         <v>18.32</v>
       </c>
-      <c r="R39" s="14" t="n">
-        <f aca="false">IF(COUNT(F39,I39,L39)=0,"Sem cotação",ROUND(P39,2))</f>
+      <c r="R39" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S39" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R39),ROUNDDOWN(R39*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T39" s="14" t="n">
+        <f aca="false">IF(COUNT(F39,I39,L39)=0,"Sem cotação",IF(ISNUMBER(S39),MIN(ROUND(P39,2),S39),ROUND(P39,2)))</f>
         <v>15.82</v>
       </c>
-      <c r="S39" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R39),D39*R39,0)</f>
+      <c r="U39" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R39),ISNUMBER(T39)),T39/R39-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V39" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T39),D39*T39,0)</f>
         <v>14317.1</v>
       </c>
     </row>
@@ -6263,40 +7070,40 @@
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>826</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>257.8</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>144.49</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>180</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N40" s="12" t="n">
         <f aca="false">IF(COUNT(F40,I40,L40)=0,"",MIN(F40,I40,L40))</f>
@@ -6314,12 +7121,23 @@
         <f aca="false">IF(COUNT(F40,I40,L40)=0,"",MAX(F40,I40,L40))</f>
         <v>257.8</v>
       </c>
-      <c r="R40" s="14" t="n">
-        <f aca="false">IF(COUNT(F40,I40,L40)=0,"Sem cotação",ROUND(P40,2))</f>
+      <c r="R40" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S40" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R40),ROUNDDOWN(R40*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T40" s="14" t="n">
+        <f aca="false">IF(COUNT(F40,I40,L40)=0,"Sem cotação",IF(ISNUMBER(S40),MIN(ROUND(P40,2),S40),ROUND(P40,2)))</f>
         <v>180</v>
       </c>
-      <c r="S40" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R40),D40*R40,0)</f>
+      <c r="U40" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R40),ISNUMBER(T40)),T40/R40-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V40" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T40),D40*T40,0)</f>
         <v>148680</v>
       </c>
     </row>
@@ -6328,40 +7146,40 @@
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>137.5</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>186.38</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>238</v>
       </c>
       <c r="M41" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N41" s="12" t="n">
         <f aca="false">IF(COUNT(F41,I41,L41)=0,"",MIN(F41,I41,L41))</f>
@@ -6379,12 +7197,23 @@
         <f aca="false">IF(COUNT(F41,I41,L41)=0,"",MAX(F41,I41,L41))</f>
         <v>238</v>
       </c>
-      <c r="R41" s="14" t="n">
-        <f aca="false">IF(COUNT(F41,I41,L41)=0,"Sem cotação",ROUND(P41,2))</f>
+      <c r="R41" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S41" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R41),ROUNDDOWN(R41*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T41" s="14" t="n">
+        <f aca="false">IF(COUNT(F41,I41,L41)=0,"Sem cotação",IF(ISNUMBER(S41),MIN(ROUND(P41,2),S41),ROUND(P41,2)))</f>
         <v>186.38</v>
       </c>
-      <c r="S41" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R41),D41*R41,0)</f>
+      <c r="U41" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R41),ISNUMBER(T41)),T41/R41-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V41" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T41),D41*T41,0)</f>
         <v>168673.9</v>
       </c>
     </row>
@@ -6393,34 +7222,34 @@
         <v>40</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>68</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L42" s="12"/>
       <c r="M42" s="10"/>
@@ -6440,12 +7269,23 @@
         <f aca="false">IF(COUNT(F42,I42,L42)=0,"",MAX(F42,I42,L42))</f>
         <v>68</v>
       </c>
-      <c r="R42" s="14" t="n">
-        <f aca="false">IF(COUNT(F42,I42,L42)=0,"Sem cotação",ROUND(P42,2))</f>
+      <c r="R42" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S42" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R42),ROUNDDOWN(R42*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T42" s="14" t="n">
+        <f aca="false">IF(COUNT(F42,I42,L42)=0,"Sem cotação",IF(ISNUMBER(S42),MIN(ROUND(P42,2),S42),ROUND(P42,2)))</f>
         <v>49</v>
       </c>
-      <c r="S42" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R42),D42*R42,0)</f>
+      <c r="U42" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R42),ISNUMBER(T42)),T42/R42-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V42" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T42),D42*T42,0)</f>
         <v>44345</v>
       </c>
     </row>
@@ -6454,40 +7294,40 @@
         <v>41</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>1496</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>41.1</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>78.5</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>25.3</v>
       </c>
       <c r="M43" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N43" s="12" t="n">
         <f aca="false">IF(COUNT(F43,I43,L43)=0,"",MIN(F43,I43,L43))</f>
@@ -6505,12 +7345,23 @@
         <f aca="false">IF(COUNT(F43,I43,L43)=0,"",MAX(F43,I43,L43))</f>
         <v>78.5</v>
       </c>
-      <c r="R43" s="14" t="n">
-        <f aca="false">IF(COUNT(F43,I43,L43)=0,"Sem cotação",ROUND(P43,2))</f>
+      <c r="R43" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S43" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R43),ROUNDDOWN(R43*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T43" s="14" t="n">
+        <f aca="false">IF(COUNT(F43,I43,L43)=0,"Sem cotação",IF(ISNUMBER(S43),MIN(ROUND(P43,2),S43),ROUND(P43,2)))</f>
         <v>41.1</v>
       </c>
-      <c r="S43" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R43),D43*R43,0)</f>
+      <c r="U43" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R43),ISNUMBER(T43)),T43/R43-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V43" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T43),D43*T43,0)</f>
         <v>61485.6</v>
       </c>
     </row>
@@ -6519,40 +7370,40 @@
         <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>1496</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>69.5</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>78.5</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>90</v>
       </c>
       <c r="M44" s="13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N44" s="12" t="n">
         <f aca="false">IF(COUNT(F44,I44,L44)=0,"",MIN(F44,I44,L44))</f>
@@ -6570,12 +7421,23 @@
         <f aca="false">IF(COUNT(F44,I44,L44)=0,"",MAX(F44,I44,L44))</f>
         <v>90</v>
       </c>
-      <c r="R44" s="14" t="n">
-        <f aca="false">IF(COUNT(F44,I44,L44)=0,"Sem cotação",ROUND(P44,2))</f>
+      <c r="R44" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S44" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R44),ROUNDDOWN(R44*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T44" s="14" t="n">
+        <f aca="false">IF(COUNT(F44,I44,L44)=0,"Sem cotação",IF(ISNUMBER(S44),MIN(ROUND(P44,2),S44),ROUND(P44,2)))</f>
         <v>78.5</v>
       </c>
-      <c r="S44" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R44),D44*R44,0)</f>
+      <c r="U44" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R44),ISNUMBER(T44)),T44/R44-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V44" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T44),D44*T44,0)</f>
         <v>117436</v>
       </c>
     </row>
@@ -6584,40 +7446,40 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>640</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>85.2</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>115.53</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>107</v>
       </c>
       <c r="M45" s="13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N45" s="12" t="n">
         <f aca="false">IF(COUNT(F45,I45,L45)=0,"",MIN(F45,I45,L45))</f>
@@ -6635,12 +7497,23 @@
         <f aca="false">IF(COUNT(F45,I45,L45)=0,"",MAX(F45,I45,L45))</f>
         <v>115.53</v>
       </c>
-      <c r="R45" s="14" t="n">
-        <f aca="false">IF(COUNT(F45,I45,L45)=0,"Sem cotação",ROUND(P45,2))</f>
+      <c r="R45" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S45" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R45),ROUNDDOWN(R45*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T45" s="14" t="n">
+        <f aca="false">IF(COUNT(F45,I45,L45)=0,"Sem cotação",IF(ISNUMBER(S45),MIN(ROUND(P45,2),S45),ROUND(P45,2)))</f>
         <v>107</v>
       </c>
-      <c r="S45" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R45),D45*R45,0)</f>
+      <c r="U45" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R45),ISNUMBER(T45)),T45/R45-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V45" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T45),D45*T45,0)</f>
         <v>68480</v>
       </c>
     </row>
@@ -6649,40 +7522,40 @@
         <v>44</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>5027</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>85.2</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>115.53</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>121</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N46" s="12" t="n">
         <f aca="false">IF(COUNT(F46,I46,L46)=0,"",MIN(F46,I46,L46))</f>
@@ -6700,12 +7573,23 @@
         <f aca="false">IF(COUNT(F46,I46,L46)=0,"",MAX(F46,I46,L46))</f>
         <v>121</v>
       </c>
-      <c r="R46" s="14" t="n">
-        <f aca="false">IF(COUNT(F46,I46,L46)=0,"Sem cotação",ROUND(P46,2))</f>
+      <c r="R46" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S46" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R46),ROUNDDOWN(R46*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T46" s="14" t="n">
+        <f aca="false">IF(COUNT(F46,I46,L46)=0,"Sem cotação",IF(ISNUMBER(S46),MIN(ROUND(P46,2),S46),ROUND(P46,2)))</f>
         <v>115.53</v>
       </c>
-      <c r="S46" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R46),D46*R46,0)</f>
+      <c r="U46" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R46),ISNUMBER(T46)),T46/R46-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V46" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T46),D46*T46,0)</f>
         <v>580769.31</v>
       </c>
     </row>
@@ -6714,40 +7598,40 @@
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>3174</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>101.25</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>137.21</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>98</v>
       </c>
       <c r="M47" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N47" s="12" t="n">
         <f aca="false">IF(COUNT(F47,I47,L47)=0,"",MIN(F47,I47,L47))</f>
@@ -6765,12 +7649,23 @@
         <f aca="false">IF(COUNT(F47,I47,L47)=0,"",MAX(F47,I47,L47))</f>
         <v>137.21</v>
       </c>
-      <c r="R47" s="14" t="n">
-        <f aca="false">IF(COUNT(F47,I47,L47)=0,"Sem cotação",ROUND(P47,2))</f>
+      <c r="R47" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S47" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R47),ROUNDDOWN(R47*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T47" s="14" t="n">
+        <f aca="false">IF(COUNT(F47,I47,L47)=0,"Sem cotação",IF(ISNUMBER(S47),MIN(ROUND(P47,2),S47),ROUND(P47,2)))</f>
         <v>101.25</v>
       </c>
-      <c r="S47" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R47),D47*R47,0)</f>
+      <c r="U47" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R47),ISNUMBER(T47)),T47/R47-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V47" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T47),D47*T47,0)</f>
         <v>321367.5</v>
       </c>
     </row>
@@ -6779,40 +7674,40 @@
         <v>46</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>3174</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>133</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I48" s="12" t="n">
         <v>180.2</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>128.87</v>
       </c>
       <c r="M48" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N48" s="12" t="n">
         <f aca="false">IF(COUNT(F48,I48,L48)=0,"",MIN(F48,I48,L48))</f>
@@ -6830,12 +7725,23 @@
         <f aca="false">IF(COUNT(F48,I48,L48)=0,"",MAX(F48,I48,L48))</f>
         <v>180.2</v>
       </c>
-      <c r="R48" s="14" t="n">
-        <f aca="false">IF(COUNT(F48,I48,L48)=0,"Sem cotação",ROUND(P48,2))</f>
+      <c r="R48" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S48" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R48),ROUNDDOWN(R48*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T48" s="14" t="n">
+        <f aca="false">IF(COUNT(F48,I48,L48)=0,"Sem cotação",IF(ISNUMBER(S48),MIN(ROUND(P48,2),S48),ROUND(P48,2)))</f>
         <v>133</v>
       </c>
-      <c r="S48" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R48),D48*R48,0)</f>
+      <c r="U48" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R48),ISNUMBER(T48)),T48/R48-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V48" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T48),D48*T48,0)</f>
         <v>422142</v>
       </c>
     </row>
@@ -6844,40 +7750,40 @@
         <v>47</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>2715</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>164.75</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>223.2</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L49" s="12" t="n">
         <v>159.25</v>
       </c>
       <c r="M49" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N49" s="12" t="n">
         <f aca="false">IF(COUNT(F49,I49,L49)=0,"",MIN(F49,I49,L49))</f>
@@ -6895,12 +7801,23 @@
         <f aca="false">IF(COUNT(F49,I49,L49)=0,"",MAX(F49,I49,L49))</f>
         <v>223.2</v>
       </c>
-      <c r="R49" s="14" t="n">
-        <f aca="false">IF(COUNT(F49,I49,L49)=0,"Sem cotação",ROUND(P49,2))</f>
+      <c r="R49" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S49" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R49),ROUNDDOWN(R49*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T49" s="14" t="n">
+        <f aca="false">IF(COUNT(F49,I49,L49)=0,"Sem cotação",IF(ISNUMBER(S49),MIN(ROUND(P49,2),S49),ROUND(P49,2)))</f>
         <v>164.75</v>
       </c>
-      <c r="S49" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R49),D49*R49,0)</f>
+      <c r="U49" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R49),ISNUMBER(T49)),T49/R49-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V49" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T49),D49*T49,0)</f>
         <v>447296.25</v>
       </c>
     </row>
@@ -6909,40 +7826,40 @@
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>5027</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>183.8</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I50" s="12" t="n">
         <v>248.99</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L50" s="12" t="n">
         <v>177.87</v>
       </c>
       <c r="M50" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N50" s="12" t="n">
         <f aca="false">IF(COUNT(F50,I50,L50)=0,"",MIN(F50,I50,L50))</f>
@@ -6960,12 +7877,23 @@
         <f aca="false">IF(COUNT(F50,I50,L50)=0,"",MAX(F50,I50,L50))</f>
         <v>248.99</v>
       </c>
-      <c r="R50" s="14" t="n">
-        <f aca="false">IF(COUNT(F50,I50,L50)=0,"Sem cotação",ROUND(P50,2))</f>
+      <c r="R50" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S50" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R50),ROUNDDOWN(R50*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T50" s="14" t="n">
+        <f aca="false">IF(COUNT(F50,I50,L50)=0,"Sem cotação",IF(ISNUMBER(S50),MIN(ROUND(P50,2),S50),ROUND(P50,2)))</f>
         <v>183.8</v>
       </c>
-      <c r="S50" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R50),D50*R50,0)</f>
+      <c r="U50" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R50),ISNUMBER(T50)),T50/R50-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V50" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T50),D50*T50,0)</f>
         <v>923962.6</v>
       </c>
     </row>
@@ -6974,40 +7902,40 @@
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>5027</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>164.75</v>
       </c>
       <c r="G51" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>223.2</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L51" s="12" t="n">
         <v>94.55</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N51" s="12" t="n">
         <f aca="false">IF(COUNT(F51,I51,L51)=0,"",MIN(F51,I51,L51))</f>
@@ -7025,12 +7953,23 @@
         <f aca="false">IF(COUNT(F51,I51,L51)=0,"",MAX(F51,I51,L51))</f>
         <v>223.2</v>
       </c>
-      <c r="R51" s="14" t="n">
-        <f aca="false">IF(COUNT(F51,I51,L51)=0,"Sem cotação",ROUND(P51,2))</f>
+      <c r="R51" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S51" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R51),ROUNDDOWN(R51*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T51" s="14" t="n">
+        <f aca="false">IF(COUNT(F51,I51,L51)=0,"Sem cotação",IF(ISNUMBER(S51),MIN(ROUND(P51,2),S51),ROUND(P51,2)))</f>
         <v>164.75</v>
       </c>
-      <c r="S51" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R51),D51*R51,0)</f>
+      <c r="U51" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R51),ISNUMBER(T51)),T51/R51-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V51" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T51),D51*T51,0)</f>
         <v>828198.25</v>
       </c>
     </row>
@@ -7039,40 +7978,40 @@
         <v>50</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>5491</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F52" s="12" t="n">
         <v>183.8</v>
       </c>
       <c r="G52" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>248.99</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="L52" s="12" t="n">
         <v>123.83</v>
       </c>
       <c r="M52" s="13" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="N52" s="12" t="n">
         <f aca="false">IF(COUNT(F52,I52,L52)=0,"",MIN(F52,I52,L52))</f>
@@ -7090,12 +8029,23 @@
         <f aca="false">IF(COUNT(F52,I52,L52)=0,"",MAX(F52,I52,L52))</f>
         <v>248.99</v>
       </c>
-      <c r="R52" s="14" t="n">
-        <f aca="false">IF(COUNT(F52,I52,L52)=0,"Sem cotação",ROUND(P52,2))</f>
+      <c r="R52" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S52" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R52),ROUNDDOWN(R52*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T52" s="14" t="n">
+        <f aca="false">IF(COUNT(F52,I52,L52)=0,"Sem cotação",IF(ISNUMBER(S52),MIN(ROUND(P52,2),S52),ROUND(P52,2)))</f>
         <v>183.8</v>
       </c>
-      <c r="S52" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R52),D52*R52,0)</f>
+      <c r="U52" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R52),ISNUMBER(T52)),T52/R52-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V52" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T52),D52*T52,0)</f>
         <v>1009245.8</v>
       </c>
     </row>
@@ -7104,40 +8054,40 @@
         <v>51</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>101.25</v>
       </c>
       <c r="G53" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>137.21</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="L53" s="12" t="n">
         <v>98</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N53" s="12" t="n">
         <f aca="false">IF(COUNT(F53,I53,L53)=0,"",MIN(F53,I53,L53))</f>
@@ -7155,12 +8105,23 @@
         <f aca="false">IF(COUNT(F53,I53,L53)=0,"",MAX(F53,I53,L53))</f>
         <v>137.21</v>
       </c>
-      <c r="R53" s="14" t="n">
-        <f aca="false">IF(COUNT(F53,I53,L53)=0,"Sem cotação",ROUND(P53,2))</f>
+      <c r="R53" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S53" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R53),ROUNDDOWN(R53*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T53" s="14" t="n">
+        <f aca="false">IF(COUNT(F53,I53,L53)=0,"Sem cotação",IF(ISNUMBER(S53),MIN(ROUND(P53,2),S53),ROUND(P53,2)))</f>
         <v>101.25</v>
       </c>
-      <c r="S53" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R53),D53*R53,0)</f>
+      <c r="U53" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R53),ISNUMBER(T53)),T53/R53-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V53" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T53),D53*T53,0)</f>
         <v>91631.25</v>
       </c>
     </row>
@@ -7169,40 +8130,40 @@
         <v>52</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>56.5</v>
       </c>
       <c r="G54" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>71.36</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K54" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>42.5</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N54" s="12" t="n">
         <f aca="false">IF(COUNT(F54,I54,L54)=0,"",MIN(F54,I54,L54))</f>
@@ -7220,12 +8181,23 @@
         <f aca="false">IF(COUNT(F54,I54,L54)=0,"",MAX(F54,I54,L54))</f>
         <v>71.36</v>
       </c>
-      <c r="R54" s="14" t="n">
-        <f aca="false">IF(COUNT(F54,I54,L54)=0,"Sem cotação",ROUND(P54,2))</f>
+      <c r="R54" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S54" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R54),ROUNDDOWN(R54*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T54" s="14" t="n">
+        <f aca="false">IF(COUNT(F54,I54,L54)=0,"Sem cotação",IF(ISNUMBER(S54),MIN(ROUND(P54,2),S54),ROUND(P54,2)))</f>
         <v>56.5</v>
       </c>
-      <c r="S54" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R54),D54*R54,0)</f>
+      <c r="U54" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R54),ISNUMBER(T54)),T54/R54-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V54" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T54),D54*T54,0)</f>
         <v>51132.5</v>
       </c>
     </row>
@@ -7234,40 +8206,40 @@
         <v>53</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>243.25</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>343.95</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L55" s="12" t="n">
         <v>329.77</v>
       </c>
       <c r="M55" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N55" s="12" t="n">
         <f aca="false">IF(COUNT(F55,I55,L55)=0,"",MIN(F55,I55,L55))</f>
@@ -7285,12 +8257,23 @@
         <f aca="false">IF(COUNT(F55,I55,L55)=0,"",MAX(F55,I55,L55))</f>
         <v>343.95</v>
       </c>
-      <c r="R55" s="14" t="n">
-        <f aca="false">IF(COUNT(F55,I55,L55)=0,"Sem cotação",ROUND(P55,2))</f>
+      <c r="R55" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S55" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R55),ROUNDDOWN(R55*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T55" s="14" t="n">
+        <f aca="false">IF(COUNT(F55,I55,L55)=0,"Sem cotação",IF(ISNUMBER(S55),MIN(ROUND(P55,2),S55),ROUND(P55,2)))</f>
         <v>329.77</v>
       </c>
-      <c r="S55" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R55),D55*R55,0)</f>
+      <c r="U55" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R55),ISNUMBER(T55)),T55/R55-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V55" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T55),D55*T55,0)</f>
         <v>298441.85</v>
       </c>
     </row>
@@ -7299,40 +8282,40 @@
         <v>54</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>179.75</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I56" s="12" t="n">
         <v>252.11</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K56" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="L56" s="12" t="n">
         <v>243.78</v>
       </c>
       <c r="M56" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="N56" s="12" t="n">
         <f aca="false">IF(COUNT(F56,I56,L56)=0,"",MIN(F56,I56,L56))</f>
@@ -7350,12 +8333,23 @@
         <f aca="false">IF(COUNT(F56,I56,L56)=0,"",MAX(F56,I56,L56))</f>
         <v>252.11</v>
       </c>
-      <c r="R56" s="14" t="n">
-        <f aca="false">IF(COUNT(F56,I56,L56)=0,"Sem cotação",ROUND(P56,2))</f>
+      <c r="R56" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S56" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R56),ROUNDDOWN(R56*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T56" s="14" t="n">
+        <f aca="false">IF(COUNT(F56,I56,L56)=0,"Sem cotação",IF(ISNUMBER(S56),MIN(ROUND(P56,2),S56),ROUND(P56,2)))</f>
         <v>243.78</v>
       </c>
-      <c r="S56" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R56),D56*R56,0)</f>
+      <c r="U56" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R56),ISNUMBER(T56)),T56/R56-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V56" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T56),D56*T56,0)</f>
         <v>220620.9</v>
       </c>
     </row>
@@ -7364,34 +8358,34 @@
         <v>55</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>86.7</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="10"/>
@@ -7411,12 +8405,23 @@
         <f aca="false">IF(COUNT(F57,I57,L57)=0,"",MAX(F57,I57,L57))</f>
         <v>86.7</v>
       </c>
-      <c r="R57" s="14" t="n">
-        <f aca="false">IF(COUNT(F57,I57,L57)=0,"Sem cotação",ROUND(P57,2))</f>
+      <c r="R57" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S57" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R57),ROUNDDOWN(R57*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T57" s="14" t="n">
+        <f aca="false">IF(COUNT(F57,I57,L57)=0,"Sem cotação",IF(ISNUMBER(S57),MIN(ROUND(P57,2),S57),ROUND(P57,2)))</f>
         <v>53.35</v>
       </c>
-      <c r="S57" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R57),D57*R57,0)</f>
+      <c r="U57" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R57),ISNUMBER(T57)),T57/R57-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V57" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T57),D57*T57,0)</f>
         <v>48281.75</v>
       </c>
     </row>
@@ -7425,26 +8430,26 @@
         <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="10"/>
       <c r="H58" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I58" s="12"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L58" s="12"/>
       <c r="M58" s="10"/>
@@ -7464,12 +8469,23 @@
         <f aca="false">IF(COUNT(F58,I58,L58)=0,"",MAX(F58,I58,L58))</f>
         <v/>
       </c>
-      <c r="R58" s="14" t="str">
-        <f aca="false">IF(COUNT(F58,I58,L58)=0,"Sem cotação",ROUND(P58,2))</f>
+      <c r="R58" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S58" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R58),ROUNDDOWN(R58*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T58" s="14" t="str">
+        <f aca="false">IF(COUNT(F58,I58,L58)=0,"Sem cotação",IF(ISNUMBER(S58),MIN(ROUND(P58,2),S58),ROUND(P58,2)))</f>
         <v>Sem cotação</v>
       </c>
-      <c r="S58" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R58),D58*R58,0)</f>
+      <c r="U58" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R58),ISNUMBER(T58)),T58/R58-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V58" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T58),D58*T58,0)</f>
         <v>0</v>
       </c>
     </row>
@@ -7478,40 +8494,40 @@
         <v>57</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>196</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>306.75</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>415.75</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K59" s="10" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="L59" s="12" t="n">
         <v>610.5</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N59" s="12" t="n">
         <f aca="false">IF(COUNT(F59,I59,L59)=0,"",MIN(F59,I59,L59))</f>
@@ -7529,12 +8545,23 @@
         <f aca="false">IF(COUNT(F59,I59,L59)=0,"",MAX(F59,I59,L59))</f>
         <v>610.5</v>
       </c>
-      <c r="R59" s="14" t="n">
-        <f aca="false">IF(COUNT(F59,I59,L59)=0,"Sem cotação",ROUND(P59,2))</f>
+      <c r="R59" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S59" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R59),ROUNDDOWN(R59*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T59" s="14" t="n">
+        <f aca="false">IF(COUNT(F59,I59,L59)=0,"Sem cotação",IF(ISNUMBER(S59),MIN(ROUND(P59,2),S59),ROUND(P59,2)))</f>
         <v>415.75</v>
       </c>
-      <c r="S59" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R59),D59*R59,0)</f>
+      <c r="U59" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R59),ISNUMBER(T59)),T59/R59-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V59" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T59),D59*T59,0)</f>
         <v>81487</v>
       </c>
     </row>
@@ -7543,40 +8570,40 @@
         <v>58</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>71.9</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>123.5</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>52</v>
       </c>
       <c r="M60" s="13" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="N60" s="12" t="n">
         <f aca="false">IF(COUNT(F60,I60,L60)=0,"",MIN(F60,I60,L60))</f>
@@ -7594,12 +8621,23 @@
         <f aca="false">IF(COUNT(F60,I60,L60)=0,"",MAX(F60,I60,L60))</f>
         <v>123.5</v>
       </c>
-      <c r="R60" s="14" t="n">
-        <f aca="false">IF(COUNT(F60,I60,L60)=0,"Sem cotação",ROUND(P60,2))</f>
+      <c r="R60" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S60" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R60),ROUNDDOWN(R60*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T60" s="14" t="n">
+        <f aca="false">IF(COUNT(F60,I60,L60)=0,"Sem cotação",IF(ISNUMBER(S60),MIN(ROUND(P60,2),S60),ROUND(P60,2)))</f>
         <v>71.9</v>
       </c>
-      <c r="S60" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R60),D60*R60,0)</f>
+      <c r="U60" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R60),ISNUMBER(T60)),T60/R60-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V60" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T60),D60*T60,0)</f>
         <v>65069.5</v>
       </c>
     </row>
@@ -7608,30 +8646,30 @@
         <v>59</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>53.8</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="I61" s="12"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L61" s="12"/>
       <c r="M61" s="10"/>
@@ -7651,12 +8689,23 @@
         <f aca="false">IF(COUNT(F61,I61,L61)=0,"",MAX(F61,I61,L61))</f>
         <v>53.8</v>
       </c>
-      <c r="R61" s="14" t="n">
-        <f aca="false">IF(COUNT(F61,I61,L61)=0,"Sem cotação",ROUND(P61,2))</f>
+      <c r="R61" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S61" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R61),ROUNDDOWN(R61*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T61" s="14" t="n">
+        <f aca="false">IF(COUNT(F61,I61,L61)=0,"Sem cotação",IF(ISNUMBER(S61),MIN(ROUND(P61,2),S61),ROUND(P61,2)))</f>
         <v>53.8</v>
       </c>
-      <c r="S61" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R61),D61*R61,0)</f>
+      <c r="U61" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R61),ISNUMBER(T61)),T61/R61-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V61" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T61),D61*T61,0)</f>
         <v>48689</v>
       </c>
     </row>
@@ -7665,40 +8714,40 @@
         <v>60</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>242.75</v>
       </c>
       <c r="G62" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I62" s="12" t="n">
         <v>331.82</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L62" s="12" t="n">
         <v>339.58</v>
       </c>
       <c r="M62" s="13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N62" s="12" t="n">
         <f aca="false">IF(COUNT(F62,I62,L62)=0,"",MIN(F62,I62,L62))</f>
@@ -7716,12 +8765,23 @@
         <f aca="false">IF(COUNT(F62,I62,L62)=0,"",MAX(F62,I62,L62))</f>
         <v>339.58</v>
       </c>
-      <c r="R62" s="14" t="n">
-        <f aca="false">IF(COUNT(F62,I62,L62)=0,"Sem cotação",ROUND(P62,2))</f>
+      <c r="R62" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S62" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R62),ROUNDDOWN(R62*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T62" s="14" t="n">
+        <f aca="false">IF(COUNT(F62,I62,L62)=0,"Sem cotação",IF(ISNUMBER(S62),MIN(ROUND(P62,2),S62),ROUND(P62,2)))</f>
         <v>331.82</v>
       </c>
-      <c r="S62" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R62),D62*R62,0)</f>
+      <c r="U62" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R62),ISNUMBER(T62)),T62/R62-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V62" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T62),D62*T62,0)</f>
         <v>300297.1</v>
       </c>
     </row>
@@ -7730,34 +8790,34 @@
         <v>61</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>120</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>105.75</v>
       </c>
       <c r="G63" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>143.39</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L63" s="12"/>
       <c r="M63" s="10"/>
@@ -7777,12 +8837,23 @@
         <f aca="false">IF(COUNT(F63,I63,L63)=0,"",MAX(F63,I63,L63))</f>
         <v>143.39</v>
       </c>
-      <c r="R63" s="14" t="n">
-        <f aca="false">IF(COUNT(F63,I63,L63)=0,"Sem cotação",ROUND(P63,2))</f>
+      <c r="R63" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S63" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R63),ROUNDDOWN(R63*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T63" s="14" t="n">
+        <f aca="false">IF(COUNT(F63,I63,L63)=0,"Sem cotação",IF(ISNUMBER(S63),MIN(ROUND(P63,2),S63),ROUND(P63,2)))</f>
         <v>124.57</v>
       </c>
-      <c r="S63" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R63),D63*R63,0)</f>
+      <c r="U63" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R63),ISNUMBER(T63)),T63/R63-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V63" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T63),D63*T63,0)</f>
         <v>14948.4</v>
       </c>
     </row>
@@ -7791,40 +8862,40 @@
         <v>62</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>135</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>178.25</v>
       </c>
       <c r="G64" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="I64" s="12" t="n">
         <v>240.59</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="L64" s="12" t="n">
         <v>259.88</v>
       </c>
       <c r="M64" s="13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N64" s="12" t="n">
         <f aca="false">IF(COUNT(F64,I64,L64)=0,"",MIN(F64,I64,L64))</f>
@@ -7842,12 +8913,23 @@
         <f aca="false">IF(COUNT(F64,I64,L64)=0,"",MAX(F64,I64,L64))</f>
         <v>259.88</v>
       </c>
-      <c r="R64" s="14" t="n">
-        <f aca="false">IF(COUNT(F64,I64,L64)=0,"Sem cotação",ROUND(P64,2))</f>
+      <c r="R64" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S64" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R64),ROUNDDOWN(R64*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T64" s="14" t="n">
+        <f aca="false">IF(COUNT(F64,I64,L64)=0,"Sem cotação",IF(ISNUMBER(S64),MIN(ROUND(P64,2),S64),ROUND(P64,2)))</f>
         <v>240.59</v>
       </c>
-      <c r="S64" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R64),D64*R64,0)</f>
+      <c r="U64" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R64),ISNUMBER(T64)),T64/R64-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V64" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T64),D64*T64,0)</f>
         <v>32479.65</v>
       </c>
     </row>
@@ -7856,40 +8938,40 @@
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>72</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>306.75</v>
       </c>
       <c r="G65" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>415.75</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="L65" s="12" t="n">
         <v>514.65</v>
       </c>
       <c r="M65" s="13" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="N65" s="12" t="n">
         <f aca="false">IF(COUNT(F65,I65,L65)=0,"",MIN(F65,I65,L65))</f>
@@ -7907,12 +8989,23 @@
         <f aca="false">IF(COUNT(F65,I65,L65)=0,"",MAX(F65,I65,L65))</f>
         <v>514.65</v>
       </c>
-      <c r="R65" s="14" t="n">
-        <f aca="false">IF(COUNT(F65,I65,L65)=0,"Sem cotação",ROUND(P65,2))</f>
+      <c r="R65" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S65" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R65),ROUNDDOWN(R65*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T65" s="14" t="n">
+        <f aca="false">IF(COUNT(F65,I65,L65)=0,"Sem cotação",IF(ISNUMBER(S65),MIN(ROUND(P65,2),S65),ROUND(P65,2)))</f>
         <v>415.75</v>
       </c>
-      <c r="S65" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R65),D65*R65,0)</f>
+      <c r="U65" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R65),ISNUMBER(T65)),T65/R65-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V65" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T65),D65*T65,0)</f>
         <v>29934</v>
       </c>
     </row>
@@ -7921,34 +9014,34 @@
         <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>72</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>72.5</v>
       </c>
       <c r="G66" s="13" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>156</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="L66" s="12"/>
       <c r="M66" s="10"/>
@@ -7968,44 +9061,58 @@
         <f aca="false">IF(COUNT(F66,I66,L66)=0,"",MAX(F66,I66,L66))</f>
         <v>156</v>
       </c>
-      <c r="R66" s="14" t="n">
-        <f aca="false">IF(COUNT(F66,I66,L66)=0,"Sem cotação",ROUND(P66,2))</f>
+      <c r="R66" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="S66" s="12" t="str">
+        <f aca="false">IF(ISNUMBER(R66),ROUNDDOWN(R66*0.96,2),"—")</f>
+        <v>—</v>
+      </c>
+      <c r="T66" s="14" t="n">
+        <f aca="false">IF(COUNT(F66,I66,L66)=0,"Sem cotação",IF(ISNUMBER(S66),MIN(ROUND(P66,2),S66),ROUND(P66,2)))</f>
         <v>114.25</v>
       </c>
-      <c r="S66" s="12" t="n">
-        <f aca="false">IF(ISNUMBER(R66),D66*R66,0)</f>
+      <c r="U66" s="15" t="str">
+        <f aca="false">IF(AND(ISNUMBER(R66),ISNUMBER(T66)),T66/R66-1,"—")</f>
+        <v>—</v>
+      </c>
+      <c r="V66" s="12" t="n">
+        <f aca="false">IF(ISNUMBER(T66),D66*T66,0)</f>
         <v>8226</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="15"/>
+      <c r="A67" s="16"/>
       <c r="B67" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C67" s="15"/>
-      <c r="D67" s="15"/>
-      <c r="E67" s="15"/>
-      <c r="F67" s="15"/>
-      <c r="G67" s="15"/>
-      <c r="H67" s="15"/>
-      <c r="I67" s="15"/>
-      <c r="J67" s="15"/>
-      <c r="K67" s="15"/>
-      <c r="L67" s="15"/>
-      <c r="M67" s="15"/>
-      <c r="N67" s="15"/>
-      <c r="O67" s="15"/>
-      <c r="P67" s="15"/>
-      <c r="Q67" s="15"/>
-      <c r="R67" s="15"/>
-      <c r="S67" s="7" t="n">
-        <f aca="false">SUM(S3:S66)</f>
+        <v>43</v>
+      </c>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16"/>
+      <c r="J67" s="16"/>
+      <c r="K67" s="16"/>
+      <c r="L67" s="16"/>
+      <c r="M67" s="16"/>
+      <c r="N67" s="16"/>
+      <c r="O67" s="16"/>
+      <c r="P67" s="16"/>
+      <c r="Q67" s="16"/>
+      <c r="R67" s="16"/>
+      <c r="S67" s="16"/>
+      <c r="T67" s="16"/>
+      <c r="U67" s="16"/>
+      <c r="V67" s="7" t="n">
+        <f aca="false">SUM(V3:V66)</f>
         <v>20579182.67</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:S1"/>
+    <mergeCell ref="A1:V1"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="https://ciminas.mg.gov.br"/>
@@ -8200,19 +9307,19 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="16" t="s">
-        <v>230</v>
+      <c r="A1" s="17" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8220,10 +9327,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="17" t="s">
-        <v>35</v>
+        <v>37</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8231,10 +9338,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>37</v>
+        <v>124</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8242,10 +9349,10 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>39</v>
+        <v>238</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8253,10 +9360,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>45</v>
+        <v>239</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8264,10 +9371,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8275,10 +9382,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>49</v>
+        <v>51</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8286,10 +9393,10 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>52</v>
+        <v>240</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8297,10 +9404,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>56</v>
+        <v>58</v>
+      </c>
+      <c r="C10" s="18" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8308,10 +9415,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8319,10 +9426,10 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>75</v>
+        <v>77</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8330,10 +9437,10 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>77</v>
+        <v>79</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8341,10 +9448,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>80</v>
+        <v>82</v>
+      </c>
+      <c r="C14" s="18" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8352,10 +9459,10 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>82</v>
+        <v>84</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8363,10 +9470,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>89</v>
+        <v>91</v>
+      </c>
+      <c r="C16" s="18" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8374,10 +9481,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>91</v>
+        <v>241</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8385,10 +9492,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>94</v>
+        <v>242</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8396,10 +9503,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>96</v>
+        <v>99</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8407,10 +9514,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="C20" s="17" t="s">
-        <v>98</v>
+        <v>243</v>
+      </c>
+      <c r="C20" s="18" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8418,10 +9525,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>103</v>
+        <v>244</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8429,10 +9536,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>111</v>
+        <v>245</v>
+      </c>
+      <c r="C22" s="18" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8440,10 +9547,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>122</v>
+        <v>125</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8451,10 +9558,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>124</v>
+        <v>127</v>
+      </c>
+      <c r="C24" s="18" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8462,10 +9569,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>128</v>
+        <v>131</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8473,10 +9580,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>134</v>
+        <v>137</v>
+      </c>
+      <c r="C26" s="18" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8484,10 +9591,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>139</v>
+        <v>166</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8495,10 +9602,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>144</v>
+        <v>147</v>
+      </c>
+      <c r="C28" s="18" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8506,10 +9613,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C29" s="17" t="s">
-        <v>148</v>
+        <v>151</v>
+      </c>
+      <c r="C29" s="18" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8517,10 +9624,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="C30" s="17" t="s">
-        <v>185</v>
+        <v>192</v>
+      </c>
+      <c r="C30" s="18" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8528,10 +9635,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="C31" s="17" t="s">
-        <v>191</v>
+        <v>194</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8539,10 +9646,10 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="C32" s="17" t="s">
-        <v>221</v>
+        <v>224</v>
+      </c>
+      <c r="C32" s="18" t="s">
+        <v>225</v>
       </c>
     </row>
   </sheetData>

--- a/Cotacao_Servicos_Saude_Unidade_Movel_2026-10-07.xlsx
+++ b/Cotacao_Servicos_Saude_Unidade_Movel_2026-10-07.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="252">
   <si>
     <t xml:space="preserve">COTAÇÃO DE PREÇOS DE REFERÊNCIA – SERVIÇOS ESPECIALIZADOS EM SAÚDE EM UNIDADES MÓVEIS (Carretas)</t>
   </si>
@@ -61,7 +61,7 @@
     <t xml:space="preserve">VALOR GLOBAL ESTIMADO</t>
   </si>
   <si>
-    <t xml:space="preserve">Metodologia: para cada item foram reunidos até três preços de contratações públicas (credenciamentos, pregões, atas de registro de preços, contratos e tabelas de credenciamento de órgãos e consórcios públicos), indicados nas colunas Fonte/Valor/Link de cada lote. O valor unitário de referência de cada item corresponde à MEDIANA dos preços coletados (Lei nº 14.133/2021, art. 23; IN SEGES/ME nº 65/2021, art. 6º), apresentada ao lado do menor preço, da média e do maior preço. Para os serviços com correspondente na Tabela de Serviços de Saúde executados em unidades móveis/itinerantes do ICISMEP (TSPS 2026), a mediana foi confrontada com o valor ICISMEP e limitada a 96% desse valor (redução mínima de 4%), como ajuste percentual para assegurar a vantajosidade da contratação. Itens marcados como 'análogo' usam procedimento equivalente quando não havia o item idêntico na fonte. Itens com menos de três preços estão sujeitos à justificativa prevista no art. 6º, §5º, da IN SEGES/ME nº 65/2021. Os quantitativos são estimativas do TR e não geram obrigação de execução.</t>
+    <t xml:space="preserve">Metodologia: para cada item foram reunidos até três preços de contratações públicas (credenciamentos, pregões, atas de registro de preços, contratos e tabelas de credenciamento de órgãos e consórcios públicos), indicados nas colunas Fonte/Valor/Link de cada lote. O valor unitário de referência de cada item corresponde à MEDIANA dos preços coletados (Lei nº 14.133/2021, art. 23; IN SEGES/ME nº 65/2021, art. 6º), apresentada ao lado do menor preço, da média e do maior preço. Para os serviços com correspondente na Tabela de Serviços de Saúde executados em unidades móveis/itinerantes do ICISMEP (TSPS 2026), a mediana foi confrontada com o valor ICISMEP (coluna de diferença percentual), demonstrando que o valor de referência resultante das cotações é inferior ao praticado por aquele consórcio para o mesmo serviço. Itens marcados como 'análogo' usam procedimento equivalente quando não havia o item idêntico na fonte. Itens com menos de três preços estão sujeitos à justificativa prevista no art. 6º, §5º, da IN SEGES/ME nº 65/2021. Os quantitativos são estimativas do TR e não geram obrigação de execução.</t>
   </si>
   <si>
     <t xml:space="preserve">LOTE 1 – EXAMES DE MAMOGRAFIA BILATERAL (unidade móvel)</t>
@@ -121,7 +121,7 @@
     <t xml:space="preserve">Valor ICISMEP – TSPS 2026, serviço em unidade móvel/itinerante (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">Limite: ICISMEP − 4% (R$)</t>
+    <t xml:space="preserve">Teto de verificação: ICISMEP − 4% (R$)</t>
   </si>
   <si>
     <t xml:space="preserve">Valor unit. referência (R$)</t>
@@ -265,492 +265,504 @@
     <t xml:space="preserve">https://www.sarapui.sp.gov.br/ata-registro-preco/page/1/download/839</t>
   </si>
   <si>
+    <t xml:space="preserve">CIM Expandida Sul – Tabela de valores vigente a partir de 01/01/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRASSONOGRAFIA TRANSVAGINAL (ENDOVAGINAL), em unidade móvel, com laudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FMS Quilombo/SC – Credenciamento 05/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://quilombo.sc.gov.br/uploads/sites/96/2025/04/5-EDITAL-DE-CREDENCIAMENTO-05-2025-exames-imagem.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISAMUSEP/PR – Tabela CISAMUSEP 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cisamusep.org.br/uploads/arquivoChamamento/TABELA-CISAMUSEP-2026.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRASSONOGRAFIA DE VIAS URINÁRIAS, em unidade móvel, com laudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISPARA/MG – Tabela Oficial de Consultas, Procedimentos e Serviços jan/2026 (aparelho urinário)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Lucas do Rio Verde/MT – Credenciamento 002/2026 (Inexig. 006/2026) (aparelho urinário)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRASSONOGRAFIA DE PRÓSTATA (VIA ABDOMINAL), em unidade móvel, com laudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECOCARDIOGRAMA TRANSTORÁCICO, em unidade móvel, com laudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fundação iNOVA Capixaba/ES – Pregão Eletrônico 068/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://inovacapixaba.es.gov.br/media/Editais/Licita%C3%A7%C3%A3o/Preg%C3%A3o/Edital_n%C2%BA_068_2025_2024_T5Q1Z_Servi%C3%A7os_M%C3%A9dicos_de_Ecocardiograma_REPUBL..pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Paragominas/PA – Pregão Eletrônico 9/2026-000027 (ecocardiograma transtorácico com doppler)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pncp.gov.br/app/editais/05193057000178/2026/124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sem correspondente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DENSITOMETRIA ÓSSEA, em unidade móvel, com laudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Foz do Jordão/PR – Credenciamento 008/2025 (corpo inteiro)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pncp.gov.br/pncp-api/v1/orgaos/01603719000180/compras/2025/95/arquivos/1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Praia Grande/SP – Tabela Oficial de Valores SESAP 2026 (coluna e/ou fêmur)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.praiagrande.sp.gov.br/arquivos/ChamadaPublica/46047.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRASSONOGRAFIA DE MAMAS, em unidade móvel, com laudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPIRN – Tabela de Serviços de Saúde (publ. 01/2025) (mamária bilateral)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://copirn.org.br/wp-content/uploads/2025/01/TABELA-DE-SERVICOS-DE-SAUDE-COPIRN-2.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISAMUSEP/PR – Tabela CISAMUSEP 2026 (mamária bilateral)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRASSONOGRAFIA DE AXILAS, em unidade móvel, com laudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FMS Vargem/SC – Pregão Eletrônico 005/2025 (análogo: partes moles)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.vargem.sc.gov.br/uploads/sites/94/2025/03/Edital-FMS-VRG-2025_013_PE_005_90023-Ultrassom.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COPIRN – Tabela de Serviços de Saúde (publ. 01/2025) (análogo: mamária bilateral)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISAMUSEP/PR – Tabela CISAMUSEP 2026 (análogo: mamária bilateral)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ULTRASSONOGRAFIA DE ARTICULAÇÕES/PARTES MOLES, em unidade móvel, com laudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISUM/MG – Credenciamento 2026 (ultrassonografias, sob demanda) (musculoesquelética/articulação)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://ia.mabus.com.br/licitacao/6466406/credenciamento-consorcio-intermunicipal-de-saude-uniao-da-mata-leopoldina-mg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOTE 4 – RESSONÂNCIA MAGNÉTICA (unidade móvel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RESSONÂNCIA MAGNÉTICA, em unidade móvel, valor único por exame independentemente da região anatômica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIS Circuito das Águas/MG – Credenciamento 04/2025 (Proc. 054/2025), carreta itinerante (carreta itinerante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Livramento de Nossa Senhora/BA – Chamamento Público 008/2026 (sem contraste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pncp.gov.br/app/editais/13674817000197/2026/64</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Iuiú/BA – Edital de Credenciamento 022/2026 (sem contraste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRASTE PARA RESSONÂNCIA MAGNÉTICA (meio de contraste, insumos e aplicação), vinculado ao item 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Sarapuí/SP – Ata de Registro de Preços (RM e USG) (diferença entre exame com e sem contraste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Livramento de Nossa Senhora/BA – Chamamento Público 008/2026 (diferença: R$ 700,00 com contraste − R$ 400,00 sem)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Iuiú/BA – Edital de Credenciamento 022/2026 (diferença: R$ 653,33 com contraste − R$ 543,33 sem)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LOTE 5 – ATENDIMENTOS E PROCEDIMENTOS ODONTOLÓGICOS (unidade móvel)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consulta especializada em ODONTOLOGIA/SAÚDE BUCAL, em unidade móvel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Senado Federal/SIS – Tabela própria de credenciamento – Odontologia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www12.senado.leg.br/institucional/sis/pdfs/tabela-odontologia-v2-nv.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPU/Plan-Assiste – Anexo V da Norma Complementar 50 (2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://planassiste.mpu.mp.br/o-plan-assiste/normas/normas-cpmplementares/anexo_v_nc_50.pdf/@@download/file/Anexo_V_NC_50.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atividade educativa em saúde bucal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Procedimento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.gov.br/mme/pt-br/assuntos/orgaos-vinculados/nuclep/plano-de-saude/orientacoes-ao-credenciado/TABELADEPROCEDIMENTOSODONTOLGICOS.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atividade educativa para pais e cuidadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025 (orientação de higiene bucal para pais/cuidadores)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (análogo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adequação do meio bucal (por arcada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC Saúde – Tabela de Reembolso Odontológico 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bcb.gov.br/content/acessoinformacao/bcsaude_docs/Tabela_de_Reembolsos_procedimentos_odontologicos_2026.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ajuste oclusal por desgaste seletivo (por sessão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicação de selante - Técnica invasiva (por elemento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC Saúde – Tabela de Procedimentos Odontológicos, Edital de Chamamento 2026 (selante por elemento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.bcb.gov.br/content/acessoinformacao/bcsaude_docs/Tabela_Procedimentos_Odontologicos_Edital_Chamamento_26.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicação tópica de flúor - por arcada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC Saúde – Tabela de Procedimentos Odontológicos, Edital de Chamamento 2026 (verniz fluoretado, 4 hemiarcadas)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capeamento pulpar direto (excluindo restauração final)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://fiosaude.org.br/wp-content/uploads/2025/04/tabela_Odontologica_Fiosaude_2025-2026.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Condicionamento em Odontologia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Controle de biofilme (por sessão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STJ/Pró-Ser – Tabela Odontológica 2025 (vigência a partir de 01/03/2025)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.stj.jus.br/sites/portalp/SiteAssets/Paginas/Sob-medida/Publico-interno/Pro-Ser/Informacoes-aos-credenciados/Tabela_Odontologica_PRECOS_2025.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coroa provisória (por elemento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STJ/Pró-Ser – Tabela Odontológica 2025 (vigência a partir de 01/03/2025) (sem pino)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Curativo de demora</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabelecimento de vínculo com paciente idoso independente (por sessão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025 (análogo: vínculo com idoso/cuidador)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabelecimento de vínculo com paciente idoso parcialmente dependente (por sessão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabelecimento de vínculo com paciente com necessidades especiais (por sessão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025 (análogo: idoso totalmente dependente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabelecimento de vínculo com paciente idoso totalmente dependente (por sessão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabelecimento de vínculo com paciente idoso, com cuidador de paciente idoso ou com cuidador de paciente com necessidades especiais</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estabilização do paciente por meio de contenção física e/ou mecânica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exodontia a retalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exodontia de dente decíduo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC Saúde – Tabela de Procedimentos Odontológicos, Edital de Chamamento 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exodontia de dente permanente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exodontia de permanente por indicação ortodôntica/protética</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (análogo: exodontia simples de permanente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPU/Plan-Assiste – Anexo V da Norma Complementar 50 (2026) (análogo: exodontia simples de permanente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exodontia de raiz residual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frenulotomia labial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (frenulectomia labial)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frenulotomia lingual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (frenulectomia lingual)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gengivectomia (por sextante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gengivoplastia (por sextante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Odontosecção / radilectomia / tunelização</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (amputação radicular)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orientação de higiene bucal para pais e/ou cuidadores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (atividade educativa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicação de cariostático - 1 sessão - duas arcadas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (por dente)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aplicação de selante de fóssulas e fissuras - por elemento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Profilaxia e polimento coronário</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prótese parcial fixa provisória (por elemento)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prótese parcial removível com grampos bilateral</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSUD – Resolução 034/2025 (17/04/2025) – Tabela de Prótese Odontológica (prótese parcial removível)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.consud.org/uploads/pagina/arquivos/RESOLUCAO-034-2025-TABELA-DE-PROTESE-ODONTOLOGICA-docx-2.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prótese parcial removível provisória em acrílico com ou sem grampos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prótese total (por arcada)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONSUD – Resolução 034/2025 (17/04/2025) – Tabela de Prótese Odontológica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radiografia periapical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TJDFT/Pró-Saúde – Tabela Odontológica Própria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.tjdft.jus.br/pro-saude/tabelas-proprias-do-pro-saude/tabela-propria-odontologica-ajuste-cynthia.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remoção de dente retido (incluso/impactado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BC Saúde – Tabela de Procedimentos Odontológicos, Edital de Chamamento 2026 (semi-incluso/impactado)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remoção de material obturador intracanal para retratamento endodôntico</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (análogo: retratamento unirradicular)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remoção de trabalhos protéticos - por elementos suportes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração atraumática - por elemento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (análogo: ionômero 1 face)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (análogo: ionômero)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração em ionômero de vidro – Classe I - 1 face</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração em ionômero de vidro – Classe II - 2 faces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração em ionômero de vidro – Classe II - 3 faces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração resina fotopolimerizável - Classe I - 1 face</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração resina fotopolimerizável Classe II - 2 faces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração resina fotopolimerizável Classe II - 3 faces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração resina fotopolimerizável Classe II - 4 faces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração resina fotopolimerizável Classe III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração resina fotopolimerizável Classe IV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração resina fotopolimerizável Classe V</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MPU/Plan-Assiste – Anexo V da Norma Complementar 50 (2026) (1 face)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restauração temporária/tratamento expectante</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retratamento endodôntico de canino e pré-molar birradiculares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retratamento endodôntico de incisivo/canino/pré-molar unirradiculares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sutura de ferida na região BMF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025 (análogo: excisão e sutura de lesão na boca)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sedação medicamentosa ambulatorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Retratamento endodôntico de molar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (multirradicular)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tratamento de alveolite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TRF3 – Tabela Odontológica Credenciados</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.trf3.jus.br/documentos/ubas/Odontologia/Credenc_pac_espec_vigencia_1_08_07.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tratamento de fluorose</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tratamento endodôntico de canino/pré-molar - birradiculares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TJDFT/Pró-Saúde – Tabela Odontológica Própria (pré-molar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tratamento endodôntico de dentes com rizogênese incompleta (por sessão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tratamento endodôntico de incisivo/canino/pré-molar - unirradicular</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TJDFT/Pró-Saúde – Tabela Odontológica Própria (incisivo ou canino)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tratamento endodôntico de molar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ulectomia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CONTRATAÇÕES E TABELAS PÚBLICAS DE REFERÊNCIA (links)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nº</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contratação / Documento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICISMEP/MG – TSPS jan/2026, atualização II (Unidade Móvel Saúde da Mulher)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SESA/ES – Credenciamento SRSV/NRA 001/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pref. Três Lagoas/MS – Edital de Credenciamento 002/2026</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pref. Lucas do Rio Verde/MT – Credenciamento 002/2026 (Inexig. 006/2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULTRASSONOGRAFIA TRANSVAGINAL (ENDOVAGINAL), em unidade móvel, com laudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FMS Quilombo/SC – Credenciamento 05/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://quilombo.sc.gov.br/uploads/sites/96/2025/04/5-EDITAL-DE-CREDENCIAMENTO-05-2025-exames-imagem.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Conselheiro Lafaiete/MG – Edital de Credenciamento 009/2025 (publ. 05/2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://conselheirolafaiete.mg.gov.br/v1/wp-content/uploads/2026/05/EDITAL-CRED-009.2025-EXAMES-DE-IMAGEM.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULTRASSONOGRAFIA DE VIAS URINÁRIAS, em unidade móvel, com laudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Lucas do Rio Verde/MT – Credenciamento 002/2026 (Inexig. 006/2026) (aparelho urinário)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Conselheiro Lafaiete/MG – Edital de Credenciamento 009/2025 (publ. 05/2026) (aparelho urinário)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULTRASSONOGRAFIA DE PRÓSTATA (VIA ABDOMINAL), em unidade móvel, com laudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECOCARDIOGRAMA TRANSTORÁCICO, em unidade móvel, com laudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fundação iNOVA Capixaba/ES – Pregão Eletrônico 068/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://inovacapixaba.es.gov.br/media/Editais/Licita%C3%A7%C3%A3o/Preg%C3%A3o/Edital_n%C2%BA_068_2025_2024_T5Q1Z_Servi%C3%A7os_M%C3%A9dicos_de_Ecocardiograma_REPUBL..pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Paragominas/PA – Pregão Eletrônico 9/2026-000027 (ecocardiograma transtorácico com doppler)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://pncp.gov.br/app/editais/05193057000178/2026/124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sem correspondente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DENSITOMETRIA ÓSSEA, em unidade móvel, com laudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Foz do Jordão/PR – Credenciamento 008/2025 (corpo inteiro)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://pncp.gov.br/pncp-api/v1/orgaos/01603719000180/compras/2025/95/arquivos/1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIM Expandida Sul – Tabela de valores vigente a partir de 01/01/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Praia Grande/SP – Tabela Oficial de Valores SESAP 2026 (coluna e/ou fêmur)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.praiagrande.sp.gov.br/arquivos/ChamadaPublica/46047.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULTRASSONOGRAFIA DE MAMAS, em unidade móvel, com laudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Lucas do Rio Verde/MT – Credenciamento 002/2026 (Inexig. 006/2026) (mamária bilateral)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULTRASSONOGRAFIA DE AXILAS, em unidade móvel, com laudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FMS Vargem/SC – Pregão Eletrônico 005/2025 (análogo: partes moles)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.vargem.sc.gov.br/uploads/sites/94/2025/03/Edital-FMS-VRG-2025_013_PE_005_90023-Ultrassom.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Lucas do Rio Verde/MT – Credenciamento 002/2026 (Inexig. 006/2026) (mamária bilateral incluindo axilas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIM Expandida Sul – Tabela de valores vigente a partir de 01/01/2026 (análogo: US mamária)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ULTRASSONOGRAFIA DE ARTICULAÇÕES/PARTES MOLES, em unidade móvel, com laudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOTE 4 – RESSONÂNCIA MAGNÉTICA (unidade móvel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RESSONÂNCIA MAGNÉTICA, em unidade móvel, valor único por exame independentemente da região anatômica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIS Circuito das Águas/MG – Credenciamento 04/2025 (Proc. 054/2025), carreta itinerante (carreta itinerante)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Livramento de Nossa Senhora/BA – Chamamento Público 008/2026 (sem contraste)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://pncp.gov.br/app/editais/13674817000197/2026/64</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Iuiú/BA – Edital de Credenciamento 022/2026 (sem contraste)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTRASTE PARA RESSONÂNCIA MAGNÉTICA (meio de contraste, insumos e aplicação), vinculado ao item 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicação</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Sarapuí/SP – Ata de Registro de Preços (RM e USG) (diferença entre exame com e sem contraste)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Livramento de Nossa Senhora/BA – Chamamento Público 008/2026 (diferença: R$ 700,00 com contraste − R$ 400,00 sem)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Iuiú/BA – Edital de Credenciamento 022/2026 (diferença: R$ 653,33 com contraste − R$ 543,33 sem)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LOTE 5 – ATENDIMENTOS E PROCEDIMENTOS ODONTOLÓGICOS (unidade móvel)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta especializada em ODONTOLOGIA/SAÚDE BUCAL, em unidade móvel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Senado Federal/SIS – Tabela própria de credenciamento – Odontologia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www12.senado.leg.br/institucional/sis/pdfs/tabela-odontologia-v2-nv.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPU/Plan-Assiste – Anexo V da Norma Complementar 50 (2026)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://planassiste.mpu.mp.br/o-plan-assiste/normas/normas-cpmplementares/anexo_v_nc_50.pdf/@@download/file/Anexo_V_NC_50.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atividade educativa em saúde bucal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Procedimento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.gov.br/mme/pt-br/assuntos/orgaos-vinculados/nuclep/plano-de-saude/orientacoes-ao-credenciado/TABELADEPROCEDIMENTOSODONTOLGICOS.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Atividade educativa para pais e cuidadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025 (orientação de higiene bucal para pais/cuidadores)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (análogo)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Adequação do meio bucal (por arcada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC Saúde – Tabela de Reembolso Odontológico 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.bcb.gov.br/content/acessoinformacao/bcsaude_docs/Tabela_de_Reembolsos_procedimentos_odontologicos_2026.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ajuste oclusal por desgaste seletivo (por sessão)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicação de selante - Técnica invasiva (por elemento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC Saúde – Tabela de Procedimentos Odontológicos, Edital de Chamamento 2026 (selante por elemento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.bcb.gov.br/content/acessoinformacao/bcsaude_docs/Tabela_Procedimentos_Odontologicos_Edital_Chamamento_26.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicação tópica de flúor - por arcada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC Saúde – Tabela de Procedimentos Odontológicos, Edital de Chamamento 2026 (verniz fluoretado, 4 hemiarcadas)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capeamento pulpar direto (excluindo restauração final)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://fiosaude.org.br/wp-content/uploads/2025/04/tabela_Odontologica_Fiosaude_2025-2026.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Condicionamento em Odontologia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Controle de biofilme (por sessão)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STJ/Pró-Ser – Tabela Odontológica 2025 (vigência a partir de 01/03/2025)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.stj.jus.br/sites/portalp/SiteAssets/Paginas/Sob-medida/Publico-interno/Pro-Ser/Informacoes-aos-credenciados/Tabela_Odontologica_PRECOS_2025.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coroa provisória (por elemento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">STJ/Pró-Ser – Tabela Odontológica 2025 (vigência a partir de 01/03/2025) (sem pino)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Curativo de demora</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estabelecimento de vínculo com paciente idoso independente (por sessão)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025 (análogo: vínculo com idoso/cuidador)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estabelecimento de vínculo com paciente idoso parcialmente dependente (por sessão)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estabelecimento de vínculo com paciente com necessidades especiais (por sessão)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025 (análogo: idoso totalmente dependente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estabelecimento de vínculo com paciente idoso totalmente dependente (por sessão)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estabelecimento de vínculo com paciente idoso, com cuidador de paciente idoso ou com cuidador de paciente com necessidades especiais</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estabilização do paciente por meio de contenção física e/ou mecânica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exodontia a retalho</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exodontia de dente decíduo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC Saúde – Tabela de Procedimentos Odontológicos, Edital de Chamamento 2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exodontia de dente permanente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exodontia de permanente por indicação ortodôntica/protética</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (análogo: exodontia simples de permanente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPU/Plan-Assiste – Anexo V da Norma Complementar 50 (2026) (análogo: exodontia simples de permanente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Exodontia de raiz residual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frenulotomia labial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (frenulectomia labial)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frenulotomia lingual</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (frenulectomia lingual)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gengivectomia (por sextante)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gengivoplastia (por sextante)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Odontosecção / radilectomia / tunelização</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (amputação radicular)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Orientação de higiene bucal para pais e/ou cuidadores</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (atividade educativa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicação de cariostático - 1 sessão - duas arcadas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (por dente)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aplicação de selante de fóssulas e fissuras - por elemento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Profilaxia e polimento coronário</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prótese parcial fixa provisória (por elemento)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prótese parcial removível com grampos bilateral</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONSUD – Resolução 034/2025 (17/04/2025) – Tabela de Prótese Odontológica (prótese parcial removível)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.consud.org/uploads/pagina/arquivos/RESOLUCAO-034-2025-TABELA-DE-PROTESE-ODONTOLOGICA-docx-2.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prótese parcial removível provisória em acrílico com ou sem grampos</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prótese total (por arcada)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONSUD – Resolução 034/2025 (17/04/2025) – Tabela de Prótese Odontológica</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Radiografia periapical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TJDFT/Pró-Saúde – Tabela Odontológica Própria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.tjdft.jus.br/pro-saude/tabelas-proprias-do-pro-saude/tabela-propria-odontologica-ajuste-cynthia.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remoção de dente retido (incluso/impactado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BC Saúde – Tabela de Procedimentos Odontológicos, Edital de Chamamento 2026 (semi-incluso/impactado)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remoção de material obturador intracanal para retratamento endodôntico</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (análogo: retratamento unirradicular)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remoção de trabalhos protéticos - por elementos suportes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração atraumática - por elemento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (análogo: ionômero 1 face)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NUCLEP/MME – Tabela de Procedimentos Odontológicos (análogo: ionômero)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração em ionômero de vidro – Classe I - 1 face</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração em ionômero de vidro – Classe II - 2 faces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração em ionômero de vidro – Classe II - 3 faces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração resina fotopolimerizável - Classe I - 1 face</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração resina fotopolimerizável Classe II - 2 faces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração resina fotopolimerizável Classe II - 3 faces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração resina fotopolimerizável Classe II - 4 faces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração resina fotopolimerizável Classe III</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração resina fotopolimerizável Classe IV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração resina fotopolimerizável Classe V</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MPU/Plan-Assiste – Anexo V da Norma Complementar 50 (2026) (1 face)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restauração temporária/tratamento expectante</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retratamento endodôntico de canino e pré-molar birradiculares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retratamento endodôntico de incisivo/canino/pré-molar unirradiculares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sutura de ferida na região BMF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CIMINAS/MG – Termo de Contrato 741/2025 (Credenciamento 040/2025 – Sistema Carretas da Saúde), 30/09/2025 (análogo: excisão e sutura de lesão na boca)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sedação medicamentosa ambulatorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Retratamento endodôntico de molar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FioSaúde – Tabela Odontológica, vigência 02/04/2025 a 31/03/2026 (multirradicular)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tratamento de alveolite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TRF3 – Tabela Odontológica Credenciados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.trf3.jus.br/documentos/ubas/Odontologia/Credenc_pac_espec_vigencia_1_08_07.pdf</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tratamento de fluorose</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tratamento endodôntico de canino/pré-molar - birradiculares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TJDFT/Pró-Saúde – Tabela Odontológica Própria (pré-molar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tratamento endodôntico de dentes com rizogênese incompleta (por sessão)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tratamento endodôntico de incisivo/canino/pré-molar - unirradicular</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TJDFT/Pró-Saúde – Tabela Odontológica Própria (incisivo ou canino)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tratamento endodôntico de molar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ulectomia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTRATAÇÕES E TABELAS PÚBLICAS DE REFERÊNCIA (links)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nº</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Contratação / Documento</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICISMEP/MG – TSPS jan/2026, atualização II (Unidade Móvel Saúde da Mulher)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SESA/ES – Credenciamento SRSV/NRA 001/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pref. Três Lagoas/MS – Edital de Credenciamento 002/2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pref. Paragominas/PA – Pregão Eletrônico 9/2026-000027</t>
   </si>
   <si>
@@ -760,7 +772,13 @@
     <t xml:space="preserve">Pref. Praia Grande/SP – Tabela Oficial de Valores SESAP 2026</t>
   </si>
   <si>
+    <t xml:space="preserve">COPIRN – Tabela de Serviços de Saúde (publ. 01/2025)</t>
+  </si>
+  <si>
     <t xml:space="preserve">FMS Vargem/SC – Pregão Eletrônico 005/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISUM/MG – Credenciamento 2026 (ultrassonografias, sob demanda)</t>
   </si>
   <si>
     <t xml:space="preserve">Pref. Livramento de Nossa Senhora/BA – Chamamento Público 008/2026</t>
@@ -1312,7 +1330,7 @@
       </c>
       <c r="B8" s="5" t="n">
         <f aca="false">'Lote 3 - Exames'!V12</f>
-        <v>17831513.1</v>
+        <v>17203713.65</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1339,7 +1357,7 @@
       </c>
       <c r="B11" s="7" t="n">
         <f aca="false">SUM(B6:B10)</f>
-        <v>77746165.82</v>
+        <v>77118366.37</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1576,7 +1594,7 @@
         <v>134.83</v>
       </c>
       <c r="T3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
         <v>133.41</v>
       </c>
       <c r="U3" s="15" t="n">
@@ -1823,7 +1841,7 @@
         <v>240</v>
       </c>
       <c r="T3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
         <v>92.48</v>
       </c>
       <c r="U3" s="15" t="n">
@@ -1899,7 +1917,7 @@
         <v>240</v>
       </c>
       <c r="T4" s="14" t="n">
-        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",IF(ISNUMBER(S4),MIN(ROUND(P4,2),S4),ROUND(P4,2)))</f>
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
         <v>97.63</v>
       </c>
       <c r="U4" s="15" t="n">
@@ -1975,7 +1993,7 @@
         <v>240</v>
       </c>
       <c r="T5" s="14" t="n">
-        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",IF(ISNUMBER(S5),MIN(ROUND(P5,2),S5),ROUND(P5,2)))</f>
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
         <v>100</v>
       </c>
       <c r="U5" s="15" t="n">
@@ -2051,7 +2069,7 @@
         <v>240</v>
       </c>
       <c r="T6" s="14" t="n">
-        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",IF(ISNUMBER(S6),MIN(ROUND(P6,2),S6),ROUND(P6,2)))</f>
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
         <v>114.97</v>
       </c>
       <c r="U6" s="15" t="n">
@@ -2127,7 +2145,7 @@
         <v>240</v>
       </c>
       <c r="T7" s="14" t="n">
-        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",IF(ISNUMBER(S7),MIN(ROUND(P7,2),S7),ROUND(P7,2)))</f>
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
         <v>96.5</v>
       </c>
       <c r="U7" s="15" t="n">
@@ -2203,7 +2221,7 @@
         <v>240</v>
       </c>
       <c r="T8" s="14" t="n">
-        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",IF(ISNUMBER(S8),MIN(ROUND(P8,2),S8),ROUND(P8,2)))</f>
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
         <v>103.2</v>
       </c>
       <c r="U8" s="15" t="n">
@@ -2279,7 +2297,7 @@
         <v>240</v>
       </c>
       <c r="T9" s="14" t="n">
-        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",IF(ISNUMBER(S9),MIN(ROUND(P9,2),S9),ROUND(P9,2)))</f>
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
         <v>101.56</v>
       </c>
       <c r="U9" s="15" t="n">
@@ -2355,7 +2373,7 @@
         <v>240</v>
       </c>
       <c r="T10" s="14" t="n">
-        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",IF(ISNUMBER(S10),MIN(ROUND(P10,2),S10),ROUND(P10,2)))</f>
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
         <v>115</v>
       </c>
       <c r="U10" s="15" t="n">
@@ -2431,7 +2449,7 @@
         <v>240</v>
       </c>
       <c r="T11" s="14" t="n">
-        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",IF(ISNUMBER(S11),MIN(ROUND(P11,2),S11),ROUND(P11,2)))</f>
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
         <v>90</v>
       </c>
       <c r="U11" s="15" t="n">
@@ -2507,7 +2525,7 @@
         <v>240</v>
       </c>
       <c r="T12" s="14" t="n">
-        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",IF(ISNUMBER(S12),MIN(ROUND(P12,2),S12),ROUND(P12,2)))</f>
+        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",ROUND(P12,2))</f>
         <v>105.87</v>
       </c>
       <c r="U12" s="15" t="n">
@@ -2583,7 +2601,7 @@
         <v>240</v>
       </c>
       <c r="T13" s="14" t="n">
-        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",IF(ISNUMBER(S13),MIN(ROUND(P13,2),S13),ROUND(P13,2)))</f>
+        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",ROUND(P13,2))</f>
         <v>106.1</v>
       </c>
       <c r="U13" s="15" t="n">
@@ -2659,7 +2677,7 @@
         <v>240</v>
       </c>
       <c r="T14" s="14" t="n">
-        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",IF(ISNUMBER(S14),MIN(ROUND(P14,2),S14),ROUND(P14,2)))</f>
+        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",ROUND(P14,2))</f>
         <v>97.63</v>
       </c>
       <c r="U14" s="15" t="n">
@@ -2735,7 +2753,7 @@
         <v>240</v>
       </c>
       <c r="T15" s="14" t="n">
-        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",IF(ISNUMBER(S15),MIN(ROUND(P15,2),S15),ROUND(P15,2)))</f>
+        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",ROUND(P15,2))</f>
         <v>90</v>
       </c>
       <c r="U15" s="15" t="n">
@@ -2811,7 +2829,7 @@
         <v>240</v>
       </c>
       <c r="T16" s="14" t="n">
-        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",IF(ISNUMBER(S16),MIN(ROUND(P16,2),S16),ROUND(P16,2)))</f>
+        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",ROUND(P16,2))</f>
         <v>91.96</v>
       </c>
       <c r="U16" s="15" t="n">
@@ -2887,7 +2905,7 @@
         <v>240</v>
       </c>
       <c r="T17" s="14" t="n">
-        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",IF(ISNUMBER(S17),MIN(ROUND(P17,2),S17),ROUND(P17,2)))</f>
+        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",ROUND(P17,2))</f>
         <v>95.2</v>
       </c>
       <c r="U17" s="15" t="n">
@@ -3135,38 +3153,38 @@
         <v>78</v>
       </c>
       <c r="H3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I3" s="12" t="n">
+        <v>83.54</v>
+      </c>
+      <c r="J3" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I3" s="12" t="n">
-        <v>136.91</v>
-      </c>
-      <c r="J3" s="13" t="s">
+      <c r="L3" s="12" t="n">
+        <v>60.72</v>
+      </c>
+      <c r="M3" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="K3" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="L3" s="12" t="n">
-        <v>83.54</v>
-      </c>
-      <c r="M3" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="N3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MIN(F3,I3,L3))</f>
-        <v>83.54</v>
+        <v>60.72</v>
       </c>
       <c r="O3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",AVERAGE(F3,I3,L3))</f>
-        <v>111.833333333333</v>
+        <v>86.4366666666667</v>
       </c>
       <c r="P3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MEDIAN(F3,I3,L3))</f>
-        <v>115.05</v>
+        <v>83.54</v>
       </c>
       <c r="Q3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MAX(F3,I3,L3))</f>
-        <v>136.91</v>
+        <v>115.05</v>
       </c>
       <c r="R3" s="12" t="n">
         <v>87.92</v>
@@ -3176,16 +3194,16 @@
         <v>84.4</v>
       </c>
       <c r="T3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
+        <v>83.54</v>
       </c>
       <c r="U3" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(R3),ISNUMBER(T3)),T3/R3-1,"—")</f>
-        <v>-0.0400363967242948</v>
+        <v>-0.0498180163785259</v>
       </c>
       <c r="V3" s="12" t="n">
         <f aca="false">IF(ISNUMBER(T3),D3*T3,0)</f>
-        <v>5536640</v>
+        <v>5480224</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3211,38 +3229,38 @@
         <v>83</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="I4" s="12" t="n">
-        <v>87.9</v>
+        <v>77.4</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>84</v>
       </c>
       <c r="L4" s="12" t="n">
-        <v>150</v>
+        <v>53.07</v>
       </c>
       <c r="M4" s="13" t="s">
         <v>85</v>
       </c>
       <c r="N4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MIN(F4,I4,L4))</f>
-        <v>87.9</v>
+        <v>53.07</v>
       </c>
       <c r="O4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",AVERAGE(F4,I4,L4))</f>
-        <v>109.3</v>
+        <v>73.49</v>
       </c>
       <c r="P4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MEDIAN(F4,I4,L4))</f>
-        <v>90</v>
+        <v>77.4</v>
       </c>
       <c r="Q4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MAX(F4,I4,L4))</f>
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="R4" s="12" t="n">
         <v>87.92</v>
@@ -3252,16 +3270,16 @@
         <v>84.4</v>
       </c>
       <c r="T4" s="14" t="n">
-        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",IF(ISNUMBER(S4),MIN(ROUND(P4,2),S4),ROUND(P4,2)))</f>
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
+        <v>77.4</v>
       </c>
       <c r="U4" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(R4),ISNUMBER(T4)),T4/R4-1,"—")</f>
-        <v>-0.0400363967242948</v>
+        <v>-0.119654231119199</v>
       </c>
       <c r="V4" s="12" t="n">
         <f aca="false">IF(ISNUMBER(T4),D4*T4,0)</f>
-        <v>882824</v>
+        <v>809604</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3290,19 +3308,19 @@
         <v>87</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>89.72</v>
+        <v>81.87</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="K5" s="10" t="s">
         <v>88</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>135</v>
+        <v>89.72</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="N5" s="12" t="n">
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MIN(F5,I5,L5))</f>
@@ -3310,15 +3328,15 @@
       </c>
       <c r="O5" s="12" t="n">
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",AVERAGE(F5,I5,L5))</f>
-        <v>95.8366666666667</v>
+        <v>78.1266666666667</v>
       </c>
       <c r="P5" s="12" t="n">
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MEDIAN(F5,I5,L5))</f>
-        <v>89.72</v>
+        <v>81.87</v>
       </c>
       <c r="Q5" s="12" t="n">
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MAX(F5,I5,L5))</f>
-        <v>135</v>
+        <v>89.72</v>
       </c>
       <c r="R5" s="12" t="n">
         <v>87.92</v>
@@ -3328,16 +3346,16 @@
         <v>84.4</v>
       </c>
       <c r="T5" s="14" t="n">
-        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",IF(ISNUMBER(S5),MIN(ROUND(P5,2),S5),ROUND(P5,2)))</f>
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
+        <v>81.87</v>
       </c>
       <c r="U5" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(R5),ISNUMBER(T5)),T5/R5-1,"—")</f>
-        <v>-0.0400363967242948</v>
+        <v>-0.0688125568698816</v>
       </c>
       <c r="V5" s="12" t="n">
         <f aca="false">IF(ISNUMBER(T5),D5*T5,0)</f>
-        <v>1799830</v>
+        <v>1745877.75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3345,7 +3363,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>36</v>
@@ -3363,34 +3381,34 @@
         <v>83</v>
       </c>
       <c r="H6" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="I6" s="12" t="n">
+        <v>71.28</v>
+      </c>
+      <c r="J6" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="K6" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I6" s="12" t="n">
-        <v>85.72</v>
-      </c>
-      <c r="J6" s="13" t="s">
+      <c r="L6" s="12" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="M6" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="K6" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="L6" s="12" t="n">
-        <v>71.28</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>69</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MIN(F6,I6,L6))</f>
-        <v>71.28</v>
+        <v>44.28</v>
       </c>
       <c r="O6" s="12" t="n">
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",AVERAGE(F6,I6,L6))</f>
-        <v>82.3333333333333</v>
+        <v>68.52</v>
       </c>
       <c r="P6" s="12" t="n">
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MEDIAN(F6,I6,L6))</f>
-        <v>85.72</v>
+        <v>71.28</v>
       </c>
       <c r="Q6" s="12" t="n">
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MAX(F6,I6,L6))</f>
@@ -3404,16 +3422,16 @@
         <v>84.4</v>
       </c>
       <c r="T6" s="14" t="n">
-        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",IF(ISNUMBER(S6),MIN(ROUND(P6,2),S6),ROUND(P6,2)))</f>
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
+        <v>71.28</v>
       </c>
       <c r="U6" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(R6),ISNUMBER(T6)),T6/R6-1,"—")</f>
-        <v>-0.0400363967242948</v>
+        <v>-0.18926296633303</v>
       </c>
       <c r="V6" s="12" t="n">
         <f aca="false">IF(ISNUMBER(T6),D6*T6,0)</f>
-        <v>882824</v>
+        <v>745588.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3421,7 +3439,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C7" s="10" t="s">
         <v>36</v>
@@ -3430,22 +3448,22 @@
         <v>14885</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>211.26</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>244.92</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K7" s="10" t="s">
         <v>49</v>
@@ -3473,14 +3491,14 @@
         <v>244.92</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S7" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R7),ROUNDDOWN(R7*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T7" s="14" t="n">
-        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",IF(ISNUMBER(S7),MIN(ROUND(P7,2),S7),ROUND(P7,2)))</f>
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
         <v>211.26</v>
       </c>
       <c r="U7" s="15" t="str">
@@ -3497,7 +3515,7 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C8" s="10" t="s">
         <v>36</v>
@@ -3506,31 +3524,31 @@
         <v>3174</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>187.17</v>
       </c>
       <c r="G8" s="13" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="I8" s="12" t="n">
         <v>64.37</v>
       </c>
       <c r="J8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>100</v>
-      </c>
-      <c r="K8" s="10" t="s">
-        <v>101</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>75</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N8" s="12" t="n">
         <f aca="false">IF(COUNT(F8,I8,L8)=0,"",MIN(F8,I8,L8))</f>
@@ -3549,14 +3567,14 @@
         <v>187.17</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S8" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R8),ROUNDDOWN(R8*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T8" s="14" t="n">
-        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",IF(ISNUMBER(S8),MIN(ROUND(P8,2),S8),ROUND(P8,2)))</f>
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
         <v>75</v>
       </c>
       <c r="U8" s="15" t="str">
@@ -3573,7 +3591,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>36</v>
@@ -3591,38 +3609,38 @@
         <v>83</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" s="12" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="J9" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="I9" s="12" t="n">
-        <v>90.74</v>
-      </c>
-      <c r="J9" s="13" t="s">
-        <v>80</v>
-      </c>
       <c r="K9" s="10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>44.28</v>
+        <v>47.76</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="N9" s="12" t="n">
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MIN(F9,I9,L9))</f>
-        <v>44.28</v>
+        <v>47.76</v>
       </c>
       <c r="O9" s="12" t="n">
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",AVERAGE(F9,I9,L9))</f>
-        <v>75.0066666666667</v>
+        <v>71.5466666666667</v>
       </c>
       <c r="P9" s="12" t="n">
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MEDIAN(F9,I9,L9))</f>
-        <v>90</v>
+        <v>76.88</v>
       </c>
       <c r="Q9" s="12" t="n">
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MAX(F9,I9,L9))</f>
-        <v>90.74</v>
+        <v>90</v>
       </c>
       <c r="R9" s="12" t="n">
         <v>87.92</v>
@@ -3632,24 +3650,24 @@
         <v>84.4</v>
       </c>
       <c r="T9" s="14" t="n">
-        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",IF(ISNUMBER(S9),MIN(ROUND(P9,2),S9),ROUND(P9,2)))</f>
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
+        <v>76.88</v>
       </c>
       <c r="U9" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(R9),ISNUMBER(T9)),T9/R9-1,"—")</f>
-        <v>-0.0400363967242948</v>
+        <v>-0.125568698817107</v>
       </c>
       <c r="V9" s="12" t="n">
         <f aca="false">IF(ISNUMBER(T9),D9*T9,0)</f>
-        <v>381910</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>347882</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="10" t="s">
         <v>36</v>
@@ -3658,43 +3676,43 @@
         <v>4525</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>100.74</v>
       </c>
       <c r="G10" s="13" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>90.74</v>
+        <v>76.88</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>80</v>
+        <v>104</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>44.28</v>
+        <v>47.76</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="N10" s="12" t="n">
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MIN(F10,I10,L10))</f>
-        <v>44.28</v>
+        <v>47.76</v>
       </c>
       <c r="O10" s="12" t="n">
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",AVERAGE(F10,I10,L10))</f>
-        <v>78.5866666666667</v>
+        <v>75.1266666666667</v>
       </c>
       <c r="P10" s="12" t="n">
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MEDIAN(F10,I10,L10))</f>
-        <v>90.74</v>
+        <v>76.88</v>
       </c>
       <c r="Q10" s="12" t="n">
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MAX(F10,I10,L10))</f>
@@ -3708,24 +3726,24 @@
         <v>84.4</v>
       </c>
       <c r="T10" s="14" t="n">
-        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",IF(ISNUMBER(S10),MIN(ROUND(P10,2),S10),ROUND(P10,2)))</f>
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
+        <v>76.88</v>
       </c>
       <c r="U10" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(R10),ISNUMBER(T10)),T10/R10-1,"—")</f>
-        <v>-0.0400363967242948</v>
+        <v>-0.125568698817107</v>
       </c>
       <c r="V10" s="12" t="n">
         <f aca="false">IF(ISNUMBER(T10),D10*T10,0)</f>
-        <v>381910</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>347882</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="10" t="s">
         <v>36</v>
@@ -3743,38 +3761,38 @@
         <v>83</v>
       </c>
       <c r="H11" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>80</v>
+      </c>
+      <c r="J11" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="K11" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="I11" s="12" t="n">
-        <v>86.98</v>
-      </c>
-      <c r="J11" s="13" t="s">
+      <c r="L11" s="12" t="n">
+        <v>54.87</v>
+      </c>
+      <c r="M11" s="13" t="s">
         <v>80</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>155</v>
-      </c>
-      <c r="M11" s="13" t="s">
-        <v>85</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MIN(F11,I11,L11))</f>
-        <v>86.98</v>
+        <v>54.87</v>
       </c>
       <c r="O11" s="12" t="n">
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",AVERAGE(F11,I11,L11))</f>
-        <v>112.43</v>
+        <v>76.7266666666667</v>
       </c>
       <c r="P11" s="12" t="n">
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MEDIAN(F11,I11,L11))</f>
-        <v>95.31</v>
+        <v>80</v>
       </c>
       <c r="Q11" s="12" t="n">
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MAX(F11,I11,L11))</f>
-        <v>155</v>
+        <v>95.31</v>
       </c>
       <c r="R11" s="12" t="n">
         <v>87.92</v>
@@ -3784,16 +3802,16 @@
         <v>84.4</v>
       </c>
       <c r="T11" s="14" t="n">
-        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",IF(ISNUMBER(S11),MIN(ROUND(P11,2),S11),ROUND(P11,2)))</f>
-        <v>84.4</v>
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
+        <v>80</v>
       </c>
       <c r="U11" s="15" t="n">
         <f aca="false">IF(AND(ISNUMBER(R11),ISNUMBER(T11)),T11/R11-1,"—")</f>
-        <v>-0.0400363967242948</v>
+        <v>-0.0900818926296634</v>
       </c>
       <c r="V11" s="12" t="n">
         <f aca="false">IF(ISNUMBER(T11),D11*T11,0)</f>
-        <v>4582920</v>
+        <v>4344000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3822,7 +3840,7 @@
       <c r="U12" s="16"/>
       <c r="V12" s="7" t="n">
         <f aca="false">SUM(V3:V11)</f>
-        <v>17831513.1</v>
+        <v>17203713.65</v>
       </c>
     </row>
   </sheetData>
@@ -3831,17 +3849,17 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G3" r:id="rId1" display="https://www.sarapui.sp.gov.br/ata-registro-preco/page/1/download/839"/>
-    <hyperlink ref="J3" r:id="rId2" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
-    <hyperlink ref="M3" r:id="rId3" display="https://www.cispara.mg.gov.br/transparencia/tabela-oficial-de-procedimentos/tabela-oficial-de-procedimentos-2026/543-01-tabela-oficial-de-consultas-procedimentos-e-servicos-janeiro-de-2026/file"/>
+    <hyperlink ref="J3" r:id="rId2" display="https://www.cispara.mg.gov.br/transparencia/tabela-oficial-de-procedimentos/tabela-oficial-de-procedimentos-2026/543-01-tabela-oficial-de-consultas-procedimentos-e-servicos-janeiro-de-2026/file"/>
+    <hyperlink ref="M3" r:id="rId3" display="https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file"/>
     <hyperlink ref="G4" r:id="rId4" display="https://quilombo.sc.gov.br/uploads/sites/96/2025/04/5-EDITAL-DE-CREDENCIAMENTO-05-2025-exames-imagem.pdf"/>
-    <hyperlink ref="J4" r:id="rId5" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
-    <hyperlink ref="M4" r:id="rId6" display="https://conselheirolafaiete.mg.gov.br/v1/wp-content/uploads/2026/05/EDITAL-CRED-009.2025-EXAMES-DE-IMAGEM.pdf"/>
+    <hyperlink ref="J4" r:id="rId5" display="https://www.cispara.mg.gov.br/transparencia/tabela-oficial-de-procedimentos/tabela-oficial-de-procedimentos-2026/543-01-tabela-oficial-de-consultas-procedimentos-e-servicos-janeiro-de-2026/file"/>
+    <hyperlink ref="M4" r:id="rId6" display="https://www.cisamusep.org.br/uploads/arquivoChamamento/TABELA-CISAMUSEP-2026.pdf"/>
     <hyperlink ref="G5" r:id="rId7" display="https://www.sarapui.sp.gov.br/ata-registro-preco/page/1/download/839"/>
-    <hyperlink ref="J5" r:id="rId8" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
-    <hyperlink ref="M5" r:id="rId9" display="https://conselheirolafaiete.mg.gov.br/v1/wp-content/uploads/2026/05/EDITAL-CRED-009.2025-EXAMES-DE-IMAGEM.pdf"/>
+    <hyperlink ref="J5" r:id="rId8" display="https://www.cispara.mg.gov.br/transparencia/tabela-oficial-de-procedimentos/tabela-oficial-de-procedimentos-2026/543-01-tabela-oficial-de-consultas-procedimentos-e-servicos-janeiro-de-2026/file"/>
+    <hyperlink ref="M5" r:id="rId9" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
     <hyperlink ref="G6" r:id="rId10" display="https://quilombo.sc.gov.br/uploads/sites/96/2025/04/5-EDITAL-DE-CREDENCIAMENTO-05-2025-exames-imagem.pdf"/>
-    <hyperlink ref="J6" r:id="rId11" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
-    <hyperlink ref="M6" r:id="rId12" display="https://www.cispara.mg.gov.br/transparencia/tabela-oficial-de-procedimentos/tabela-oficial-de-procedimentos-2026/543-01-tabela-oficial-de-consultas-procedimentos-e-servicos-janeiro-de-2026/file"/>
+    <hyperlink ref="J6" r:id="rId11" display="https://www.cispara.mg.gov.br/transparencia/tabela-oficial-de-procedimentos/tabela-oficial-de-procedimentos-2026/543-01-tabela-oficial-de-consultas-procedimentos-e-servicos-janeiro-de-2026/file"/>
+    <hyperlink ref="M6" r:id="rId12" display="https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file"/>
     <hyperlink ref="G7" r:id="rId13" display="https://inovacapixaba.es.gov.br/media/Editais/Licita%C3%A7%C3%A3o/Preg%C3%A3o/Edital_n%C2%BA_068_2025_2024_T5Q1Z_Servi%C3%A7os_M%C3%A9dicos_de_Ecocardiograma_REPUBL..pdf"/>
     <hyperlink ref="J7" r:id="rId14" display="https://pncp.gov.br/app/editais/05193057000178/2026/124"/>
     <hyperlink ref="M7" r:id="rId15" display="https://www.cisame.mg.gov.br/compliance/tabela-de-precos-e-servicos/"/>
@@ -3849,14 +3867,14 @@
     <hyperlink ref="J8" r:id="rId17" display="https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file"/>
     <hyperlink ref="M8" r:id="rId18" display="https://www.praiagrande.sp.gov.br/arquivos/ChamadaPublica/46047.pdf"/>
     <hyperlink ref="G9" r:id="rId19" display="https://quilombo.sc.gov.br/uploads/sites/96/2025/04/5-EDITAL-DE-CREDENCIAMENTO-05-2025-exames-imagem.pdf"/>
-    <hyperlink ref="J9" r:id="rId20" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
-    <hyperlink ref="M9" r:id="rId21" display="https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file"/>
+    <hyperlink ref="J9" r:id="rId20" display="https://copirn.org.br/wp-content/uploads/2025/01/TABELA-DE-SERVICOS-DE-SAUDE-COPIRN-2.pdf"/>
+    <hyperlink ref="M9" r:id="rId21" display="https://www.cisamusep.org.br/uploads/arquivoChamamento/TABELA-CISAMUSEP-2026.pdf"/>
     <hyperlink ref="G10" r:id="rId22" display="https://www.vargem.sc.gov.br/uploads/sites/94/2025/03/Edital-FMS-VRG-2025_013_PE_005_90023-Ultrassom.pdf"/>
-    <hyperlink ref="J10" r:id="rId23" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
-    <hyperlink ref="M10" r:id="rId24" display="https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file"/>
+    <hyperlink ref="J10" r:id="rId23" display="https://copirn.org.br/wp-content/uploads/2025/01/TABELA-DE-SERVICOS-DE-SAUDE-COPIRN-2.pdf"/>
+    <hyperlink ref="M10" r:id="rId24" display="https://www.cisamusep.org.br/uploads/arquivoChamamento/TABELA-CISAMUSEP-2026.pdf"/>
     <hyperlink ref="G11" r:id="rId25" display="https://quilombo.sc.gov.br/uploads/sites/96/2025/04/5-EDITAL-DE-CREDENCIAMENTO-05-2025-exames-imagem.pdf"/>
-    <hyperlink ref="J11" r:id="rId26" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
-    <hyperlink ref="M11" r:id="rId27" display="https://conselheirolafaiete.mg.gov.br/v1/wp-content/uploads/2026/05/EDITAL-CRED-009.2025-EXAMES-DE-IMAGEM.pdf"/>
+    <hyperlink ref="J11" r:id="rId26" display="https://ia.mabus.com.br/licitacao/6466406/credenciamento-consorcio-intermunicipal-de-saude-uniao-da-mata-leopoldina-mg"/>
+    <hyperlink ref="M11" r:id="rId27" display="https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3899,7 +3917,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3996,7 +4014,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>36</v>
@@ -4005,7 +4023,7 @@
         <v>27150</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>420</v>
@@ -4014,16 +4032,16 @@
         <v>38</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="I3" s="12" t="n">
         <v>400</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="L3" s="12" t="n">
         <v>543.33</v>
@@ -4048,14 +4066,14 @@
         <v>543.33</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S3" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R3),ROUNDDOWN(R3*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
         <v>420</v>
       </c>
       <c r="U3" s="15" t="str">
@@ -4072,16 +4090,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>4073</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="F4" s="12" t="n">
         <v>77</v>
@@ -4090,16 +4108,16 @@
         <v>78</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I4" s="12" t="n">
         <v>300</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="L4" s="12" t="n">
         <v>110</v>
@@ -4124,14 +4142,14 @@
         <v>300</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S4" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R4),ROUNDDOWN(R4*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T4" s="14" t="n">
-        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",IF(ISNUMBER(S4),MIN(ROUND(P4,2),S4),ROUND(P4,2)))</f>
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
         <v>110</v>
       </c>
       <c r="U4" s="15" t="str">
@@ -4225,7 +4243,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4322,7 +4340,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C3" s="10" t="s">
         <v>46</v>
@@ -4331,7 +4349,7 @@
         <v>90118</v>
       </c>
       <c r="E3" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F3" s="12" t="n">
         <v>66.5</v>
@@ -4340,22 +4358,22 @@
         <v>40</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I3" s="12" t="n">
         <v>90.1</v>
       </c>
       <c r="J3" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K3" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L3" s="12" t="n">
         <v>78.4</v>
       </c>
       <c r="M3" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N3" s="12" t="n">
         <f aca="false">IF(COUNT(F3,I3,L3)=0,"",MIN(F3,I3,L3))</f>
@@ -4374,14 +4392,14 @@
         <v>90.1</v>
       </c>
       <c r="R3" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S3" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R3),ROUNDDOWN(R3*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T3" s="14" t="n">
-        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",IF(ISNUMBER(S3),MIN(ROUND(P3,2),S3),ROUND(P3,2)))</f>
+        <f aca="false">IF(COUNT(F3,I3,L3)=0,"Sem cotação",ROUND(P3,2))</f>
         <v>78.4</v>
       </c>
       <c r="U3" s="15" t="str">
@@ -4398,16 +4416,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D4" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F4" s="12" t="n">
         <v>53.8</v>
@@ -4416,22 +4434,22 @@
         <v>40</v>
       </c>
       <c r="H4" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I4" s="12" t="n">
         <v>76.05</v>
       </c>
       <c r="J4" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K4" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L4" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M4" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N4" s="12" t="n">
         <f aca="false">IF(COUNT(F4,I4,L4)=0,"",MIN(F4,I4,L4))</f>
@@ -4450,14 +4468,14 @@
         <v>76.05</v>
       </c>
       <c r="R4" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S4" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R4),ROUNDDOWN(R4*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T4" s="14" t="n">
-        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",IF(ISNUMBER(S4),MIN(ROUND(P4,2),S4),ROUND(P4,2)))</f>
+        <f aca="false">IF(COUNT(F4,I4,L4)=0,"Sem cotação",ROUND(P4,2))</f>
         <v>53.8</v>
       </c>
       <c r="U4" s="15" t="str">
@@ -4474,16 +4492,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>133</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>130</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>53.8</v>
@@ -4492,22 +4510,22 @@
         <v>40</v>
       </c>
       <c r="H5" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I5" s="12" t="n">
         <v>76.05</v>
       </c>
       <c r="J5" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K5" s="10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="L5" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M5" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N5" s="12" t="n">
         <f aca="false">IF(COUNT(F5,I5,L5)=0,"",MIN(F5,I5,L5))</f>
@@ -4526,14 +4544,14 @@
         <v>76.05</v>
       </c>
       <c r="R5" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S5" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R5),ROUNDDOWN(R5*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T5" s="14" t="n">
-        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",IF(ISNUMBER(S5),MIN(ROUND(P5,2),S5),ROUND(P5,2)))</f>
+        <f aca="false">IF(COUNT(F5,I5,L5)=0,"Sem cotação",ROUND(P5,2))</f>
         <v>53.8</v>
       </c>
       <c r="U5" s="15" t="str">
@@ -4550,16 +4568,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D6" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>69.5</v>
@@ -4568,22 +4586,22 @@
         <v>40</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I6" s="12" t="n">
         <v>98.27</v>
       </c>
       <c r="J6" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K6" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L6" s="12" t="n">
         <v>83.97</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="N6" s="12" t="n">
         <f aca="false">IF(COUNT(F6,I6,L6)=0,"",MIN(F6,I6,L6))</f>
@@ -4602,14 +4620,14 @@
         <v>98.27</v>
       </c>
       <c r="R6" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S6" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R6),ROUNDDOWN(R6*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T6" s="14" t="n">
-        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",IF(ISNUMBER(S6),MIN(ROUND(P6,2),S6),ROUND(P6,2)))</f>
+        <f aca="false">IF(COUNT(F6,I6,L6)=0,"Sem cotação",ROUND(P6,2))</f>
         <v>83.97</v>
       </c>
       <c r="U6" s="15" t="str">
@@ -4626,16 +4644,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D7" s="11" t="n">
         <v>1376</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>82.2</v>
@@ -4644,16 +4662,16 @@
         <v>40</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I7" s="12" t="n">
         <v>116.21</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K7" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L7" s="12"/>
       <c r="M7" s="10"/>
@@ -4674,14 +4692,14 @@
         <v>116.21</v>
       </c>
       <c r="R7" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S7" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R7),ROUNDDOWN(R7*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T7" s="14" t="n">
-        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",IF(ISNUMBER(S7),MIN(ROUND(P7,2),S7),ROUND(P7,2)))</f>
+        <f aca="false">IF(COUNT(F7,I7,L7)=0,"Sem cotação",ROUND(P7,2))</f>
         <v>99.21</v>
       </c>
       <c r="U7" s="15" t="str">
@@ -4698,16 +4716,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D8" s="11" t="n">
         <v>1282</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F8" s="12" t="n">
         <v>80.7</v>
@@ -4716,22 +4734,22 @@
         <v>40</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I8" s="12" t="n">
         <v>109.36</v>
       </c>
       <c r="J8" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K8" s="10" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L8" s="12" t="n">
         <v>43.9</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N8" s="12" t="n">
         <f aca="false">IF(COUNT(F8,I8,L8)=0,"",MIN(F8,I8,L8))</f>
@@ -4750,14 +4768,14 @@
         <v>109.36</v>
       </c>
       <c r="R8" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S8" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R8),ROUNDDOWN(R8*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T8" s="14" t="n">
-        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",IF(ISNUMBER(S8),MIN(ROUND(P8,2),S8),ROUND(P8,2)))</f>
+        <f aca="false">IF(COUNT(F8,I8,L8)=0,"Sem cotação",ROUND(P8,2))</f>
         <v>80.7</v>
       </c>
       <c r="U8" s="15" t="str">
@@ -4774,16 +4792,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>14903</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>66.5</v>
@@ -4792,22 +4810,22 @@
         <v>40</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I9" s="12" t="n">
         <v>90.1</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K9" s="10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="L9" s="12" t="n">
         <v>54.44</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N9" s="12" t="n">
         <f aca="false">IF(COUNT(F9,I9,L9)=0,"",MIN(F9,I9,L9))</f>
@@ -4826,14 +4844,14 @@
         <v>90.1</v>
       </c>
       <c r="R9" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S9" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R9),ROUNDDOWN(R9*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T9" s="14" t="n">
-        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",IF(ISNUMBER(S9),MIN(ROUND(P9,2),S9),ROUND(P9,2)))</f>
+        <f aca="false">IF(COUNT(F9,I9,L9)=0,"Sem cotação",ROUND(P9,2))</f>
         <v>66.5</v>
       </c>
       <c r="U9" s="15" t="str">
@@ -4850,16 +4868,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D10" s="11" t="n">
         <v>4471</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>69.5</v>
@@ -4868,22 +4886,22 @@
         <v>40</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I10" s="12" t="n">
         <v>90</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K10" s="10" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="L10" s="12" t="n">
         <v>82.42</v>
       </c>
       <c r="M10" s="13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="N10" s="12" t="n">
         <f aca="false">IF(COUNT(F10,I10,L10)=0,"",MIN(F10,I10,L10))</f>
@@ -4902,14 +4920,14 @@
         <v>90</v>
       </c>
       <c r="R10" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S10" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R10),ROUNDDOWN(R10*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T10" s="14" t="n">
-        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",IF(ISNUMBER(S10),MIN(ROUND(P10,2),S10),ROUND(P10,2)))</f>
+        <f aca="false">IF(COUNT(F10,I10,L10)=0,"Sem cotação",ROUND(P10,2))</f>
         <v>82.42</v>
       </c>
       <c r="U10" s="15" t="str">
@@ -4926,16 +4944,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D11" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F11" s="12" t="n">
         <v>53.8</v>
@@ -4944,22 +4962,22 @@
         <v>40</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>72.91</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K11" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>73</v>
       </c>
       <c r="M11" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">IF(COUNT(F11,I11,L11)=0,"",MIN(F11,I11,L11))</f>
@@ -4978,14 +4996,14 @@
         <v>73</v>
       </c>
       <c r="R11" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S11" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R11),ROUNDDOWN(R11*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T11" s="14" t="n">
-        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",IF(ISNUMBER(S11),MIN(ROUND(P11,2),S11),ROUND(P11,2)))</f>
+        <f aca="false">IF(COUNT(F11,I11,L11)=0,"Sem cotação",ROUND(P11,2))</f>
         <v>72.91</v>
       </c>
       <c r="U11" s="15" t="str">
@@ -5002,16 +5020,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D12" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F12" s="12" t="n">
         <v>71</v>
@@ -5020,22 +5038,22 @@
         <v>40</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I12" s="12" t="n">
         <v>96.28</v>
       </c>
       <c r="J12" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K12" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>48</v>
       </c>
       <c r="M12" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">IF(COUNT(F12,I12,L12)=0,"",MIN(F12,I12,L12))</f>
@@ -5054,14 +5072,14 @@
         <v>96.28</v>
       </c>
       <c r="R12" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S12" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R12),ROUNDDOWN(R12*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T12" s="14" t="n">
-        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",IF(ISNUMBER(S12),MIN(ROUND(P12,2),S12),ROUND(P12,2)))</f>
+        <f aca="false">IF(COUNT(F12,I12,L12)=0,"Sem cotação",ROUND(P12,2))</f>
         <v>71</v>
       </c>
       <c r="U12" s="15" t="str">
@@ -5078,16 +5096,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D13" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F13" s="12" t="n">
         <v>101.25</v>
@@ -5096,22 +5114,22 @@
         <v>40</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>104.5</v>
       </c>
       <c r="J13" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K13" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>167</v>
       </c>
       <c r="M13" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N13" s="12" t="n">
         <f aca="false">IF(COUNT(F13,I13,L13)=0,"",MIN(F13,I13,L13))</f>
@@ -5130,14 +5148,14 @@
         <v>167</v>
       </c>
       <c r="R13" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S13" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R13),ROUNDDOWN(R13*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T13" s="14" t="n">
-        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",IF(ISNUMBER(S13),MIN(ROUND(P13,2),S13),ROUND(P13,2)))</f>
+        <f aca="false">IF(COUNT(F13,I13,L13)=0,"Sem cotação",ROUND(P13,2))</f>
         <v>104.5</v>
       </c>
       <c r="U13" s="15" t="str">
@@ -5154,16 +5172,16 @@
         <v>12</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D14" s="11" t="n">
         <v>5083</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>108.75</v>
@@ -5172,22 +5190,22 @@
         <v>40</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>166</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K14" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L14" s="12" t="n">
         <v>61</v>
       </c>
       <c r="M14" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N14" s="12" t="n">
         <f aca="false">IF(COUNT(F14,I14,L14)=0,"",MIN(F14,I14,L14))</f>
@@ -5206,14 +5224,14 @@
         <v>166</v>
       </c>
       <c r="R14" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S14" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R14),ROUNDDOWN(R14*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T14" s="14" t="n">
-        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",IF(ISNUMBER(S14),MIN(ROUND(P14,2),S14),ROUND(P14,2)))</f>
+        <f aca="false">IF(COUNT(F14,I14,L14)=0,"Sem cotação",ROUND(P14,2))</f>
         <v>108.75</v>
       </c>
       <c r="U14" s="15" t="str">
@@ -5230,16 +5248,16 @@
         <v>13</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D15" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>66.5</v>
@@ -5248,12 +5266,12 @@
         <v>40</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I15" s="12"/>
       <c r="J15" s="10"/>
       <c r="K15" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L15" s="12"/>
       <c r="M15" s="10"/>
@@ -5274,14 +5292,14 @@
         <v>66.5</v>
       </c>
       <c r="R15" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S15" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R15),ROUNDDOWN(R15*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T15" s="14" t="n">
-        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",IF(ISNUMBER(S15),MIN(ROUND(P15,2),S15),ROUND(P15,2)))</f>
+        <f aca="false">IF(COUNT(F15,I15,L15)=0,"Sem cotação",ROUND(P15,2))</f>
         <v>66.5</v>
       </c>
       <c r="U15" s="15" t="str">
@@ -5298,16 +5316,16 @@
         <v>14</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D16" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F16" s="12" t="n">
         <v>82.2</v>
@@ -5316,12 +5334,12 @@
         <v>40</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I16" s="12"/>
       <c r="J16" s="10"/>
       <c r="K16" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L16" s="12"/>
       <c r="M16" s="10"/>
@@ -5342,14 +5360,14 @@
         <v>82.2</v>
       </c>
       <c r="R16" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S16" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R16),ROUNDDOWN(R16*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T16" s="14" t="n">
-        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",IF(ISNUMBER(S16),MIN(ROUND(P16,2),S16),ROUND(P16,2)))</f>
+        <f aca="false">IF(COUNT(F16,I16,L16)=0,"Sem cotação",ROUND(P16,2))</f>
         <v>82.2</v>
       </c>
       <c r="U16" s="15" t="str">
@@ -5366,16 +5384,16 @@
         <v>15</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D17" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="F17" s="12" t="n">
         <v>107.6</v>
@@ -5384,12 +5402,12 @@
         <v>40</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I17" s="12"/>
       <c r="J17" s="10"/>
       <c r="K17" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L17" s="12"/>
       <c r="M17" s="10"/>
@@ -5410,14 +5428,14 @@
         <v>107.6</v>
       </c>
       <c r="R17" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S17" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R17),ROUNDDOWN(R17*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T17" s="14" t="n">
-        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",IF(ISNUMBER(S17),MIN(ROUND(P17,2),S17),ROUND(P17,2)))</f>
+        <f aca="false">IF(COUNT(F17,I17,L17)=0,"Sem cotação",ROUND(P17,2))</f>
         <v>107.6</v>
       </c>
       <c r="U17" s="15" t="str">
@@ -5434,16 +5452,16 @@
         <v>16</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F18" s="12" t="n">
         <v>107.6</v>
@@ -5452,12 +5470,12 @@
         <v>40</v>
       </c>
       <c r="H18" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I18" s="12"/>
       <c r="J18" s="10"/>
       <c r="K18" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L18" s="12"/>
       <c r="M18" s="10"/>
@@ -5478,14 +5496,14 @@
         <v>107.6</v>
       </c>
       <c r="R18" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S18" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R18),ROUNDDOWN(R18*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T18" s="14" t="n">
-        <f aca="false">IF(COUNT(F18,I18,L18)=0,"Sem cotação",IF(ISNUMBER(S18),MIN(ROUND(P18,2),S18),ROUND(P18,2)))</f>
+        <f aca="false">IF(COUNT(F18,I18,L18)=0,"Sem cotação",ROUND(P18,2))</f>
         <v>107.6</v>
       </c>
       <c r="U18" s="15" t="str">
@@ -5502,16 +5520,16 @@
         <v>17</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D19" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F19" s="12" t="n">
         <v>66.5</v>
@@ -5520,12 +5538,12 @@
         <v>40</v>
       </c>
       <c r="H19" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I19" s="12"/>
       <c r="J19" s="10"/>
       <c r="K19" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L19" s="12"/>
       <c r="M19" s="10"/>
@@ -5546,14 +5564,14 @@
         <v>66.5</v>
       </c>
       <c r="R19" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S19" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R19),ROUNDDOWN(R19*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T19" s="14" t="n">
-        <f aca="false">IF(COUNT(F19,I19,L19)=0,"Sem cotação",IF(ISNUMBER(S19),MIN(ROUND(P19,2),S19),ROUND(P19,2)))</f>
+        <f aca="false">IF(COUNT(F19,I19,L19)=0,"Sem cotação",ROUND(P19,2))</f>
         <v>66.5</v>
       </c>
       <c r="U19" s="15" t="str">
@@ -5570,16 +5588,16 @@
         <v>18</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D20" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F20" s="12" t="n">
         <v>107.6</v>
@@ -5588,12 +5606,12 @@
         <v>40</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I20" s="12"/>
       <c r="J20" s="10"/>
       <c r="K20" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L20" s="12"/>
       <c r="M20" s="10"/>
@@ -5614,14 +5632,14 @@
         <v>107.6</v>
       </c>
       <c r="R20" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S20" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R20),ROUNDDOWN(R20*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T20" s="14" t="n">
-        <f aca="false">IF(COUNT(F20,I20,L20)=0,"Sem cotação",IF(ISNUMBER(S20),MIN(ROUND(P20,2),S20),ROUND(P20,2)))</f>
+        <f aca="false">IF(COUNT(F20,I20,L20)=0,"Sem cotação",ROUND(P20,2))</f>
         <v>107.6</v>
       </c>
       <c r="U20" s="15" t="str">
@@ -5638,16 +5656,16 @@
         <v>19</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D21" s="11" t="n">
         <v>3092</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F21" s="12" t="n">
         <v>124.8</v>
@@ -5656,22 +5674,22 @@
         <v>40</v>
       </c>
       <c r="H21" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>127.89</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K21" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>123.5</v>
       </c>
       <c r="M21" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N21" s="12" t="n">
         <f aca="false">IF(COUNT(F21,I21,L21)=0,"",MIN(F21,I21,L21))</f>
@@ -5690,14 +5708,14 @@
         <v>127.89</v>
       </c>
       <c r="R21" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S21" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R21),ROUNDDOWN(R21*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T21" s="14" t="n">
-        <f aca="false">IF(COUNT(F21,I21,L21)=0,"Sem cotação",IF(ISNUMBER(S21),MIN(ROUND(P21,2),S21),ROUND(P21,2)))</f>
+        <f aca="false">IF(COUNT(F21,I21,L21)=0,"Sem cotação",ROUND(P21,2))</f>
         <v>124.8</v>
       </c>
       <c r="U21" s="15" t="str">
@@ -5714,16 +5732,16 @@
         <v>20</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D22" s="11" t="n">
         <v>10860</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F22" s="12" t="n">
         <v>68</v>
@@ -5732,22 +5750,22 @@
         <v>40</v>
       </c>
       <c r="H22" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>70.5</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K22" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>53.28</v>
       </c>
       <c r="M22" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N22" s="12" t="n">
         <f aca="false">IF(COUNT(F22,I22,L22)=0,"",MIN(F22,I22,L22))</f>
@@ -5766,14 +5784,14 @@
         <v>70.5</v>
       </c>
       <c r="R22" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S22" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R22),ROUNDDOWN(R22*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T22" s="14" t="n">
-        <f aca="false">IF(COUNT(F22,I22,L22)=0,"Sem cotação",IF(ISNUMBER(S22),MIN(ROUND(P22,2),S22),ROUND(P22,2)))</f>
+        <f aca="false">IF(COUNT(F22,I22,L22)=0,"Sem cotação",ROUND(P22,2))</f>
         <v>68</v>
       </c>
       <c r="U22" s="15" t="str">
@@ -5790,16 +5808,16 @@
         <v>21</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D23" s="11" t="n">
         <v>181</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>104.25</v>
@@ -5808,22 +5826,22 @@
         <v>40</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I23" s="12" t="n">
         <v>99</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K23" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>98.49</v>
       </c>
       <c r="M23" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N23" s="12" t="n">
         <f aca="false">IF(COUNT(F23,I23,L23)=0,"",MIN(F23,I23,L23))</f>
@@ -5842,14 +5860,14 @@
         <v>104.25</v>
       </c>
       <c r="R23" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S23" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R23),ROUNDDOWN(R23*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T23" s="14" t="n">
-        <f aca="false">IF(COUNT(F23,I23,L23)=0,"Sem cotação",IF(ISNUMBER(S23),MIN(ROUND(P23,2),S23),ROUND(P23,2)))</f>
+        <f aca="false">IF(COUNT(F23,I23,L23)=0,"Sem cotação",ROUND(P23,2))</f>
         <v>99</v>
       </c>
       <c r="U23" s="15" t="str">
@@ -5866,16 +5884,16 @@
         <v>22</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D24" s="11" t="n">
         <v>2528</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>124.8</v>
@@ -5884,22 +5902,22 @@
         <v>40</v>
       </c>
       <c r="H24" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>99</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K24" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="L24" s="12" t="n">
         <v>98.49</v>
       </c>
       <c r="M24" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N24" s="12" t="n">
         <f aca="false">IF(COUNT(F24,I24,L24)=0,"",MIN(F24,I24,L24))</f>
@@ -5918,14 +5936,14 @@
         <v>124.8</v>
       </c>
       <c r="R24" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S24" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R24),ROUNDDOWN(R24*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T24" s="14" t="n">
-        <f aca="false">IF(COUNT(F24,I24,L24)=0,"Sem cotação",IF(ISNUMBER(S24),MIN(ROUND(P24,2),S24),ROUND(P24,2)))</f>
+        <f aca="false">IF(COUNT(F24,I24,L24)=0,"Sem cotação",ROUND(P24,2))</f>
         <v>99</v>
       </c>
       <c r="U24" s="15" t="str">
@@ -5942,16 +5960,16 @@
         <v>23</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D25" s="11" t="n">
         <v>97</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>104.25</v>
@@ -5960,22 +5978,22 @@
         <v>40</v>
       </c>
       <c r="H25" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="I25" s="12" t="n">
         <v>113</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="K25" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>100.45</v>
       </c>
       <c r="M25" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N25" s="12" t="n">
         <f aca="false">IF(COUNT(F25,I25,L25)=0,"",MIN(F25,I25,L25))</f>
@@ -5994,14 +6012,14 @@
         <v>113</v>
       </c>
       <c r="R25" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S25" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R25),ROUNDDOWN(R25*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T25" s="14" t="n">
-        <f aca="false">IF(COUNT(F25,I25,L25)=0,"Sem cotação",IF(ISNUMBER(S25),MIN(ROUND(P25,2),S25),ROUND(P25,2)))</f>
+        <f aca="false">IF(COUNT(F25,I25,L25)=0,"Sem cotação",ROUND(P25,2))</f>
         <v>104.25</v>
       </c>
       <c r="U25" s="15" t="str">
@@ -6018,16 +6036,16 @@
         <v>24</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D26" s="11" t="n">
         <v>102</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F26" s="12" t="n">
         <v>139.6</v>
@@ -6036,22 +6054,22 @@
         <v>40</v>
       </c>
       <c r="H26" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>152</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K26" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>82.5</v>
       </c>
       <c r="M26" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N26" s="12" t="n">
         <f aca="false">IF(COUNT(F26,I26,L26)=0,"",MIN(F26,I26,L26))</f>
@@ -6070,14 +6088,14 @@
         <v>152</v>
       </c>
       <c r="R26" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S26" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R26),ROUNDDOWN(R26*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T26" s="14" t="n">
-        <f aca="false">IF(COUNT(F26,I26,L26)=0,"Sem cotação",IF(ISNUMBER(S26),MIN(ROUND(P26,2),S26),ROUND(P26,2)))</f>
+        <f aca="false">IF(COUNT(F26,I26,L26)=0,"Sem cotação",ROUND(P26,2))</f>
         <v>139.6</v>
       </c>
       <c r="U26" s="15" t="str">
@@ -6094,16 +6112,16 @@
         <v>25</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D27" s="11" t="n">
         <v>48</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F27" s="12" t="n">
         <v>171.35</v>
@@ -6112,22 +6130,22 @@
         <v>40</v>
       </c>
       <c r="H27" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>166</v>
       </c>
       <c r="J27" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L27" s="12" t="n">
         <v>82.5</v>
       </c>
       <c r="M27" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N27" s="12" t="n">
         <f aca="false">IF(COUNT(F27,I27,L27)=0,"",MIN(F27,I27,L27))</f>
@@ -6146,14 +6164,14 @@
         <v>171.35</v>
       </c>
       <c r="R27" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S27" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R27),ROUNDDOWN(R27*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T27" s="14" t="n">
-        <f aca="false">IF(COUNT(F27,I27,L27)=0,"Sem cotação",IF(ISNUMBER(S27),MIN(ROUND(P27,2),S27),ROUND(P27,2)))</f>
+        <f aca="false">IF(COUNT(F27,I27,L27)=0,"Sem cotação",ROUND(P27,2))</f>
         <v>166</v>
       </c>
       <c r="U27" s="15" t="str">
@@ -6170,16 +6188,16 @@
         <v>26</v>
       </c>
       <c r="B28" s="10" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D28" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F28" s="12" t="n">
         <v>235.75</v>
@@ -6188,16 +6206,16 @@
         <v>40</v>
       </c>
       <c r="H28" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>200.5</v>
       </c>
       <c r="J28" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L28" s="12"/>
       <c r="M28" s="10"/>
@@ -6218,14 +6236,14 @@
         <v>235.75</v>
       </c>
       <c r="R28" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S28" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R28),ROUNDDOWN(R28*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T28" s="14" t="n">
-        <f aca="false">IF(COUNT(F28,I28,L28)=0,"Sem cotação",IF(ISNUMBER(S28),MIN(ROUND(P28,2),S28),ROUND(P28,2)))</f>
+        <f aca="false">IF(COUNT(F28,I28,L28)=0,"Sem cotação",ROUND(P28,2))</f>
         <v>218.13</v>
       </c>
       <c r="U28" s="15" t="str">
@@ -6242,16 +6260,16 @@
         <v>27</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C29" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D29" s="11" t="n">
         <v>48</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F29" s="12" t="n">
         <v>136</v>
@@ -6260,12 +6278,12 @@
         <v>40</v>
       </c>
       <c r="H29" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I29" s="12"/>
       <c r="J29" s="10"/>
       <c r="K29" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L29" s="12"/>
       <c r="M29" s="10"/>
@@ -6286,14 +6304,14 @@
         <v>136</v>
       </c>
       <c r="R29" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S29" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R29),ROUNDDOWN(R29*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T29" s="14" t="n">
-        <f aca="false">IF(COUNT(F29,I29,L29)=0,"Sem cotação",IF(ISNUMBER(S29),MIN(ROUND(P29,2),S29),ROUND(P29,2)))</f>
+        <f aca="false">IF(COUNT(F29,I29,L29)=0,"Sem cotação",ROUND(P29,2))</f>
         <v>136</v>
       </c>
       <c r="U29" s="15" t="str">
@@ -6310,16 +6328,16 @@
         <v>28</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D30" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F30" s="12" t="n">
         <v>110.25</v>
@@ -6328,22 +6346,22 @@
         <v>40</v>
       </c>
       <c r="H30" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>149.56</v>
       </c>
       <c r="J30" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L30" s="12" t="n">
         <v>150</v>
       </c>
       <c r="M30" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N30" s="12" t="n">
         <f aca="false">IF(COUNT(F30,I30,L30)=0,"",MIN(F30,I30,L30))</f>
@@ -6362,14 +6380,14 @@
         <v>150</v>
       </c>
       <c r="R30" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S30" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R30),ROUNDDOWN(R30*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T30" s="14" t="n">
-        <f aca="false">IF(COUNT(F30,I30,L30)=0,"Sem cotação",IF(ISNUMBER(S30),MIN(ROUND(P30,2),S30),ROUND(P30,2)))</f>
+        <f aca="false">IF(COUNT(F30,I30,L30)=0,"Sem cotação",ROUND(P30,2))</f>
         <v>149.56</v>
       </c>
       <c r="U30" s="15" t="str">
@@ -6386,16 +6404,16 @@
         <v>29</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D31" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F31" s="12" t="n">
         <v>53.8</v>
@@ -6404,22 +6422,22 @@
         <v>40</v>
       </c>
       <c r="H31" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I31" s="12" t="n">
         <v>76.05</v>
       </c>
       <c r="J31" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>19</v>
       </c>
       <c r="M31" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N31" s="12" t="n">
         <f aca="false">IF(COUNT(F31,I31,L31)=0,"",MIN(F31,I31,L31))</f>
@@ -6438,14 +6456,14 @@
         <v>76.05</v>
       </c>
       <c r="R31" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S31" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R31),ROUNDDOWN(R31*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T31" s="14" t="n">
-        <f aca="false">IF(COUNT(F31,I31,L31)=0,"Sem cotação",IF(ISNUMBER(S31),MIN(ROUND(P31,2),S31),ROUND(P31,2)))</f>
+        <f aca="false">IF(COUNT(F31,I31,L31)=0,"Sem cotação",ROUND(P31,2))</f>
         <v>53.8</v>
       </c>
       <c r="U31" s="15" t="str">
@@ -6462,16 +6480,16 @@
         <v>30</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D32" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>53.8</v>
@@ -6480,22 +6498,22 @@
         <v>40</v>
       </c>
       <c r="H32" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>72.91</v>
       </c>
       <c r="J32" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M32" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N32" s="12" t="n">
         <f aca="false">IF(COUNT(F32,I32,L32)=0,"",MIN(F32,I32,L32))</f>
@@ -6514,14 +6532,14 @@
         <v>72.91</v>
       </c>
       <c r="R32" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S32" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R32),ROUNDDOWN(R32*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T32" s="14" t="n">
-        <f aca="false">IF(COUNT(F32,I32,L32)=0,"Sem cotação",IF(ISNUMBER(S32),MIN(ROUND(P32,2),S32),ROUND(P32,2)))</f>
+        <f aca="false">IF(COUNT(F32,I32,L32)=0,"Sem cotação",ROUND(P32,2))</f>
         <v>53.8</v>
       </c>
       <c r="U32" s="15" t="str">
@@ -6538,40 +6556,40 @@
         <v>31</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D33" s="11" t="n">
         <v>21942</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>64.31</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="H33" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="I33" s="12" t="n">
         <v>43.9</v>
       </c>
       <c r="J33" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>10.3</v>
       </c>
       <c r="M33" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N33" s="12" t="n">
         <f aca="false">IF(COUNT(F33,I33,L33)=0,"",MIN(F33,I33,L33))</f>
@@ -6590,14 +6608,14 @@
         <v>64.31</v>
       </c>
       <c r="R33" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S33" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R33),ROUNDDOWN(R33*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T33" s="14" t="n">
-        <f aca="false">IF(COUNT(F33,I33,L33)=0,"Sem cotação",IF(ISNUMBER(S33),MIN(ROUND(P33,2),S33),ROUND(P33,2)))</f>
+        <f aca="false">IF(COUNT(F33,I33,L33)=0,"Sem cotação",ROUND(P33,2))</f>
         <v>43.9</v>
       </c>
       <c r="U33" s="15" t="str">
@@ -6614,16 +6632,16 @@
         <v>32</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D34" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>69.5</v>
@@ -6632,22 +6650,22 @@
         <v>40</v>
       </c>
       <c r="H34" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I34" s="12" t="n">
         <v>94.22</v>
       </c>
       <c r="J34" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L34" s="12" t="n">
         <v>19.5</v>
       </c>
       <c r="M34" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N34" s="12" t="n">
         <f aca="false">IF(COUNT(F34,I34,L34)=0,"",MIN(F34,I34,L34))</f>
@@ -6666,14 +6684,14 @@
         <v>94.22</v>
       </c>
       <c r="R34" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S34" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R34),ROUNDDOWN(R34*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T34" s="14" t="n">
-        <f aca="false">IF(COUNT(F34,I34,L34)=0,"Sem cotação",IF(ISNUMBER(S34),MIN(ROUND(P34,2),S34),ROUND(P34,2)))</f>
+        <f aca="false">IF(COUNT(F34,I34,L34)=0,"Sem cotação",ROUND(P34,2))</f>
         <v>69.5</v>
       </c>
       <c r="U34" s="15" t="str">
@@ -6690,16 +6708,16 @@
         <v>33</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D35" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>101.25</v>
@@ -6708,22 +6726,22 @@
         <v>40</v>
       </c>
       <c r="H35" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I35" s="12" t="n">
         <v>137.21</v>
       </c>
       <c r="J35" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M35" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N35" s="12" t="n">
         <f aca="false">IF(COUNT(F35,I35,L35)=0,"",MIN(F35,I35,L35))</f>
@@ -6742,14 +6760,14 @@
         <v>137.21</v>
       </c>
       <c r="R35" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S35" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R35),ROUNDDOWN(R35*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T35" s="14" t="n">
-        <f aca="false">IF(COUNT(F35,I35,L35)=0,"Sem cotação",IF(ISNUMBER(S35),MIN(ROUND(P35,2),S35),ROUND(P35,2)))</f>
+        <f aca="false">IF(COUNT(F35,I35,L35)=0,"Sem cotação",ROUND(P35,2))</f>
         <v>101.25</v>
       </c>
       <c r="U35" s="15" t="str">
@@ -6766,16 +6784,16 @@
         <v>34</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D36" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>473</v>
@@ -6784,22 +6802,22 @@
         <v>40</v>
       </c>
       <c r="H36" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>641.01</v>
       </c>
       <c r="J36" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="L36" s="12" t="n">
         <v>600</v>
       </c>
       <c r="M36" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N36" s="12" t="n">
         <f aca="false">IF(COUNT(F36,I36,L36)=0,"",MIN(F36,I36,L36))</f>
@@ -6818,14 +6836,14 @@
         <v>641.01</v>
       </c>
       <c r="R36" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S36" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R36),ROUNDDOWN(R36*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T36" s="14" t="n">
-        <f aca="false">IF(COUNT(F36,I36,L36)=0,"Sem cotação",IF(ISNUMBER(S36),MIN(ROUND(P36,2),S36),ROUND(P36,2)))</f>
+        <f aca="false">IF(COUNT(F36,I36,L36)=0,"Sem cotação",ROUND(P36,2))</f>
         <v>600</v>
       </c>
       <c r="U36" s="15" t="str">
@@ -6842,16 +6860,16 @@
         <v>35</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D37" s="11" t="n">
         <v>242</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>214.5</v>
@@ -6860,22 +6878,22 @@
         <v>40</v>
       </c>
       <c r="H37" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I37" s="12" t="n">
         <v>290.89</v>
       </c>
       <c r="J37" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L37" s="12" t="n">
         <v>638</v>
       </c>
       <c r="M37" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N37" s="12" t="n">
         <f aca="false">IF(COUNT(F37,I37,L37)=0,"",MIN(F37,I37,L37))</f>
@@ -6894,14 +6912,14 @@
         <v>638</v>
       </c>
       <c r="R37" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S37" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R37),ROUNDDOWN(R37*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T37" s="14" t="n">
-        <f aca="false">IF(COUNT(F37,I37,L37)=0,"Sem cotação",IF(ISNUMBER(S37),MIN(ROUND(P37,2),S37),ROUND(P37,2)))</f>
+        <f aca="false">IF(COUNT(F37,I37,L37)=0,"Sem cotação",ROUND(P37,2))</f>
         <v>290.89</v>
       </c>
       <c r="U37" s="15" t="str">
@@ -6918,16 +6936,16 @@
         <v>36</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D38" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F38" s="12" t="n">
         <v>482</v>
@@ -6936,22 +6954,22 @@
         <v>40</v>
       </c>
       <c r="H38" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I38" s="12" t="n">
         <v>653.36</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>450</v>
       </c>
       <c r="M38" s="13" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="N38" s="12" t="n">
         <f aca="false">IF(COUNT(F38,I38,L38)=0,"",MIN(F38,I38,L38))</f>
@@ -6970,14 +6988,14 @@
         <v>653.36</v>
       </c>
       <c r="R38" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S38" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R38),ROUNDDOWN(R38*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T38" s="14" t="n">
-        <f aca="false">IF(COUNT(F38,I38,L38)=0,"Sem cotação",IF(ISNUMBER(S38),MIN(ROUND(P38,2),S38),ROUND(P38,2)))</f>
+        <f aca="false">IF(COUNT(F38,I38,L38)=0,"Sem cotação",ROUND(P38,2))</f>
         <v>482</v>
       </c>
       <c r="U38" s="15" t="str">
@@ -6994,16 +7012,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D39" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F39" s="12" t="n">
         <v>11.66</v>
@@ -7012,22 +7030,22 @@
         <v>40</v>
       </c>
       <c r="H39" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I39" s="12" t="n">
         <v>15.82</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L39" s="12" t="n">
         <v>18.32</v>
       </c>
       <c r="M39" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N39" s="12" t="n">
         <f aca="false">IF(COUNT(F39,I39,L39)=0,"",MIN(F39,I39,L39))</f>
@@ -7046,14 +7064,14 @@
         <v>18.32</v>
       </c>
       <c r="R39" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S39" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R39),ROUNDDOWN(R39*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T39" s="14" t="n">
-        <f aca="false">IF(COUNT(F39,I39,L39)=0,"Sem cotação",IF(ISNUMBER(S39),MIN(ROUND(P39,2),S39),ROUND(P39,2)))</f>
+        <f aca="false">IF(COUNT(F39,I39,L39)=0,"Sem cotação",ROUND(P39,2))</f>
         <v>15.82</v>
       </c>
       <c r="U39" s="15" t="str">
@@ -7070,16 +7088,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D40" s="11" t="n">
         <v>826</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F40" s="12" t="n">
         <v>257.8</v>
@@ -7088,22 +7106,22 @@
         <v>40</v>
       </c>
       <c r="H40" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I40" s="12" t="n">
         <v>144.49</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>180</v>
       </c>
       <c r="M40" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N40" s="12" t="n">
         <f aca="false">IF(COUNT(F40,I40,L40)=0,"",MIN(F40,I40,L40))</f>
@@ -7122,14 +7140,14 @@
         <v>257.8</v>
       </c>
       <c r="R40" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S40" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R40),ROUNDDOWN(R40*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T40" s="14" t="n">
-        <f aca="false">IF(COUNT(F40,I40,L40)=0,"Sem cotação",IF(ISNUMBER(S40),MIN(ROUND(P40,2),S40),ROUND(P40,2)))</f>
+        <f aca="false">IF(COUNT(F40,I40,L40)=0,"Sem cotação",ROUND(P40,2))</f>
         <v>180</v>
       </c>
       <c r="U40" s="15" t="str">
@@ -7146,16 +7164,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D41" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>137.5</v>
@@ -7164,22 +7182,22 @@
         <v>40</v>
       </c>
       <c r="H41" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>186.38</v>
       </c>
       <c r="J41" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>238</v>
       </c>
       <c r="M41" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N41" s="12" t="n">
         <f aca="false">IF(COUNT(F41,I41,L41)=0,"",MIN(F41,I41,L41))</f>
@@ -7198,14 +7216,14 @@
         <v>238</v>
       </c>
       <c r="R41" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S41" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R41),ROUNDDOWN(R41*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T41" s="14" t="n">
-        <f aca="false">IF(COUNT(F41,I41,L41)=0,"Sem cotação",IF(ISNUMBER(S41),MIN(ROUND(P41,2),S41),ROUND(P41,2)))</f>
+        <f aca="false">IF(COUNT(F41,I41,L41)=0,"Sem cotação",ROUND(P41,2))</f>
         <v>186.38</v>
       </c>
       <c r="U41" s="15" t="str">
@@ -7222,16 +7240,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D42" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>68</v>
@@ -7240,16 +7258,16 @@
         <v>40</v>
       </c>
       <c r="H42" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J42" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L42" s="12"/>
       <c r="M42" s="10"/>
@@ -7270,14 +7288,14 @@
         <v>68</v>
       </c>
       <c r="R42" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S42" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R42),ROUNDDOWN(R42*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T42" s="14" t="n">
-        <f aca="false">IF(COUNT(F42,I42,L42)=0,"Sem cotação",IF(ISNUMBER(S42),MIN(ROUND(P42,2),S42),ROUND(P42,2)))</f>
+        <f aca="false">IF(COUNT(F42,I42,L42)=0,"Sem cotação",ROUND(P42,2))</f>
         <v>49</v>
       </c>
       <c r="U42" s="15" t="str">
@@ -7294,16 +7312,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D43" s="11" t="n">
         <v>1496</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>41.1</v>
@@ -7312,22 +7330,22 @@
         <v>40</v>
       </c>
       <c r="H43" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>78.5</v>
       </c>
       <c r="J43" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>25.3</v>
       </c>
       <c r="M43" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N43" s="12" t="n">
         <f aca="false">IF(COUNT(F43,I43,L43)=0,"",MIN(F43,I43,L43))</f>
@@ -7346,14 +7364,14 @@
         <v>78.5</v>
       </c>
       <c r="R43" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S43" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R43),ROUNDDOWN(R43*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T43" s="14" t="n">
-        <f aca="false">IF(COUNT(F43,I43,L43)=0,"Sem cotação",IF(ISNUMBER(S43),MIN(ROUND(P43,2),S43),ROUND(P43,2)))</f>
+        <f aca="false">IF(COUNT(F43,I43,L43)=0,"Sem cotação",ROUND(P43,2))</f>
         <v>41.1</v>
       </c>
       <c r="U43" s="15" t="str">
@@ -7370,16 +7388,16 @@
         <v>42</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D44" s="11" t="n">
         <v>1496</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>69.5</v>
@@ -7388,22 +7406,22 @@
         <v>40</v>
       </c>
       <c r="H44" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I44" s="12" t="n">
         <v>78.5</v>
       </c>
       <c r="J44" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L44" s="12" t="n">
         <v>90</v>
       </c>
       <c r="M44" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N44" s="12" t="n">
         <f aca="false">IF(COUNT(F44,I44,L44)=0,"",MIN(F44,I44,L44))</f>
@@ -7422,14 +7440,14 @@
         <v>90</v>
       </c>
       <c r="R44" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S44" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R44),ROUNDDOWN(R44*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T44" s="14" t="n">
-        <f aca="false">IF(COUNT(F44,I44,L44)=0,"Sem cotação",IF(ISNUMBER(S44),MIN(ROUND(P44,2),S44),ROUND(P44,2)))</f>
+        <f aca="false">IF(COUNT(F44,I44,L44)=0,"Sem cotação",ROUND(P44,2))</f>
         <v>78.5</v>
       </c>
       <c r="U44" s="15" t="str">
@@ -7446,16 +7464,16 @@
         <v>43</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D45" s="11" t="n">
         <v>640</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>85.2</v>
@@ -7464,22 +7482,22 @@
         <v>40</v>
       </c>
       <c r="H45" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>115.53</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>107</v>
       </c>
       <c r="M45" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N45" s="12" t="n">
         <f aca="false">IF(COUNT(F45,I45,L45)=0,"",MIN(F45,I45,L45))</f>
@@ -7498,14 +7516,14 @@
         <v>115.53</v>
       </c>
       <c r="R45" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S45" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R45),ROUNDDOWN(R45*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T45" s="14" t="n">
-        <f aca="false">IF(COUNT(F45,I45,L45)=0,"Sem cotação",IF(ISNUMBER(S45),MIN(ROUND(P45,2),S45),ROUND(P45,2)))</f>
+        <f aca="false">IF(COUNT(F45,I45,L45)=0,"Sem cotação",ROUND(P45,2))</f>
         <v>107</v>
       </c>
       <c r="U45" s="15" t="str">
@@ -7522,16 +7540,16 @@
         <v>44</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D46" s="11" t="n">
         <v>5027</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>85.2</v>
@@ -7540,22 +7558,22 @@
         <v>40</v>
       </c>
       <c r="H46" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I46" s="12" t="n">
         <v>115.53</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>121</v>
       </c>
       <c r="M46" s="13" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="N46" s="12" t="n">
         <f aca="false">IF(COUNT(F46,I46,L46)=0,"",MIN(F46,I46,L46))</f>
@@ -7574,14 +7592,14 @@
         <v>121</v>
       </c>
       <c r="R46" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S46" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R46),ROUNDDOWN(R46*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T46" s="14" t="n">
-        <f aca="false">IF(COUNT(F46,I46,L46)=0,"Sem cotação",IF(ISNUMBER(S46),MIN(ROUND(P46,2),S46),ROUND(P46,2)))</f>
+        <f aca="false">IF(COUNT(F46,I46,L46)=0,"Sem cotação",ROUND(P46,2))</f>
         <v>115.53</v>
       </c>
       <c r="U46" s="15" t="str">
@@ -7598,16 +7616,16 @@
         <v>45</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D47" s="11" t="n">
         <v>3174</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>101.25</v>
@@ -7616,22 +7634,22 @@
         <v>40</v>
       </c>
       <c r="H47" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>137.21</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>98</v>
       </c>
       <c r="M47" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N47" s="12" t="n">
         <f aca="false">IF(COUNT(F47,I47,L47)=0,"",MIN(F47,I47,L47))</f>
@@ -7650,14 +7668,14 @@
         <v>137.21</v>
       </c>
       <c r="R47" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S47" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R47),ROUNDDOWN(R47*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T47" s="14" t="n">
-        <f aca="false">IF(COUNT(F47,I47,L47)=0,"Sem cotação",IF(ISNUMBER(S47),MIN(ROUND(P47,2),S47),ROUND(P47,2)))</f>
+        <f aca="false">IF(COUNT(F47,I47,L47)=0,"Sem cotação",ROUND(P47,2))</f>
         <v>101.25</v>
       </c>
       <c r="U47" s="15" t="str">
@@ -7674,16 +7692,16 @@
         <v>46</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D48" s="11" t="n">
         <v>3174</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F48" s="12" t="n">
         <v>133</v>
@@ -7692,22 +7710,22 @@
         <v>40</v>
       </c>
       <c r="H48" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I48" s="12" t="n">
         <v>180.2</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>128.87</v>
       </c>
       <c r="M48" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N48" s="12" t="n">
         <f aca="false">IF(COUNT(F48,I48,L48)=0,"",MIN(F48,I48,L48))</f>
@@ -7726,14 +7744,14 @@
         <v>180.2</v>
       </c>
       <c r="R48" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S48" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R48),ROUNDDOWN(R48*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T48" s="14" t="n">
-        <f aca="false">IF(COUNT(F48,I48,L48)=0,"Sem cotação",IF(ISNUMBER(S48),MIN(ROUND(P48,2),S48),ROUND(P48,2)))</f>
+        <f aca="false">IF(COUNT(F48,I48,L48)=0,"Sem cotação",ROUND(P48,2))</f>
         <v>133</v>
       </c>
       <c r="U48" s="15" t="str">
@@ -7750,16 +7768,16 @@
         <v>47</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D49" s="11" t="n">
         <v>2715</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F49" s="12" t="n">
         <v>164.75</v>
@@ -7768,22 +7786,22 @@
         <v>40</v>
       </c>
       <c r="H49" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>223.2</v>
       </c>
       <c r="J49" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L49" s="12" t="n">
         <v>159.25</v>
       </c>
       <c r="M49" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N49" s="12" t="n">
         <f aca="false">IF(COUNT(F49,I49,L49)=0,"",MIN(F49,I49,L49))</f>
@@ -7802,14 +7820,14 @@
         <v>223.2</v>
       </c>
       <c r="R49" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S49" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R49),ROUNDDOWN(R49*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T49" s="14" t="n">
-        <f aca="false">IF(COUNT(F49,I49,L49)=0,"Sem cotação",IF(ISNUMBER(S49),MIN(ROUND(P49,2),S49),ROUND(P49,2)))</f>
+        <f aca="false">IF(COUNT(F49,I49,L49)=0,"Sem cotação",ROUND(P49,2))</f>
         <v>164.75</v>
       </c>
       <c r="U49" s="15" t="str">
@@ -7826,16 +7844,16 @@
         <v>48</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D50" s="11" t="n">
         <v>5027</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F50" s="12" t="n">
         <v>183.8</v>
@@ -7844,22 +7862,22 @@
         <v>40</v>
       </c>
       <c r="H50" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I50" s="12" t="n">
         <v>248.99</v>
       </c>
       <c r="J50" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L50" s="12" t="n">
         <v>177.87</v>
       </c>
       <c r="M50" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N50" s="12" t="n">
         <f aca="false">IF(COUNT(F50,I50,L50)=0,"",MIN(F50,I50,L50))</f>
@@ -7878,14 +7896,14 @@
         <v>248.99</v>
       </c>
       <c r="R50" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S50" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R50),ROUNDDOWN(R50*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T50" s="14" t="n">
-        <f aca="false">IF(COUNT(F50,I50,L50)=0,"Sem cotação",IF(ISNUMBER(S50),MIN(ROUND(P50,2),S50),ROUND(P50,2)))</f>
+        <f aca="false">IF(COUNT(F50,I50,L50)=0,"Sem cotação",ROUND(P50,2))</f>
         <v>183.8</v>
       </c>
       <c r="U50" s="15" t="str">
@@ -7902,16 +7920,16 @@
         <v>49</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D51" s="11" t="n">
         <v>5027</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>164.75</v>
@@ -7920,22 +7938,22 @@
         <v>40</v>
       </c>
       <c r="H51" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I51" s="12" t="n">
         <v>223.2</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L51" s="12" t="n">
         <v>94.55</v>
       </c>
       <c r="M51" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N51" s="12" t="n">
         <f aca="false">IF(COUNT(F51,I51,L51)=0,"",MIN(F51,I51,L51))</f>
@@ -7954,14 +7972,14 @@
         <v>223.2</v>
       </c>
       <c r="R51" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S51" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R51),ROUNDDOWN(R51*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T51" s="14" t="n">
-        <f aca="false">IF(COUNT(F51,I51,L51)=0,"Sem cotação",IF(ISNUMBER(S51),MIN(ROUND(P51,2),S51),ROUND(P51,2)))</f>
+        <f aca="false">IF(COUNT(F51,I51,L51)=0,"Sem cotação",ROUND(P51,2))</f>
         <v>164.75</v>
       </c>
       <c r="U51" s="15" t="str">
@@ -7978,16 +7996,16 @@
         <v>50</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D52" s="11" t="n">
         <v>5491</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F52" s="12" t="n">
         <v>183.8</v>
@@ -7996,22 +8014,22 @@
         <v>40</v>
       </c>
       <c r="H52" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I52" s="12" t="n">
         <v>248.99</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="L52" s="12" t="n">
         <v>123.83</v>
       </c>
       <c r="M52" s="13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="N52" s="12" t="n">
         <f aca="false">IF(COUNT(F52,I52,L52)=0,"",MIN(F52,I52,L52))</f>
@@ -8030,14 +8048,14 @@
         <v>248.99</v>
       </c>
       <c r="R52" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S52" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R52),ROUNDDOWN(R52*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T52" s="14" t="n">
-        <f aca="false">IF(COUNT(F52,I52,L52)=0,"Sem cotação",IF(ISNUMBER(S52),MIN(ROUND(P52,2),S52),ROUND(P52,2)))</f>
+        <f aca="false">IF(COUNT(F52,I52,L52)=0,"Sem cotação",ROUND(P52,2))</f>
         <v>183.8</v>
       </c>
       <c r="U52" s="15" t="str">
@@ -8054,16 +8072,16 @@
         <v>51</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D53" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>101.25</v>
@@ -8072,22 +8090,22 @@
         <v>40</v>
       </c>
       <c r="H53" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>137.21</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K53" s="10" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="L53" s="12" t="n">
         <v>98</v>
       </c>
       <c r="M53" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N53" s="12" t="n">
         <f aca="false">IF(COUNT(F53,I53,L53)=0,"",MIN(F53,I53,L53))</f>
@@ -8106,14 +8124,14 @@
         <v>137.21</v>
       </c>
       <c r="R53" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S53" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R53),ROUNDDOWN(R53*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T53" s="14" t="n">
-        <f aca="false">IF(COUNT(F53,I53,L53)=0,"Sem cotação",IF(ISNUMBER(S53),MIN(ROUND(P53,2),S53),ROUND(P53,2)))</f>
+        <f aca="false">IF(COUNT(F53,I53,L53)=0,"Sem cotação",ROUND(P53,2))</f>
         <v>101.25</v>
       </c>
       <c r="U53" s="15" t="str">
@@ -8130,16 +8148,16 @@
         <v>52</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D54" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F54" s="12" t="n">
         <v>56.5</v>
@@ -8148,22 +8166,22 @@
         <v>40</v>
       </c>
       <c r="H54" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>71.36</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K54" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>42.5</v>
       </c>
       <c r="M54" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N54" s="12" t="n">
         <f aca="false">IF(COUNT(F54,I54,L54)=0,"",MIN(F54,I54,L54))</f>
@@ -8182,14 +8200,14 @@
         <v>71.36</v>
       </c>
       <c r="R54" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S54" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R54),ROUNDDOWN(R54*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T54" s="14" t="n">
-        <f aca="false">IF(COUNT(F54,I54,L54)=0,"Sem cotação",IF(ISNUMBER(S54),MIN(ROUND(P54,2),S54),ROUND(P54,2)))</f>
+        <f aca="false">IF(COUNT(F54,I54,L54)=0,"Sem cotação",ROUND(P54,2))</f>
         <v>56.5</v>
       </c>
       <c r="U54" s="15" t="str">
@@ -8206,16 +8224,16 @@
         <v>53</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D55" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F55" s="12" t="n">
         <v>243.25</v>
@@ -8224,22 +8242,22 @@
         <v>40</v>
       </c>
       <c r="H55" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>343.95</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K55" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L55" s="12" t="n">
         <v>329.77</v>
       </c>
       <c r="M55" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N55" s="12" t="n">
         <f aca="false">IF(COUNT(F55,I55,L55)=0,"",MIN(F55,I55,L55))</f>
@@ -8258,14 +8276,14 @@
         <v>343.95</v>
       </c>
       <c r="R55" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S55" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R55),ROUNDDOWN(R55*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T55" s="14" t="n">
-        <f aca="false">IF(COUNT(F55,I55,L55)=0,"Sem cotação",IF(ISNUMBER(S55),MIN(ROUND(P55,2),S55),ROUND(P55,2)))</f>
+        <f aca="false">IF(COUNT(F55,I55,L55)=0,"Sem cotação",ROUND(P55,2))</f>
         <v>329.77</v>
       </c>
       <c r="U55" s="15" t="str">
@@ -8282,16 +8300,16 @@
         <v>54</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D56" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F56" s="12" t="n">
         <v>179.75</v>
@@ -8300,22 +8318,22 @@
         <v>40</v>
       </c>
       <c r="H56" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I56" s="12" t="n">
         <v>252.11</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K56" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L56" s="12" t="n">
         <v>243.78</v>
       </c>
       <c r="M56" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="N56" s="12" t="n">
         <f aca="false">IF(COUNT(F56,I56,L56)=0,"",MIN(F56,I56,L56))</f>
@@ -8334,14 +8352,14 @@
         <v>252.11</v>
       </c>
       <c r="R56" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S56" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R56),ROUNDDOWN(R56*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T56" s="14" t="n">
-        <f aca="false">IF(COUNT(F56,I56,L56)=0,"Sem cotação",IF(ISNUMBER(S56),MIN(ROUND(P56,2),S56),ROUND(P56,2)))</f>
+        <f aca="false">IF(COUNT(F56,I56,L56)=0,"Sem cotação",ROUND(P56,2))</f>
         <v>243.78</v>
       </c>
       <c r="U56" s="15" t="str">
@@ -8358,16 +8376,16 @@
         <v>55</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D57" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>86.7</v>
@@ -8376,16 +8394,16 @@
         <v>40</v>
       </c>
       <c r="H57" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>20</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="K57" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L57" s="12"/>
       <c r="M57" s="10"/>
@@ -8406,14 +8424,14 @@
         <v>86.7</v>
       </c>
       <c r="R57" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S57" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R57),ROUNDDOWN(R57*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T57" s="14" t="n">
-        <f aca="false">IF(COUNT(F57,I57,L57)=0,"Sem cotação",IF(ISNUMBER(S57),MIN(ROUND(P57,2),S57),ROUND(P57,2)))</f>
+        <f aca="false">IF(COUNT(F57,I57,L57)=0,"Sem cotação",ROUND(P57,2))</f>
         <v>53.35</v>
       </c>
       <c r="U57" s="15" t="str">
@@ -8430,26 +8448,26 @@
         <v>56</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D58" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="F58" s="12"/>
       <c r="G58" s="10"/>
       <c r="H58" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I58" s="12"/>
       <c r="J58" s="10"/>
       <c r="K58" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L58" s="12"/>
       <c r="M58" s="10"/>
@@ -8470,14 +8488,14 @@
         <v/>
       </c>
       <c r="R58" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S58" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R58),ROUNDDOWN(R58*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T58" s="14" t="str">
-        <f aca="false">IF(COUNT(F58,I58,L58)=0,"Sem cotação",IF(ISNUMBER(S58),MIN(ROUND(P58,2),S58),ROUND(P58,2)))</f>
+        <f aca="false">IF(COUNT(F58,I58,L58)=0,"Sem cotação",ROUND(P58,2))</f>
         <v>Sem cotação</v>
       </c>
       <c r="U58" s="15" t="str">
@@ -8494,16 +8512,16 @@
         <v>57</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D59" s="11" t="n">
         <v>196</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F59" s="12" t="n">
         <v>306.75</v>
@@ -8512,22 +8530,22 @@
         <v>40</v>
       </c>
       <c r="H59" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I59" s="12" t="n">
         <v>415.75</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K59" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="L59" s="12" t="n">
         <v>610.5</v>
       </c>
       <c r="M59" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="N59" s="12" t="n">
         <f aca="false">IF(COUNT(F59,I59,L59)=0,"",MIN(F59,I59,L59))</f>
@@ -8546,14 +8564,14 @@
         <v>610.5</v>
       </c>
       <c r="R59" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S59" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R59),ROUNDDOWN(R59*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T59" s="14" t="n">
-        <f aca="false">IF(COUNT(F59,I59,L59)=0,"Sem cotação",IF(ISNUMBER(S59),MIN(ROUND(P59,2),S59),ROUND(P59,2)))</f>
+        <f aca="false">IF(COUNT(F59,I59,L59)=0,"Sem cotação",ROUND(P59,2))</f>
         <v>415.75</v>
       </c>
       <c r="U59" s="15" t="str">
@@ -8570,16 +8588,16 @@
         <v>58</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D60" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F60" s="12" t="n">
         <v>71.9</v>
@@ -8588,22 +8606,22 @@
         <v>40</v>
       </c>
       <c r="H60" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>123.5</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K60" s="10" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>52</v>
       </c>
       <c r="M60" s="13" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="N60" s="12" t="n">
         <f aca="false">IF(COUNT(F60,I60,L60)=0,"",MIN(F60,I60,L60))</f>
@@ -8622,14 +8640,14 @@
         <v>123.5</v>
       </c>
       <c r="R60" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S60" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R60),ROUNDDOWN(R60*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T60" s="14" t="n">
-        <f aca="false">IF(COUNT(F60,I60,L60)=0,"Sem cotação",IF(ISNUMBER(S60),MIN(ROUND(P60,2),S60),ROUND(P60,2)))</f>
+        <f aca="false">IF(COUNT(F60,I60,L60)=0,"Sem cotação",ROUND(P60,2))</f>
         <v>71.9</v>
       </c>
       <c r="U60" s="15" t="str">
@@ -8646,16 +8664,16 @@
         <v>59</v>
       </c>
       <c r="B61" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D61" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>53.8</v>
@@ -8664,12 +8682,12 @@
         <v>40</v>
       </c>
       <c r="H61" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="I61" s="12"/>
       <c r="J61" s="10"/>
       <c r="K61" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L61" s="12"/>
       <c r="M61" s="10"/>
@@ -8690,14 +8708,14 @@
         <v>53.8</v>
       </c>
       <c r="R61" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S61" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R61),ROUNDDOWN(R61*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T61" s="14" t="n">
-        <f aca="false">IF(COUNT(F61,I61,L61)=0,"Sem cotação",IF(ISNUMBER(S61),MIN(ROUND(P61,2),S61),ROUND(P61,2)))</f>
+        <f aca="false">IF(COUNT(F61,I61,L61)=0,"Sem cotação",ROUND(P61,2))</f>
         <v>53.8</v>
       </c>
       <c r="U61" s="15" t="str">
@@ -8714,16 +8732,16 @@
         <v>60</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D62" s="11" t="n">
         <v>905</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F62" s="12" t="n">
         <v>242.75</v>
@@ -8732,22 +8750,22 @@
         <v>40</v>
       </c>
       <c r="H62" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I62" s="12" t="n">
         <v>331.82</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K62" s="10" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="L62" s="12" t="n">
         <v>339.58</v>
       </c>
       <c r="M62" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N62" s="12" t="n">
         <f aca="false">IF(COUNT(F62,I62,L62)=0,"",MIN(F62,I62,L62))</f>
@@ -8766,14 +8784,14 @@
         <v>339.58</v>
       </c>
       <c r="R62" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S62" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R62),ROUNDDOWN(R62*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T62" s="14" t="n">
-        <f aca="false">IF(COUNT(F62,I62,L62)=0,"Sem cotação",IF(ISNUMBER(S62),MIN(ROUND(P62,2),S62),ROUND(P62,2)))</f>
+        <f aca="false">IF(COUNT(F62,I62,L62)=0,"Sem cotação",ROUND(P62,2))</f>
         <v>331.82</v>
       </c>
       <c r="U62" s="15" t="str">
@@ -8790,16 +8808,16 @@
         <v>61</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D63" s="11" t="n">
         <v>120</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F63" s="12" t="n">
         <v>105.75</v>
@@ -8808,16 +8826,16 @@
         <v>40</v>
       </c>
       <c r="H63" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>143.39</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K63" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L63" s="12"/>
       <c r="M63" s="10"/>
@@ -8838,14 +8856,14 @@
         <v>143.39</v>
       </c>
       <c r="R63" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S63" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R63),ROUNDDOWN(R63*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T63" s="14" t="n">
-        <f aca="false">IF(COUNT(F63,I63,L63)=0,"Sem cotação",IF(ISNUMBER(S63),MIN(ROUND(P63,2),S63),ROUND(P63,2)))</f>
+        <f aca="false">IF(COUNT(F63,I63,L63)=0,"Sem cotação",ROUND(P63,2))</f>
         <v>124.57</v>
       </c>
       <c r="U63" s="15" t="str">
@@ -8862,16 +8880,16 @@
         <v>62</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D64" s="11" t="n">
         <v>135</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F64" s="12" t="n">
         <v>178.25</v>
@@ -8880,22 +8898,22 @@
         <v>40</v>
       </c>
       <c r="H64" s="10" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="I64" s="12" t="n">
         <v>240.59</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="K64" s="10" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="L64" s="12" t="n">
         <v>259.88</v>
       </c>
       <c r="M64" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N64" s="12" t="n">
         <f aca="false">IF(COUNT(F64,I64,L64)=0,"",MIN(F64,I64,L64))</f>
@@ -8914,14 +8932,14 @@
         <v>259.88</v>
       </c>
       <c r="R64" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S64" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R64),ROUNDDOWN(R64*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T64" s="14" t="n">
-        <f aca="false">IF(COUNT(F64,I64,L64)=0,"Sem cotação",IF(ISNUMBER(S64),MIN(ROUND(P64,2),S64),ROUND(P64,2)))</f>
+        <f aca="false">IF(COUNT(F64,I64,L64)=0,"Sem cotação",ROUND(P64,2))</f>
         <v>240.59</v>
       </c>
       <c r="U64" s="15" t="str">
@@ -8938,16 +8956,16 @@
         <v>63</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D65" s="11" t="n">
         <v>72</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F65" s="12" t="n">
         <v>306.75</v>
@@ -8956,22 +8974,22 @@
         <v>40</v>
       </c>
       <c r="H65" s="10" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>415.75</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K65" s="10" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="L65" s="12" t="n">
         <v>514.65</v>
       </c>
       <c r="M65" s="13" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="N65" s="12" t="n">
         <f aca="false">IF(COUNT(F65,I65,L65)=0,"",MIN(F65,I65,L65))</f>
@@ -8990,14 +9008,14 @@
         <v>514.65</v>
       </c>
       <c r="R65" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S65" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R65),ROUNDDOWN(R65*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T65" s="14" t="n">
-        <f aca="false">IF(COUNT(F65,I65,L65)=0,"Sem cotação",IF(ISNUMBER(S65),MIN(ROUND(P65,2),S65),ROUND(P65,2)))</f>
+        <f aca="false">IF(COUNT(F65,I65,L65)=0,"Sem cotação",ROUND(P65,2))</f>
         <v>415.75</v>
       </c>
       <c r="U65" s="15" t="str">
@@ -9014,16 +9032,16 @@
         <v>64</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D66" s="11" t="n">
         <v>72</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="F66" s="12" t="n">
         <v>72.5</v>
@@ -9032,16 +9050,16 @@
         <v>40</v>
       </c>
       <c r="H66" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="I66" s="12" t="n">
         <v>156</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K66" s="10" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="L66" s="12"/>
       <c r="M66" s="10"/>
@@ -9062,14 +9080,14 @@
         <v>156</v>
       </c>
       <c r="R66" s="12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="S66" s="12" t="str">
         <f aca="false">IF(ISNUMBER(R66),ROUNDDOWN(R66*0.96,2),"—")</f>
         <v>—</v>
       </c>
       <c r="T66" s="14" t="n">
-        <f aca="false">IF(COUNT(F66,I66,L66)=0,"Sem cotação",IF(ISNUMBER(S66),MIN(ROUND(P66,2),S66),ROUND(P66,2)))</f>
+        <f aca="false">IF(COUNT(F66,I66,L66)=0,"Sem cotação",ROUND(P66,2))</f>
         <v>114.25</v>
       </c>
       <c r="U66" s="15" t="str">
@@ -9298,7 +9316,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -9308,18 +9326,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="17" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9338,7 +9356,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C4" s="18" t="s">
         <v>40</v>
@@ -9349,7 +9367,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="C5" s="18" t="s">
         <v>42</v>
@@ -9360,7 +9378,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>48</v>
@@ -9393,7 +9411,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C9" s="18" t="s">
         <v>55</v>
@@ -9470,10 +9488,10 @@
         <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>91</v>
+        <v>244</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9481,10 +9499,10 @@
         <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>241</v>
+        <v>92</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9492,10 +9510,10 @@
         <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9503,10 +9521,10 @@
         <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" s="18" t="s">
         <v>99</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9514,10 +9532,10 @@
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9525,10 +9543,10 @@
         <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9536,10 +9554,10 @@
         <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9547,10 +9565,10 @@
         <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>125</v>
+        <v>250</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9558,10 +9576,10 @@
         <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>127</v>
+        <v>251</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9569,10 +9587,10 @@
         <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9580,10 +9598,10 @@
         <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9591,10 +9609,10 @@
         <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9602,10 +9620,10 @@
         <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9613,10 +9631,10 @@
         <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9624,10 +9642,10 @@
         <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9635,10 +9653,10 @@
         <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>194</v>
+        <v>154</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>195</v>
+        <v>155</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9646,10 +9664,32 @@
         <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>225</v>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="C34" s="18" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>
@@ -9664,26 +9704,28 @@
     <hyperlink ref="C10" r:id="rId8" display="https://cisamusep.org.br/uploads/pagina/arquivos/Tabela-Cisamusep-1206.pdf"/>
     <hyperlink ref="C11" r:id="rId9" display="https://www.cispara.mg.gov.br/transparencia/tabela-oficial-de-procedimentos/tabela-oficial-de-procedimentos-2026/543-01-tabela-oficial-de-consultas-procedimentos-e-servicos-janeiro-de-2026/file"/>
     <hyperlink ref="C12" r:id="rId10" display="https://www.sarapui.sp.gov.br/ata-registro-preco/page/1/download/839"/>
-    <hyperlink ref="C13" r:id="rId11" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
+    <hyperlink ref="C13" r:id="rId11" display="https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file"/>
     <hyperlink ref="C14" r:id="rId12" display="https://quilombo.sc.gov.br/uploads/sites/96/2025/04/5-EDITAL-DE-CREDENCIAMENTO-05-2025-exames-imagem.pdf"/>
-    <hyperlink ref="C15" r:id="rId13" display="https://conselheirolafaiete.mg.gov.br/v1/wp-content/uploads/2026/05/EDITAL-CRED-009.2025-EXAMES-DE-IMAGEM.pdf"/>
-    <hyperlink ref="C16" r:id="rId14" display="https://inovacapixaba.es.gov.br/media/Editais/Licita%C3%A7%C3%A3o/Preg%C3%A3o/Edital_n%C2%BA_068_2025_2024_T5Q1Z_Servi%C3%A7os_M%C3%A9dicos_de_Ecocardiograma_REPUBL..pdf"/>
-    <hyperlink ref="C17" r:id="rId15" display="https://pncp.gov.br/app/editais/05193057000178/2026/124"/>
-    <hyperlink ref="C18" r:id="rId16" display="https://pncp.gov.br/pncp-api/v1/orgaos/01603719000180/compras/2025/95/arquivos/1"/>
-    <hyperlink ref="C19" r:id="rId17" display="https://www.cimexpandidasul.com.br/institucional/tabela-de-servicos/562-tabela-atualizada-01-01-2026/file"/>
+    <hyperlink ref="C15" r:id="rId13" display="https://www.cisamusep.org.br/uploads/arquivoChamamento/TABELA-CISAMUSEP-2026.pdf"/>
+    <hyperlink ref="C16" r:id="rId14" display="https://lucasdorioverde.mt.gov.br/arquivos//licitacoes/3709/edital.pdf"/>
+    <hyperlink ref="C17" r:id="rId15" display="https://inovacapixaba.es.gov.br/media/Editais/Licita%C3%A7%C3%A3o/Preg%C3%A3o/Edital_n%C2%BA_068_2025_2024_T5Q1Z_Servi%C3%A7os_M%C3%A9dicos_de_Ecocardiograma_REPUBL..pdf"/>
+    <hyperlink ref="C18" r:id="rId16" display="https://pncp.gov.br/app/editais/05193057000178/2026/124"/>
+    <hyperlink ref="C19" r:id="rId17" display="https://pncp.gov.br/pncp-api/v1/orgaos/01603719000180/compras/2025/95/arquivos/1"/>
     <hyperlink ref="C20" r:id="rId18" display="https://www.praiagrande.sp.gov.br/arquivos/ChamadaPublica/46047.pdf"/>
-    <hyperlink ref="C21" r:id="rId19" display="https://www.vargem.sc.gov.br/uploads/sites/94/2025/03/Edital-FMS-VRG-2025_013_PE_005_90023-Ultrassom.pdf"/>
-    <hyperlink ref="C22" r:id="rId20" display="https://pncp.gov.br/app/editais/13674817000197/2026/64"/>
-    <hyperlink ref="C23" r:id="rId21" display="https://www12.senado.leg.br/institucional/sis/pdfs/tabela-odontologia-v2-nv.pdf"/>
-    <hyperlink ref="C24" r:id="rId22" display="https://planassiste.mpu.mp.br/o-plan-assiste/normas/normas-cpmplementares/anexo_v_nc_50.pdf/@@download/file/Anexo_V_NC_50.pdf"/>
-    <hyperlink ref="C25" r:id="rId23" display="https://www.gov.br/mme/pt-br/assuntos/orgaos-vinculados/nuclep/plano-de-saude/orientacoes-ao-credenciado/TABELADEPROCEDIMENTOSODONTOLGICOS.pdf"/>
-    <hyperlink ref="C26" r:id="rId24" display="https://www.bcb.gov.br/content/acessoinformacao/bcsaude_docs/Tabela_de_Reembolsos_procedimentos_odontologicos_2026.pdf"/>
-    <hyperlink ref="C27" r:id="rId25" display="https://www.bcb.gov.br/content/acessoinformacao/bcsaude_docs/Tabela_Procedimentos_Odontologicos_Edital_Chamamento_26.pdf"/>
-    <hyperlink ref="C28" r:id="rId26" display="https://fiosaude.org.br/wp-content/uploads/2025/04/tabela_Odontologica_Fiosaude_2025-2026.pdf"/>
-    <hyperlink ref="C29" r:id="rId27" display="https://www.stj.jus.br/sites/portalp/SiteAssets/Paginas/Sob-medida/Publico-interno/Pro-Ser/Informacoes-aos-credenciados/Tabela_Odontologica_PRECOS_2025.pdf"/>
-    <hyperlink ref="C30" r:id="rId28" display="https://www.consud.org/uploads/pagina/arquivos/RESOLUCAO-034-2025-TABELA-DE-PROTESE-ODONTOLOGICA-docx-2.pdf"/>
-    <hyperlink ref="C31" r:id="rId29" display="https://www.tjdft.jus.br/pro-saude/tabelas-proprias-do-pro-saude/tabela-propria-odontologica-ajuste-cynthia.pdf"/>
-    <hyperlink ref="C32" r:id="rId30" display="https://www.trf3.jus.br/documentos/ubas/Odontologia/Credenc_pac_espec_vigencia_1_08_07.pdf"/>
+    <hyperlink ref="C21" r:id="rId19" display="https://copirn.org.br/wp-content/uploads/2025/01/TABELA-DE-SERVICOS-DE-SAUDE-COPIRN-2.pdf"/>
+    <hyperlink ref="C22" r:id="rId20" display="https://www.vargem.sc.gov.br/uploads/sites/94/2025/03/Edital-FMS-VRG-2025_013_PE_005_90023-Ultrassom.pdf"/>
+    <hyperlink ref="C23" r:id="rId21" display="https://ia.mabus.com.br/licitacao/6466406/credenciamento-consorcio-intermunicipal-de-saude-uniao-da-mata-leopoldina-mg"/>
+    <hyperlink ref="C24" r:id="rId22" display="https://pncp.gov.br/app/editais/13674817000197/2026/64"/>
+    <hyperlink ref="C25" r:id="rId23" display="https://www12.senado.leg.br/institucional/sis/pdfs/tabela-odontologia-v2-nv.pdf"/>
+    <hyperlink ref="C26" r:id="rId24" display="https://planassiste.mpu.mp.br/o-plan-assiste/normas/normas-cpmplementares/anexo_v_nc_50.pdf/@@download/file/Anexo_V_NC_50.pdf"/>
+    <hyperlink ref="C27" r:id="rId25" display="https://www.gov.br/mme/pt-br/assuntos/orgaos-vinculados/nuclep/plano-de-saude/orientacoes-ao-credenciado/TABELADEPROCEDIMENTOSODONTOLGICOS.pdf"/>
+    <hyperlink ref="C28" r:id="rId26" display="https://www.bcb.gov.br/content/acessoinformacao/bcsaude_docs/Tabela_de_Reembolsos_procedimentos_odontologicos_2026.pdf"/>
+    <hyperlink ref="C29" r:id="rId27" display="https://www.bcb.gov.br/content/acessoinformacao/bcsaude_docs/Tabela_Procedimentos_Odontologicos_Edital_Chamamento_26.pdf"/>
+    <hyperlink ref="C30" r:id="rId28" display="https://fiosaude.org.br/wp-content/uploads/2025/04/tabela_Odontologica_Fiosaude_2025-2026.pdf"/>
+    <hyperlink ref="C31" r:id="rId29" display="https://www.stj.jus.br/sites/portalp/SiteAssets/Paginas/Sob-medida/Publico-interno/Pro-Ser/Informacoes-aos-credenciados/Tabela_Odontologica_PRECOS_2025.pdf"/>
+    <hyperlink ref="C32" r:id="rId30" display="https://www.consud.org/uploads/pagina/arquivos/RESOLUCAO-034-2025-TABELA-DE-PROTESE-ODONTOLOGICA-docx-2.pdf"/>
+    <hyperlink ref="C33" r:id="rId31" display="https://www.tjdft.jus.br/pro-saude/tabelas-proprias-do-pro-saude/tabela-propria-odontologica-ajuste-cynthia.pdf"/>
+    <hyperlink ref="C34" r:id="rId32" display="https://www.trf3.jus.br/documentos/ubas/Odontologia/Credenc_pac_espec_vigencia_1_08_07.pdf"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
